--- a/research/traditional_assets/database/data/luxembourg/luxembourg_apparel.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_apparel.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sehk_1910" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0737</v>
+        <v>-0.0397</v>
+      </c>
+      <c r="E2">
+        <v>-0.0036</v>
       </c>
       <c r="G2">
-        <v>-0.1031570594570085</v>
+        <v>0.07856015851465893</v>
       </c>
       <c r="H2">
-        <v>-0.1141529218386896</v>
+        <v>0.07217554030748907</v>
       </c>
       <c r="I2">
-        <v>-0.0339232991512608</v>
+        <v>0.1492077325955959</v>
       </c>
       <c r="J2">
-        <v>-0.0339232991512608</v>
+        <v>0.1411727513788011</v>
       </c>
       <c r="K2">
-        <v>-340.9</v>
+        <v>276.5</v>
       </c>
       <c r="L2">
-        <v>-0.1932211075213966</v>
+        <v>0.1014567203610612</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1153.5</v>
+        <v>801</v>
       </c>
       <c r="V2">
-        <v>0.3952372794243618</v>
+        <v>0.2112843238110311</v>
       </c>
       <c r="W2">
-        <v>-0.4089491362763915</v>
+        <v>0.5350232198142415</v>
       </c>
       <c r="X2">
-        <v>0.08157373016425422</v>
+        <v>0.113930566001772</v>
       </c>
       <c r="Y2">
-        <v>-0.4905228664406457</v>
+        <v>0.4210926538124695</v>
       </c>
       <c r="Z2">
-        <v>0.7870877517030995</v>
+        <v>1.516818835617769</v>
       </c>
       <c r="AA2">
-        <v>-0.02670061325931752</v>
+        <v>0.2141334883673499</v>
       </c>
       <c r="AB2">
-        <v>0.05945914421299377</v>
+        <v>0.09140173899135957</v>
       </c>
       <c r="AC2">
-        <v>-0.08615975747231129</v>
+        <v>0.1227317493759903</v>
       </c>
       <c r="AD2">
-        <v>3260.7</v>
+        <v>2550.6</v>
       </c>
       <c r="AE2">
-        <v>2.754383462847098</v>
+        <v>2.320831786112143</v>
       </c>
       <c r="AF2">
-        <v>3263.454383462847</v>
+        <v>2552.920831786112</v>
       </c>
       <c r="AG2">
-        <v>2109.954383462847</v>
+        <v>1751.920831786112</v>
       </c>
       <c r="AH2">
-        <v>0.52790010747941</v>
+        <v>0.4024136899101821</v>
       </c>
       <c r="AI2">
-        <v>0.8558635821236629</v>
+        <v>0.742555370282566</v>
       </c>
       <c r="AJ2">
-        <v>0.4196029679421743</v>
+        <v>0.3160588576069983</v>
       </c>
       <c r="AK2">
-        <v>0.793348839408052</v>
+        <v>0.6643560834517556</v>
       </c>
       <c r="AL2">
-        <v>134.9</v>
+        <v>112.7</v>
       </c>
       <c r="AM2">
-        <v>131.3</v>
+        <v>106.3</v>
       </c>
       <c r="AN2">
-        <v>130.428</v>
+        <v>5.441860465116279</v>
       </c>
       <c r="AO2">
-        <v>-0.4610822831727205</v>
+        <v>3.590062111801242</v>
       </c>
       <c r="AP2">
-        <v>84.39817533851388</v>
+        <v>3.737829809656736</v>
       </c>
       <c r="AQ2">
-        <v>-0.4737242955064737</v>
+        <v>3.806208842897461</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0737</v>
+        <v>-0.0397</v>
+      </c>
+      <c r="E3">
+        <v>-0.0036</v>
       </c>
       <c r="G3">
-        <v>-0.1031570594570085</v>
+        <v>0.07856015851465893</v>
       </c>
       <c r="H3">
-        <v>-0.1141529218386896</v>
+        <v>0.07217554030748907</v>
       </c>
       <c r="I3">
-        <v>-0.0339232991512608</v>
+        <v>0.1492077325955959</v>
       </c>
       <c r="J3">
-        <v>-0.0339232991512608</v>
+        <v>0.1411727513788011</v>
       </c>
       <c r="K3">
-        <v>-340.9</v>
+        <v>276.5</v>
       </c>
       <c r="L3">
-        <v>-0.1932211075213966</v>
+        <v>0.1014567203610612</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1153.5</v>
+        <v>801</v>
       </c>
       <c r="V3">
-        <v>0.3952372794243618</v>
+        <v>0.2112843238110311</v>
       </c>
       <c r="W3">
-        <v>-0.4089491362763915</v>
+        <v>0.5350232198142415</v>
       </c>
       <c r="X3">
-        <v>0.08157373016425422</v>
+        <v>0.113930566001772</v>
       </c>
       <c r="Y3">
-        <v>-0.4905228664406457</v>
+        <v>0.4210926538124695</v>
       </c>
       <c r="Z3">
-        <v>0.7870877517030995</v>
+        <v>1.516818835617769</v>
       </c>
       <c r="AA3">
-        <v>-0.02670061325931752</v>
+        <v>0.2141334883673499</v>
       </c>
       <c r="AB3">
-        <v>0.05945914421299377</v>
+        <v>0.09140173899135957</v>
       </c>
       <c r="AC3">
-        <v>-0.08615975747231129</v>
+        <v>0.1227317493759903</v>
       </c>
       <c r="AD3">
-        <v>3260.7</v>
+        <v>2550.6</v>
       </c>
       <c r="AE3">
-        <v>2.754383462847098</v>
+        <v>2.320831786112143</v>
       </c>
       <c r="AF3">
-        <v>3263.454383462847</v>
+        <v>2552.920831786112</v>
       </c>
       <c r="AG3">
-        <v>2109.954383462847</v>
+        <v>1751.920831786112</v>
       </c>
       <c r="AH3">
-        <v>0.52790010747941</v>
+        <v>0.4024136899101821</v>
       </c>
       <c r="AI3">
-        <v>0.8558635821236629</v>
+        <v>0.742555370282566</v>
       </c>
       <c r="AJ3">
-        <v>0.4196029679421743</v>
+        <v>0.3160588576069983</v>
       </c>
       <c r="AK3">
-        <v>0.793348839408052</v>
+        <v>0.6643560834517556</v>
       </c>
       <c r="AL3">
-        <v>134.9</v>
+        <v>112.7</v>
       </c>
       <c r="AM3">
-        <v>131.3</v>
+        <v>106.3</v>
       </c>
       <c r="AN3">
-        <v>130.428</v>
+        <v>5.441860465116279</v>
       </c>
       <c r="AO3">
-        <v>-0.4610822831727205</v>
+        <v>3.590062111801242</v>
       </c>
       <c r="AP3">
-        <v>84.39817533851388</v>
+        <v>3.737829809656736</v>
       </c>
       <c r="AQ3">
-        <v>-0.4737242955064737</v>
+        <v>3.806208842897461</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Samsonite International S.A. (SEHK:1910)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SEHK:1910</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apparel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.402413689910182</v>
+      </c>
+      <c r="F2">
+        <v>0.25</v>
+      </c>
+      <c r="G2">
+        <v>3791.1</v>
+      </c>
+      <c r="H2">
+        <v>5364.39934352471</v>
+      </c>
+      <c r="I2">
+        <v>5543.02083178611</v>
+      </c>
+      <c r="J2">
+        <v>6149.40455147123</v>
+      </c>
+      <c r="K2">
+        <v>2552.92083178611</v>
+      </c>
+      <c r="L2">
+        <v>1586.00520794653</v>
+      </c>
+      <c r="M2">
+        <v>0.0914017389913596</v>
+      </c>
+      <c r="N2">
+        <v>0.086214759035088</v>
+      </c>
+      <c r="O2">
+        <v>0.05794632</v>
+      </c>
+      <c r="P2">
+        <v>0.041283</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.113930566001772</v>
+      </c>
+      <c r="T2">
+        <v>0.101192012046784</v>
+      </c>
+      <c r="U2">
+        <v>1.27033333195787</v>
+      </c>
+      <c r="V2">
+        <v>1.05494550046484</v>
+      </c>
+      <c r="W2">
+        <v>4.66695704700847</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>-6.938893903907228e-18</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>3791.1</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.07719999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>468.7</v>
+      </c>
+      <c r="AH2">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="AI2">
+        <v>104.4</v>
+      </c>
+      <c r="AJ2">
+        <v>2552.920831786112</v>
+      </c>
+      <c r="AK2">
+        <v>2550.6</v>
+      </c>
+      <c r="AL2">
+        <v>112.7</v>
+      </c>
+      <c r="AM2">
+        <v>2550.6</v>
+      </c>
+      <c r="AN2">
+        <v>801</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08870562473746919</v>
+      </c>
+      <c r="C2">
+        <v>6643.478409019273</v>
+      </c>
+      <c r="D2">
+        <v>5842.478409019273</v>
+      </c>
+      <c r="E2">
+        <v>-2552.920831786112</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>801</v>
+      </c>
+      <c r="H2">
+        <v>3791.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>468.7</v>
+      </c>
+      <c r="K2">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L2">
+        <v>407.1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>407.1</v>
+      </c>
+      <c r="O2">
+        <v>101.53074</v>
+      </c>
+      <c r="P2">
+        <v>305.56926</v>
+      </c>
+      <c r="Q2">
+        <v>367.16926</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08870562473746919</v>
+      </c>
+      <c r="T2">
+        <v>0.8438213889496441</v>
+      </c>
+      <c r="U2">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V2">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08853618430937395</v>
+      </c>
+      <c r="C3">
+        <v>6599.942261628235</v>
+      </c>
+      <c r="D3">
+        <v>5862.382469946097</v>
+      </c>
+      <c r="E3">
+        <v>-2489.480623468251</v>
+      </c>
+      <c r="F3">
+        <v>63.44020831786113</v>
+      </c>
+      <c r="G3">
+        <v>801</v>
+      </c>
+      <c r="H3">
+        <v>3791.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>468.7</v>
+      </c>
+      <c r="K3">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L3">
+        <v>407.1</v>
+      </c>
+      <c r="M3">
+        <v>2.899217520126253</v>
+      </c>
+      <c r="N3">
+        <v>404.2007824798738</v>
+      </c>
+      <c r="O3">
+        <v>100.8076751504805</v>
+      </c>
+      <c r="P3">
+        <v>303.3931073293933</v>
+      </c>
+      <c r="Q3">
+        <v>364.9931073293932</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08908400011047873</v>
+      </c>
+      <c r="T3">
+        <v>0.8502190892985896</v>
+      </c>
+      <c r="U3">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V3">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>140.4171978038653</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08836674388127869</v>
+      </c>
+      <c r="C4">
+        <v>6556.542195502184</v>
+      </c>
+      <c r="D4">
+        <v>5882.422612137906</v>
+      </c>
+      <c r="E4">
+        <v>-2426.04041515039</v>
+      </c>
+      <c r="F4">
+        <v>126.8804166357223</v>
+      </c>
+      <c r="G4">
+        <v>801</v>
+      </c>
+      <c r="H4">
+        <v>3791.1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>468.7</v>
+      </c>
+      <c r="K4">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L4">
+        <v>407.1</v>
+      </c>
+      <c r="M4">
+        <v>5.798435040252506</v>
+      </c>
+      <c r="N4">
+        <v>401.3015649597475</v>
+      </c>
+      <c r="O4">
+        <v>100.0846103009611</v>
+      </c>
+      <c r="P4">
+        <v>301.2169546587864</v>
+      </c>
+      <c r="Q4">
+        <v>362.8169546587864</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08947009742987622</v>
+      </c>
+      <c r="T4">
+        <v>0.8567473549607789</v>
+      </c>
+      <c r="U4">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V4">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>70.20859890193267</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08819730345318345</v>
+      </c>
+      <c r="C5">
+        <v>6513.279610980779</v>
+      </c>
+      <c r="D5">
+        <v>5902.600235934362</v>
+      </c>
+      <c r="E5">
+        <v>-2362.600206832529</v>
+      </c>
+      <c r="F5">
+        <v>190.3206249535834</v>
+      </c>
+      <c r="G5">
+        <v>801</v>
+      </c>
+      <c r="H5">
+        <v>3791.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>468.7</v>
+      </c>
+      <c r="K5">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L5">
+        <v>407.1</v>
+      </c>
+      <c r="M5">
+        <v>8.697652560378758</v>
+      </c>
+      <c r="N5">
+        <v>398.4023474396213</v>
+      </c>
+      <c r="O5">
+        <v>99.36154545144157</v>
+      </c>
+      <c r="P5">
+        <v>299.0408019881797</v>
+      </c>
+      <c r="Q5">
+        <v>360.6408019881797</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08986415551874583</v>
+      </c>
+      <c r="T5">
+        <v>0.8634102240386833</v>
+      </c>
+      <c r="U5">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V5">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>46.80573260128845</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08802786302508819</v>
+      </c>
+      <c r="C6">
+        <v>6470.155927683356</v>
+      </c>
+      <c r="D6">
+        <v>5922.9167609548</v>
+      </c>
+      <c r="E6">
+        <v>-2299.159998514668</v>
+      </c>
+      <c r="F6">
+        <v>253.7608332714445</v>
+      </c>
+      <c r="G6">
+        <v>801</v>
+      </c>
+      <c r="H6">
+        <v>3791.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>468.7</v>
+      </c>
+      <c r="K6">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L6">
+        <v>407.1</v>
+      </c>
+      <c r="M6">
+        <v>11.59687008050501</v>
+      </c>
+      <c r="N6">
+        <v>395.503129919495</v>
+      </c>
+      <c r="O6">
+        <v>98.63848060192208</v>
+      </c>
+      <c r="P6">
+        <v>296.8646493175729</v>
+      </c>
+      <c r="Q6">
+        <v>358.4646493175729</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09026642315113353</v>
+      </c>
+      <c r="T6">
+        <v>0.8702119028890442</v>
+      </c>
+      <c r="U6">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V6">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>35.10429945096634</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08785842259699295</v>
+      </c>
+      <c r="C7">
+        <v>6427.172584841845</v>
+      </c>
+      <c r="D7">
+        <v>5943.373626431151</v>
+      </c>
+      <c r="E7">
+        <v>-2235.719790196807</v>
+      </c>
+      <c r="F7">
+        <v>317.2010415893056</v>
+      </c>
+      <c r="G7">
+        <v>801</v>
+      </c>
+      <c r="H7">
+        <v>3791.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>468.7</v>
+      </c>
+      <c r="K7">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L7">
+        <v>407.1</v>
+      </c>
+      <c r="M7">
+        <v>14.49608760063126</v>
+      </c>
+      <c r="N7">
+        <v>392.6039123993688</v>
+      </c>
+      <c r="O7">
+        <v>97.91541575240259</v>
+      </c>
+      <c r="P7">
+        <v>294.6884966469662</v>
+      </c>
+      <c r="Q7">
+        <v>356.2884966469662</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09067715957578205</v>
+      </c>
+      <c r="T7">
+        <v>0.87715677497836</v>
+      </c>
+      <c r="U7">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V7">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>28.08343956077307</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.0876889821688977</v>
+      </c>
+      <c r="C8">
+        <v>6384.331041640665</v>
+      </c>
+      <c r="D8">
+        <v>5963.972291547831</v>
+      </c>
+      <c r="E8">
+        <v>-2172.279581878945</v>
+      </c>
+      <c r="F8">
+        <v>380.6412499071668</v>
+      </c>
+      <c r="G8">
+        <v>801</v>
+      </c>
+      <c r="H8">
+        <v>3791.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>468.7</v>
+      </c>
+      <c r="K8">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L8">
+        <v>407.1</v>
+      </c>
+      <c r="M8">
+        <v>17.39530512075752</v>
+      </c>
+      <c r="N8">
+        <v>389.7046948792425</v>
+      </c>
+      <c r="O8">
+        <v>97.19235090288311</v>
+      </c>
+      <c r="P8">
+        <v>292.5123439763594</v>
+      </c>
+      <c r="Q8">
+        <v>354.1123439763593</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09109663507329543</v>
+      </c>
+      <c r="T8">
+        <v>0.8842494103036187</v>
+      </c>
+      <c r="U8">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V8">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>23.40286630064422</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08751954174080245</v>
+      </c>
+      <c r="C9">
+        <v>6341.632777563666</v>
+      </c>
+      <c r="D9">
+        <v>5984.714235788694</v>
+      </c>
+      <c r="E9">
+        <v>-2108.839373561084</v>
+      </c>
+      <c r="F9">
+        <v>444.0814582250279</v>
+      </c>
+      <c r="G9">
+        <v>801</v>
+      </c>
+      <c r="H9">
+        <v>3791.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>468.7</v>
+      </c>
+      <c r="K9">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L9">
+        <v>407.1</v>
+      </c>
+      <c r="M9">
+        <v>20.29452264088377</v>
+      </c>
+      <c r="N9">
+        <v>386.8054773591163</v>
+      </c>
+      <c r="O9">
+        <v>96.46928605336362</v>
+      </c>
+      <c r="P9">
+        <v>290.3361913057527</v>
+      </c>
+      <c r="Q9">
+        <v>351.9361913057526</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09152513154924996</v>
+      </c>
+      <c r="T9">
+        <v>0.8914945754208186</v>
+      </c>
+      <c r="U9">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V9">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>20.05959968626648</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08735010131270722</v>
+      </c>
+      <c r="C10">
+        <v>6299.079292748363</v>
+      </c>
+      <c r="D10">
+        <v>6005.600959291251</v>
+      </c>
+      <c r="E10">
+        <v>-2045.399165243223</v>
+      </c>
+      <c r="F10">
+        <v>507.521666542889</v>
+      </c>
+      <c r="G10">
+        <v>801</v>
+      </c>
+      <c r="H10">
+        <v>3791.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>468.7</v>
+      </c>
+      <c r="K10">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L10">
+        <v>407.1</v>
+      </c>
+      <c r="M10">
+        <v>23.19374016101002</v>
+      </c>
+      <c r="N10">
+        <v>383.90625983899</v>
+      </c>
+      <c r="O10">
+        <v>95.74622120384414</v>
+      </c>
+      <c r="P10">
+        <v>288.1600386351459</v>
+      </c>
+      <c r="Q10">
+        <v>349.7600386351459</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09196294316598611</v>
+      </c>
+      <c r="T10">
+        <v>0.8988972441275227</v>
+      </c>
+      <c r="U10">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V10">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>17.55214972548317</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08718066088461196</v>
+      </c>
+      <c r="C11">
+        <v>6256.672108347611</v>
+      </c>
+      <c r="D11">
+        <v>6026.633983208361</v>
+      </c>
+      <c r="E11">
+        <v>-1981.958956925362</v>
+      </c>
+      <c r="F11">
+        <v>570.9618748607501</v>
+      </c>
+      <c r="G11">
+        <v>801</v>
+      </c>
+      <c r="H11">
+        <v>3791.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>468.7</v>
+      </c>
+      <c r="K11">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L11">
+        <v>407.1</v>
+      </c>
+      <c r="M11">
+        <v>26.09295768113627</v>
+      </c>
+      <c r="N11">
+        <v>381.0070423188637</v>
+      </c>
+      <c r="O11">
+        <v>95.02315635432464</v>
+      </c>
+      <c r="P11">
+        <v>285.9838859645391</v>
+      </c>
+      <c r="Q11">
+        <v>347.5838859645391</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.0924103770160571</v>
+      </c>
+      <c r="T11">
+        <v>0.9064626088497587</v>
+      </c>
+      <c r="U11">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V11">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>15.60191086709615</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08701122045651671</v>
+      </c>
+      <c r="C12">
+        <v>6214.412766898889</v>
+      </c>
+      <c r="D12">
+        <v>6047.8148500775</v>
+      </c>
+      <c r="E12">
+        <v>-1918.518748607501</v>
+      </c>
+      <c r="F12">
+        <v>634.4020831786113</v>
+      </c>
+      <c r="G12">
+        <v>801</v>
+      </c>
+      <c r="H12">
+        <v>3791.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>468.7</v>
+      </c>
+      <c r="K12">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L12">
+        <v>407.1</v>
+      </c>
+      <c r="M12">
+        <v>28.99217520126253</v>
+      </c>
+      <c r="N12">
+        <v>378.1078247987375</v>
+      </c>
+      <c r="O12">
+        <v>94.30009150480517</v>
+      </c>
+      <c r="P12">
+        <v>283.8077332939324</v>
+      </c>
+      <c r="Q12">
+        <v>345.4077332939323</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09286775384057412</v>
+      </c>
+      <c r="T12">
+        <v>0.9141960927880444</v>
+      </c>
+      <c r="U12">
+        <v>0.04569999999999999</v>
+      </c>
+      <c r="V12">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>14.04171978038653</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08697388562842147</v>
+      </c>
+      <c r="C13">
+        <v>6155.659623467617</v>
+      </c>
+      <c r="D13">
+        <v>6052.501914964089</v>
+      </c>
+      <c r="E13">
+        <v>-1855.07854028964</v>
+      </c>
+      <c r="F13">
+        <v>697.8422914964724</v>
+      </c>
+      <c r="G13">
+        <v>801</v>
+      </c>
+      <c r="H13">
+        <v>3791.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>468.7</v>
+      </c>
+      <c r="K13">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L13">
+        <v>407.1</v>
+      </c>
+      <c r="M13">
+        <v>33.00794038778314</v>
+      </c>
+      <c r="N13">
+        <v>374.0920596122169</v>
+      </c>
+      <c r="O13">
+        <v>93.29855966728691</v>
+      </c>
+      <c r="P13">
+        <v>280.79349994493</v>
+      </c>
+      <c r="Q13">
+        <v>342.3934999449299</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09333540879597918</v>
+      </c>
+      <c r="T13">
+        <v>0.9221033628822467</v>
+      </c>
+      <c r="U13">
+        <v>0.04729999999999999</v>
+      </c>
+      <c r="V13">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W13">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>12.333396001608</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08681645480032621</v>
+      </c>
+      <c r="C14">
+        <v>6112.063662137237</v>
+      </c>
+      <c r="D14">
+        <v>6072.34616195157</v>
+      </c>
+      <c r="E14">
+        <v>-1791.638331971779</v>
+      </c>
+      <c r="F14">
+        <v>761.2824998143335</v>
+      </c>
+      <c r="G14">
+        <v>801</v>
+      </c>
+      <c r="H14">
+        <v>3791.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>468.7</v>
+      </c>
+      <c r="K14">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L14">
+        <v>407.1</v>
+      </c>
+      <c r="M14">
+        <v>36.00866224121797</v>
+      </c>
+      <c r="N14">
+        <v>371.0913377587821</v>
+      </c>
+      <c r="O14">
+        <v>92.55017963704027</v>
+      </c>
+      <c r="P14">
+        <v>278.5411581217418</v>
+      </c>
+      <c r="Q14">
+        <v>340.1411581217417</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09381369227309796</v>
+      </c>
+      <c r="T14">
+        <v>0.9301903436604081</v>
+      </c>
+      <c r="U14">
+        <v>0.04729999999999999</v>
+      </c>
+      <c r="V14">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W14">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>11.30561300147401</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08665902397223096</v>
+      </c>
+      <c r="C15">
+        <v>6068.598254920871</v>
+      </c>
+      <c r="D15">
+        <v>6092.320963053065</v>
+      </c>
+      <c r="E15">
+        <v>-1728.198123653917</v>
+      </c>
+      <c r="F15">
+        <v>824.7227081321946</v>
+      </c>
+      <c r="G15">
+        <v>801</v>
+      </c>
+      <c r="H15">
+        <v>3791.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>468.7</v>
+      </c>
+      <c r="K15">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L15">
+        <v>407.1</v>
+      </c>
+      <c r="M15">
+        <v>39.0093840946528</v>
+      </c>
+      <c r="N15">
+        <v>368.0906159053472</v>
+      </c>
+      <c r="O15">
+        <v>91.80179960679362</v>
+      </c>
+      <c r="P15">
+        <v>276.2888162985536</v>
+      </c>
+      <c r="Q15">
+        <v>337.8888162985536</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09430297077267927</v>
+      </c>
+      <c r="T15">
+        <v>0.9384632320426652</v>
+      </c>
+      <c r="U15">
+        <v>0.04729999999999999</v>
+      </c>
+      <c r="V15">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W15">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>10.43595046289908</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08690091234413573</v>
+      </c>
+      <c r="C16">
+        <v>5974.521172434576</v>
+      </c>
+      <c r="D16">
+        <v>6061.684088884632</v>
+      </c>
+      <c r="E16">
+        <v>-1664.757915336056</v>
+      </c>
+      <c r="F16">
+        <v>888.1629164500558</v>
+      </c>
+      <c r="G16">
+        <v>801</v>
+      </c>
+      <c r="H16">
+        <v>3791.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>468.7</v>
+      </c>
+      <c r="K16">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L16">
+        <v>407.1</v>
+      </c>
+      <c r="M16">
+        <v>45.38512503059785</v>
+      </c>
+      <c r="N16">
+        <v>361.7148749694022</v>
+      </c>
+      <c r="O16">
+        <v>90.21168981736892</v>
+      </c>
+      <c r="P16">
+        <v>271.5031851520332</v>
+      </c>
+      <c r="Q16">
+        <v>333.1031851520332</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09480362784201829</v>
+      </c>
+      <c r="T16">
+        <v>0.9469285131779981</v>
+      </c>
+      <c r="U16">
+        <v>0.05109999999999999</v>
+      </c>
+      <c r="V16">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W16">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.969899272626007</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08677200431604047</v>
+      </c>
+      <c r="C17">
+        <v>5927.369625680377</v>
+      </c>
+      <c r="D17">
+        <v>6077.972750448293</v>
+      </c>
+      <c r="E17">
+        <v>-1601.317707018195</v>
+      </c>
+      <c r="F17">
+        <v>951.6031247679168</v>
+      </c>
+      <c r="G17">
+        <v>801</v>
+      </c>
+      <c r="H17">
+        <v>3791.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>468.7</v>
+      </c>
+      <c r="K17">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L17">
+        <v>407.1</v>
+      </c>
+      <c r="M17">
+        <v>48.62691967564054</v>
+      </c>
+      <c r="N17">
+        <v>358.4730803243595</v>
+      </c>
+      <c r="O17">
+        <v>89.40318623289528</v>
+      </c>
+      <c r="P17">
+        <v>269.0698940914642</v>
+      </c>
+      <c r="Q17">
+        <v>330.6698940914642</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09531606507769466</v>
+      </c>
+      <c r="T17">
+        <v>0.9555929773988681</v>
+      </c>
+      <c r="U17">
+        <v>0.05109999999999999</v>
+      </c>
+      <c r="V17">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W17">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.371905987784274</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08664309628794523</v>
+      </c>
+      <c r="C18">
+        <v>5880.305854986063</v>
+      </c>
+      <c r="D18">
+        <v>6094.349188071841</v>
+      </c>
+      <c r="E18">
+        <v>-1537.877498700334</v>
+      </c>
+      <c r="F18">
+        <v>1015.043333085778</v>
+      </c>
+      <c r="G18">
+        <v>801</v>
+      </c>
+      <c r="H18">
+        <v>3791.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>468.7</v>
+      </c>
+      <c r="K18">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L18">
+        <v>407.1</v>
+      </c>
+      <c r="M18">
+        <v>51.86871432068325</v>
+      </c>
+      <c r="N18">
+        <v>355.2312856793168</v>
+      </c>
+      <c r="O18">
+        <v>88.59468264842162</v>
+      </c>
+      <c r="P18">
+        <v>266.6366030308952</v>
+      </c>
+      <c r="Q18">
+        <v>328.2366030308951</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09584070319993479</v>
+      </c>
+      <c r="T18">
+        <v>0.9644637383869017</v>
+      </c>
+      <c r="U18">
+        <v>0.05109999999999999</v>
+      </c>
+      <c r="V18">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W18">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.848661863547757</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08675663205984997</v>
+      </c>
+      <c r="C19">
+        <v>5802.437472511576</v>
+      </c>
+      <c r="D19">
+        <v>6079.921013915215</v>
+      </c>
+      <c r="E19">
+        <v>-1474.437290382473</v>
+      </c>
+      <c r="F19">
+        <v>1078.483541403639</v>
+      </c>
+      <c r="G19">
+        <v>801</v>
+      </c>
+      <c r="H19">
+        <v>3791.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>468.7</v>
+      </c>
+      <c r="K19">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L19">
+        <v>407.1</v>
+      </c>
+      <c r="M19">
+        <v>57.15962769439287</v>
+      </c>
+      <c r="N19">
+        <v>349.9403723056071</v>
+      </c>
+      <c r="O19">
+        <v>87.27512885301844</v>
+      </c>
+      <c r="P19">
+        <v>262.6652434525887</v>
+      </c>
+      <c r="Q19">
+        <v>324.2652434525887</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09637798320463853</v>
+      </c>
+      <c r="T19">
+        <v>0.9735482526517556</v>
+      </c>
+      <c r="U19">
+        <v>0.05299999999999999</v>
+      </c>
+      <c r="V19">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W19">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.12215975542358</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08664198543175473</v>
+      </c>
+      <c r="C20">
+        <v>5753.566944716799</v>
+      </c>
+      <c r="D20">
+        <v>6094.490694438299</v>
+      </c>
+      <c r="E20">
+        <v>-1410.997082064612</v>
+      </c>
+      <c r="F20">
+        <v>1141.9237497215</v>
+      </c>
+      <c r="G20">
+        <v>801</v>
+      </c>
+      <c r="H20">
+        <v>3791.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>468.7</v>
+      </c>
+      <c r="K20">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L20">
+        <v>407.1</v>
+      </c>
+      <c r="M20">
+        <v>60.5219587352395</v>
+      </c>
+      <c r="N20">
+        <v>346.5780412647605</v>
+      </c>
+      <c r="O20">
+        <v>86.4365634914313</v>
+      </c>
+      <c r="P20">
+        <v>260.1414777733293</v>
+      </c>
+      <c r="Q20">
+        <v>321.7414777733292</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09692836759970089</v>
+      </c>
+      <c r="T20">
+        <v>0.9828543404352642</v>
+      </c>
+      <c r="U20">
+        <v>0.05299999999999999</v>
+      </c>
+      <c r="V20">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W20">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.726484213455604</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08652733880365948</v>
+      </c>
+      <c r="C21">
+        <v>5704.766413062027</v>
+      </c>
+      <c r="D21">
+        <v>6109.130371101388</v>
+      </c>
+      <c r="E21">
+        <v>-1347.556873746751</v>
+      </c>
+      <c r="F21">
+        <v>1205.363958039361</v>
+      </c>
+      <c r="G21">
+        <v>801</v>
+      </c>
+      <c r="H21">
+        <v>3791.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>468.7</v>
+      </c>
+      <c r="K21">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L21">
+        <v>407.1</v>
+      </c>
+      <c r="M21">
+        <v>63.88428977608615</v>
+      </c>
+      <c r="N21">
+        <v>343.2157102239139</v>
+      </c>
+      <c r="O21">
+        <v>85.59799812984414</v>
+      </c>
+      <c r="P21">
+        <v>257.6177120940698</v>
+      </c>
+      <c r="Q21">
+        <v>319.2177120940697</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09749234173291293</v>
+      </c>
+      <c r="T21">
+        <v>0.9923902081640447</v>
+      </c>
+      <c r="U21">
+        <v>0.05299999999999999</v>
+      </c>
+      <c r="V21">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W21">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.372458728536888</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08671293217556424</v>
+      </c>
+      <c r="C22">
+        <v>5617.662153025854</v>
+      </c>
+      <c r="D22">
+        <v>6085.466319383077</v>
+      </c>
+      <c r="E22">
+        <v>-1284.11666542889</v>
+      </c>
+      <c r="F22">
+        <v>1268.804166357223</v>
+      </c>
+      <c r="G22">
+        <v>801</v>
+      </c>
+      <c r="H22">
+        <v>3791.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>468.7</v>
+      </c>
+      <c r="K22">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L22">
+        <v>407.1</v>
+      </c>
+      <c r="M22">
+        <v>69.78422914964723</v>
+      </c>
+      <c r="N22">
+        <v>337.3157708503528</v>
+      </c>
+      <c r="O22">
+        <v>84.12655325007802</v>
+      </c>
+      <c r="P22">
+        <v>253.1892176002748</v>
+      </c>
+      <c r="Q22">
+        <v>314.7892176002748</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09807041521945528</v>
+      </c>
+      <c r="T22">
+        <v>1.002164472586045</v>
+      </c>
+      <c r="U22">
+        <v>0.05499999999999999</v>
+      </c>
+      <c r="V22">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W22">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.833696308760588</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08661329754746899</v>
+      </c>
+      <c r="C23">
+        <v>5566.903002167291</v>
+      </c>
+      <c r="D23">
+        <v>6098.147376842374</v>
+      </c>
+      <c r="E23">
+        <v>-1220.676457111029</v>
+      </c>
+      <c r="F23">
+        <v>1332.244374675083</v>
+      </c>
+      <c r="G23">
+        <v>801</v>
+      </c>
+      <c r="H23">
+        <v>3791.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>468.7</v>
+      </c>
+      <c r="K23">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L23">
+        <v>407.1</v>
+      </c>
+      <c r="M23">
+        <v>73.27344060712959</v>
+      </c>
+      <c r="N23">
+        <v>333.8265593928704</v>
+      </c>
+      <c r="O23">
+        <v>83.25634391258191</v>
+      </c>
+      <c r="P23">
+        <v>250.5702154802885</v>
+      </c>
+      <c r="Q23">
+        <v>312.1702154802884</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09866312347780884</v>
+      </c>
+      <c r="T23">
+        <v>1.012186186740248</v>
+      </c>
+      <c r="U23">
+        <v>0.05499999999999999</v>
+      </c>
+      <c r="V23">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W23">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.555901246438655</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08651366291937373</v>
+      </c>
+      <c r="C24">
+        <v>5516.196811922793</v>
+      </c>
+      <c r="D24">
+        <v>6110.881394915738</v>
+      </c>
+      <c r="E24">
+        <v>-1157.236248793167</v>
+      </c>
+      <c r="F24">
+        <v>1395.684582992945</v>
+      </c>
+      <c r="G24">
+        <v>801</v>
+      </c>
+      <c r="H24">
+        <v>3791.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>468.7</v>
+      </c>
+      <c r="K24">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L24">
+        <v>407.1</v>
+      </c>
+      <c r="M24">
+        <v>76.76265206461196</v>
+      </c>
+      <c r="N24">
+        <v>330.337347935388</v>
+      </c>
+      <c r="O24">
+        <v>82.3861345750858</v>
+      </c>
+      <c r="P24">
+        <v>247.9512133603022</v>
+      </c>
+      <c r="Q24">
+        <v>309.5512133603022</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09927102938381248</v>
+      </c>
+      <c r="T24">
+        <v>1.022464867924045</v>
+      </c>
+      <c r="U24">
+        <v>0.05499999999999999</v>
+      </c>
+      <c r="V24">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W24">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.303360280691442</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08641402829127849</v>
+      </c>
+      <c r="C25">
+        <v>5465.543914760206</v>
+      </c>
+      <c r="D25">
+        <v>6123.668706071013</v>
+      </c>
+      <c r="E25">
+        <v>-1093.796040475306</v>
+      </c>
+      <c r="F25">
+        <v>1459.124791310806</v>
+      </c>
+      <c r="G25">
+        <v>801</v>
+      </c>
+      <c r="H25">
+        <v>3791.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>468.7</v>
+      </c>
+      <c r="K25">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L25">
+        <v>407.1</v>
+      </c>
+      <c r="M25">
+        <v>80.25186352209431</v>
+      </c>
+      <c r="N25">
+        <v>326.8481364779057</v>
+      </c>
+      <c r="O25">
+        <v>81.51592523758971</v>
+      </c>
+      <c r="P25">
+        <v>245.332211240316</v>
+      </c>
+      <c r="Q25">
+        <v>306.932211240316</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09989472505360843</v>
+      </c>
+      <c r="T25">
+        <v>1.033010527839889</v>
+      </c>
+      <c r="U25">
+        <v>0.05499999999999999</v>
+      </c>
+      <c r="V25">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W25">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.07277939892225</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08631439366318325</v>
+      </c>
+      <c r="C26">
+        <v>5414.944645936026</v>
+      </c>
+      <c r="D26">
+        <v>6136.509645564694</v>
+      </c>
+      <c r="E26">
+        <v>-1030.355832157445</v>
+      </c>
+      <c r="F26">
+        <v>1522.564999628667</v>
+      </c>
+      <c r="G26">
+        <v>801</v>
+      </c>
+      <c r="H26">
+        <v>3791.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>468.7</v>
+      </c>
+      <c r="K26">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L26">
+        <v>407.1</v>
+      </c>
+      <c r="M26">
+        <v>83.74107497957668</v>
+      </c>
+      <c r="N26">
+        <v>323.3589250204233</v>
+      </c>
+      <c r="O26">
+        <v>80.64571590009361</v>
+      </c>
+      <c r="P26">
+        <v>242.7132091203297</v>
+      </c>
+      <c r="Q26">
+        <v>304.3132091203297</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1005348337673464</v>
+      </c>
+      <c r="T26">
+        <v>1.04383370512194</v>
+      </c>
+      <c r="U26">
+        <v>0.05499999999999999</v>
+      </c>
+      <c r="V26">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W26">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.861413590633823</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08621475903508799</v>
+      </c>
+      <c r="C27">
+        <v>5364.399343524707</v>
+      </c>
+      <c r="D27">
+        <v>6149.404551471234</v>
+      </c>
+      <c r="E27">
+        <v>-966.915623839584</v>
+      </c>
+      <c r="F27">
+        <v>1586.005207946528</v>
+      </c>
+      <c r="G27">
+        <v>801</v>
+      </c>
+      <c r="H27">
+        <v>3791.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>468.7</v>
+      </c>
+      <c r="K27">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L27">
+        <v>407.1</v>
+      </c>
+      <c r="M27">
+        <v>87.23028643705904</v>
+      </c>
+      <c r="N27">
+        <v>319.869713562941</v>
+      </c>
+      <c r="O27">
+        <v>79.77550656259751</v>
+      </c>
+      <c r="P27">
+        <v>240.0942070003435</v>
+      </c>
+      <c r="Q27">
+        <v>301.6942070003435</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.101192012046784</v>
+      </c>
+      <c r="T27">
+        <v>1.054945500464845</v>
+      </c>
+      <c r="U27">
+        <v>0.05499999999999999</v>
+      </c>
+      <c r="V27">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W27">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.66695704700847</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08685671720699274</v>
+      </c>
+      <c r="C28">
+        <v>5218.81327228488</v>
+      </c>
+      <c r="D28">
+        <v>6067.25868854927</v>
+      </c>
+      <c r="E28">
+        <v>-903.4754155217229</v>
+      </c>
+      <c r="F28">
+        <v>1649.445416264389</v>
+      </c>
+      <c r="G28">
+        <v>801</v>
+      </c>
+      <c r="H28">
+        <v>3791.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>468.7</v>
+      </c>
+      <c r="K28">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L28">
+        <v>407.1</v>
+      </c>
+      <c r="M28">
+        <v>96.98739047634608</v>
+      </c>
+      <c r="N28">
+        <v>310.1126095236539</v>
+      </c>
+      <c r="O28">
+        <v>77.34208481519931</v>
+      </c>
+      <c r="P28">
+        <v>232.7705247084546</v>
+      </c>
+      <c r="Q28">
+        <v>294.3705247084546</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1018669519013415</v>
+      </c>
+      <c r="T28">
+        <v>1.066357614600802</v>
+      </c>
+      <c r="U28">
+        <v>0.05879999999999999</v>
+      </c>
+      <c r="V28">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W28">
+        <v>0.04413527999999999</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.197452864754478</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08678560537889748</v>
+      </c>
+      <c r="C29">
+        <v>5164.364382373087</v>
+      </c>
+      <c r="D29">
+        <v>6076.250006955338</v>
+      </c>
+      <c r="E29">
+        <v>-840.0352072038615</v>
+      </c>
+      <c r="F29">
+        <v>1712.885624582251</v>
+      </c>
+      <c r="G29">
+        <v>801</v>
+      </c>
+      <c r="H29">
+        <v>3791.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>468.7</v>
+      </c>
+      <c r="K29">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L29">
+        <v>407.1</v>
+      </c>
+      <c r="M29">
+        <v>100.7176747254363</v>
+      </c>
+      <c r="N29">
+        <v>306.3823252745637</v>
+      </c>
+      <c r="O29">
+        <v>76.4117519234762</v>
+      </c>
+      <c r="P29">
+        <v>229.9705733510875</v>
+      </c>
+      <c r="Q29">
+        <v>291.5705733510874</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1025603832587637</v>
+      </c>
+      <c r="T29">
+        <v>1.078082389398018</v>
+      </c>
+      <c r="U29">
+        <v>0.05879999999999999</v>
+      </c>
+      <c r="V29">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W29">
+        <v>0.04413527999999999</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.041991647541349</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08759719915080225</v>
+      </c>
+      <c r="C30">
+        <v>4999.86413888925</v>
+      </c>
+      <c r="D30">
+        <v>5975.189971789362</v>
+      </c>
+      <c r="E30">
+        <v>-776.5949988860004</v>
+      </c>
+      <c r="F30">
+        <v>1776.325832900112</v>
+      </c>
+      <c r="G30">
+        <v>801</v>
+      </c>
+      <c r="H30">
+        <v>3791.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>468.7</v>
+      </c>
+      <c r="K30">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L30">
+        <v>407.1</v>
+      </c>
+      <c r="M30">
+        <v>111.908527472707</v>
+      </c>
+      <c r="N30">
+        <v>295.191472527293</v>
+      </c>
+      <c r="O30">
+        <v>73.6207532483069</v>
+      </c>
+      <c r="P30">
+        <v>221.5707192789861</v>
+      </c>
+      <c r="Q30">
+        <v>283.1707192789861</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1032730765983365</v>
+      </c>
+      <c r="T30">
+        <v>1.090132852384045</v>
+      </c>
+      <c r="U30">
+        <v>0.063</v>
+      </c>
+      <c r="V30">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W30">
+        <v>0.0472878</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.637792482787213</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08755761252270698</v>
+      </c>
+      <c r="C31">
+        <v>4941.275226830032</v>
+      </c>
+      <c r="D31">
+        <v>5980.041268048005</v>
+      </c>
+      <c r="E31">
+        <v>-713.1547905681396</v>
+      </c>
+      <c r="F31">
+        <v>1839.766041217973</v>
+      </c>
+      <c r="G31">
+        <v>801</v>
+      </c>
+      <c r="H31">
+        <v>3791.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>468.7</v>
+      </c>
+      <c r="K31">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L31">
+        <v>407.1</v>
+      </c>
+      <c r="M31">
+        <v>115.9052605967323</v>
+      </c>
+      <c r="N31">
+        <v>291.1947394032678</v>
+      </c>
+      <c r="O31">
+        <v>72.62396800717499</v>
+      </c>
+      <c r="P31">
+        <v>218.5707713960928</v>
+      </c>
+      <c r="Q31">
+        <v>280.1707713960927</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1040058458066296</v>
+      </c>
+      <c r="T31">
+        <v>1.102522765031651</v>
+      </c>
+      <c r="U31">
+        <v>0.063</v>
+      </c>
+      <c r="V31">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W31">
+        <v>0.0472878</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.512351362691103</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08911680389461174</v>
+      </c>
+      <c r="C32">
+        <v>4692.528559693683</v>
+      </c>
+      <c r="D32">
+        <v>5794.734809229516</v>
+      </c>
+      <c r="E32">
+        <v>-649.7145822502785</v>
+      </c>
+      <c r="F32">
+        <v>1903.206249535834</v>
+      </c>
+      <c r="G32">
+        <v>801</v>
+      </c>
+      <c r="H32">
+        <v>3791.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>468.7</v>
+      </c>
+      <c r="K32">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L32">
+        <v>407.1</v>
+      </c>
+      <c r="M32">
+        <v>133.4147580924619</v>
+      </c>
+      <c r="N32">
+        <v>273.6852419075381</v>
+      </c>
+      <c r="O32">
+        <v>68.25709933174001</v>
+      </c>
+      <c r="P32">
+        <v>205.4281425757981</v>
+      </c>
+      <c r="Q32">
+        <v>267.028142575798</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1047595512780168</v>
+      </c>
+      <c r="T32">
+        <v>1.115266675183474</v>
+      </c>
+      <c r="U32">
+        <v>0.0701</v>
+      </c>
+      <c r="V32">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W32">
+        <v>0.05261705999999999</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.051386561881429</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09408672166651649</v>
+      </c>
+      <c r="C33">
+        <v>4108.1792678968</v>
+      </c>
+      <c r="D33">
+        <v>5273.825725750495</v>
+      </c>
+      <c r="E33">
+        <v>-586.2743739324173</v>
+      </c>
+      <c r="F33">
+        <v>1966.646457853695</v>
+      </c>
+      <c r="G33">
+        <v>801</v>
+      </c>
+      <c r="H33">
+        <v>3791.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>468.7</v>
+      </c>
+      <c r="K33">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L33">
+        <v>407.1</v>
+      </c>
+      <c r="M33">
+        <v>179.7514862478277</v>
+      </c>
+      <c r="N33">
+        <v>227.3485137521723</v>
+      </c>
+      <c r="O33">
+        <v>56.7007193297918</v>
+      </c>
+      <c r="P33">
+        <v>170.6477944223805</v>
+      </c>
+      <c r="Q33">
+        <v>232.2477944223805</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1055351032848065</v>
+      </c>
+      <c r="T33">
+        <v>1.12837997403535</v>
+      </c>
+      <c r="U33">
+        <v>0.0914</v>
+      </c>
+      <c r="V33">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W33">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.26479351296557</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09426030543842125</v>
+      </c>
+      <c r="C34">
+        <v>4028.23264919033</v>
+      </c>
+      <c r="D34">
+        <v>5257.319315361887</v>
+      </c>
+      <c r="E34">
+        <v>-522.834165614556</v>
+      </c>
+      <c r="F34">
+        <v>2030.086666171556</v>
+      </c>
+      <c r="G34">
+        <v>801</v>
+      </c>
+      <c r="H34">
+        <v>3791.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>468.7</v>
+      </c>
+      <c r="K34">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L34">
+        <v>407.1</v>
+      </c>
+      <c r="M34">
+        <v>185.5499212880802</v>
+      </c>
+      <c r="N34">
+        <v>221.5500787119198</v>
+      </c>
+      <c r="O34">
+        <v>55.25458963075282</v>
+      </c>
+      <c r="P34">
+        <v>166.295489081167</v>
+      </c>
+      <c r="Q34">
+        <v>227.8954890811669</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1063334656447371</v>
+      </c>
+      <c r="T34">
+        <v>1.141878958147575</v>
+      </c>
+      <c r="U34">
+        <v>0.0914</v>
+      </c>
+      <c r="V34">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W34">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.194018715685396</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.094433889210326</v>
+      </c>
+      <c r="C35">
+        <v>3948.389034067344</v>
+      </c>
+      <c r="D35">
+        <v>5240.915908556762</v>
+      </c>
+      <c r="E35">
+        <v>-459.3939572966947</v>
+      </c>
+      <c r="F35">
+        <v>2093.526874489417</v>
+      </c>
+      <c r="G35">
+        <v>801</v>
+      </c>
+      <c r="H35">
+        <v>3791.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>468.7</v>
+      </c>
+      <c r="K35">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L35">
+        <v>407.1</v>
+      </c>
+      <c r="M35">
+        <v>191.3483563283328</v>
+      </c>
+      <c r="N35">
+        <v>215.7516436716673</v>
+      </c>
+      <c r="O35">
+        <v>53.80845993171383</v>
+      </c>
+      <c r="P35">
+        <v>161.9431837399534</v>
+      </c>
+      <c r="Q35">
+        <v>223.5431837399534</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1071556597169045</v>
+      </c>
+      <c r="T35">
+        <v>1.155780897009419</v>
+      </c>
+      <c r="U35">
+        <v>0.0914</v>
+      </c>
+      <c r="V35">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W35">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.127533300058565</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09460747298223074</v>
+      </c>
+      <c r="C36">
+        <v>3868.647461379653</v>
+      </c>
+      <c r="D36">
+        <v>5224.614544186931</v>
+      </c>
+      <c r="E36">
+        <v>-395.9537489788336</v>
+      </c>
+      <c r="F36">
+        <v>2156.967082807279</v>
+      </c>
+      <c r="G36">
+        <v>801</v>
+      </c>
+      <c r="H36">
+        <v>3791.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>468.7</v>
+      </c>
+      <c r="K36">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L36">
+        <v>407.1</v>
+      </c>
+      <c r="M36">
+        <v>197.1467913685852</v>
+      </c>
+      <c r="N36">
+        <v>209.9532086314148</v>
+      </c>
+      <c r="O36">
+        <v>52.36233023267486</v>
+      </c>
+      <c r="P36">
+        <v>157.5908783987399</v>
+      </c>
+      <c r="Q36">
+        <v>219.1908783987399</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1080027687609557</v>
+      </c>
+      <c r="T36">
+        <v>1.170104106745864</v>
+      </c>
+      <c r="U36">
+        <v>0.0914</v>
+      </c>
+      <c r="V36">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W36">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.064958791233313</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09478105675413551</v>
+      </c>
+      <c r="C37">
+        <v>3789.006981900217</v>
+      </c>
+      <c r="D37">
+        <v>5208.414273025357</v>
+      </c>
+      <c r="E37">
+        <v>-332.5135406609725</v>
+      </c>
+      <c r="F37">
+        <v>2220.40729112514</v>
+      </c>
+      <c r="G37">
+        <v>801</v>
+      </c>
+      <c r="H37">
+        <v>3791.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>468.7</v>
+      </c>
+      <c r="K37">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L37">
+        <v>407.1</v>
+      </c>
+      <c r="M37">
+        <v>202.9452264088378</v>
+      </c>
+      <c r="N37">
+        <v>204.1547735911623</v>
+      </c>
+      <c r="O37">
+        <v>50.91620053363588</v>
+      </c>
+      <c r="P37">
+        <v>153.2385730575264</v>
+      </c>
+      <c r="Q37">
+        <v>214.8385730575264</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.10887594269867</v>
+      </c>
+      <c r="T37">
+        <v>1.184868030628046</v>
+      </c>
+      <c r="U37">
+        <v>0.0914</v>
+      </c>
+      <c r="V37">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W37">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.005959968626647</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1006561981260402</v>
+      </c>
+      <c r="C38">
+        <v>3230.868245310081</v>
+      </c>
+      <c r="D38">
+        <v>4713.715744753081</v>
+      </c>
+      <c r="E38">
+        <v>-269.0733323431118</v>
+      </c>
+      <c r="F38">
+        <v>2283.847499443</v>
+      </c>
+      <c r="G38">
+        <v>801</v>
+      </c>
+      <c r="H38">
+        <v>3791.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>468.7</v>
+      </c>
+      <c r="K38">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L38">
+        <v>407.1</v>
+      </c>
+      <c r="M38">
+        <v>256.9328436873375</v>
+      </c>
+      <c r="N38">
+        <v>150.1671563126625</v>
+      </c>
+      <c r="O38">
+        <v>37.45168878437805</v>
+      </c>
+      <c r="P38">
+        <v>112.7154675282845</v>
+      </c>
+      <c r="Q38">
+        <v>174.3154675282844</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1097764033219379</v>
+      </c>
+      <c r="T38">
+        <v>1.200093327131546</v>
+      </c>
+      <c r="U38">
+        <v>0.1125</v>
+      </c>
+      <c r="V38">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W38">
+        <v>0.08444249999999999</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.584460725836209</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.100988158497945</v>
+      </c>
+      <c r="C39">
+        <v>3142.266223723006</v>
+      </c>
+      <c r="D39">
+        <v>4688.553931483867</v>
+      </c>
+      <c r="E39">
+        <v>-205.6331240252507</v>
+      </c>
+      <c r="F39">
+        <v>2347.287707760861</v>
+      </c>
+      <c r="G39">
+        <v>801</v>
+      </c>
+      <c r="H39">
+        <v>3791.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>468.7</v>
+      </c>
+      <c r="K39">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L39">
+        <v>407.1</v>
+      </c>
+      <c r="M39">
+        <v>264.0698671230969</v>
+      </c>
+      <c r="N39">
+        <v>143.0301328769032</v>
+      </c>
+      <c r="O39">
+        <v>35.67171513949966</v>
+      </c>
+      <c r="P39">
+        <v>107.3584177374035</v>
+      </c>
+      <c r="Q39">
+        <v>168.9584177374035</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1107054499967381</v>
+      </c>
+      <c r="T39">
+        <v>1.215801966381189</v>
+      </c>
+      <c r="U39">
+        <v>0.1125</v>
+      </c>
+      <c r="V39">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W39">
+        <v>0.08444249999999999</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>1.541637462975771</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1013201188698497</v>
+      </c>
+      <c r="C40">
+        <v>3053.93140331986</v>
+      </c>
+      <c r="D40">
+        <v>4663.659319398583</v>
+      </c>
+      <c r="E40">
+        <v>-142.1929157073891</v>
+      </c>
+      <c r="F40">
+        <v>2410.727916078723</v>
+      </c>
+      <c r="G40">
+        <v>801</v>
+      </c>
+      <c r="H40">
+        <v>3791.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>468.7</v>
+      </c>
+      <c r="K40">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L40">
+        <v>407.1</v>
+      </c>
+      <c r="M40">
+        <v>271.2068905588563</v>
+      </c>
+      <c r="N40">
+        <v>135.8931094411437</v>
+      </c>
+      <c r="O40">
+        <v>33.89174149462126</v>
+      </c>
+      <c r="P40">
+        <v>102.0013679465225</v>
+      </c>
+      <c r="Q40">
+        <v>163.6013679465224</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1116644659191125</v>
+      </c>
+      <c r="T40">
+        <v>1.232017335929207</v>
+      </c>
+      <c r="U40">
+        <v>0.1125</v>
+      </c>
+      <c r="V40">
+        <v>0.2494000000000001</v>
+      </c>
+      <c r="W40">
+        <v>0.08444249999999999</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>1.501068056055356</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1301809102716067</v>
+      </c>
+      <c r="C41">
+        <v>1517.569789579718</v>
+      </c>
+      <c r="D41">
+        <v>3190.737913976302</v>
+      </c>
+      <c r="E41">
+        <v>-78.75270738952804</v>
+      </c>
+      <c r="F41">
+        <v>2474.168124396584</v>
+      </c>
+      <c r="G41">
+        <v>801</v>
+      </c>
+      <c r="H41">
+        <v>3791.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>468.7</v>
+      </c>
+      <c r="K41">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L41">
+        <v>407.1</v>
+      </c>
+      <c r="M41">
+        <v>486.4214532563684</v>
+      </c>
+      <c r="N41">
+        <v>-79.32145325636839</v>
+      </c>
+      <c r="O41">
+        <v>-19.78277044213828</v>
+      </c>
+      <c r="P41">
+        <v>-59.53868281423011</v>
+      </c>
+      <c r="Q41">
+        <v>2.061317185769859</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.113952578237804</v>
+      </c>
+      <c r="T41">
+        <v>1.270705522380893</v>
+      </c>
+      <c r="U41">
+        <v>0.1966</v>
+      </c>
+      <c r="V41">
+        <v>0.208729979568743</v>
+      </c>
+      <c r="W41">
+        <v>0.1555636860167851</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.836928546787261</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1317589102716067</v>
+      </c>
+      <c r="C42">
+        <v>1399.966032942031</v>
+      </c>
+      <c r="D42">
+        <v>3136.574365656476</v>
+      </c>
+      <c r="E42">
+        <v>-15.31249907166693</v>
+      </c>
+      <c r="F42">
+        <v>2537.608332714445</v>
+      </c>
+      <c r="G42">
+        <v>801</v>
+      </c>
+      <c r="H42">
+        <v>3791.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>468.7</v>
+      </c>
+      <c r="K42">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L42">
+        <v>407.1</v>
+      </c>
+      <c r="M42">
+        <v>498.8937982116599</v>
+      </c>
+      <c r="N42">
+        <v>-91.79379821165986</v>
+      </c>
+      <c r="O42">
+        <v>-22.89337327398798</v>
+      </c>
+      <c r="P42">
+        <v>-68.90042493767189</v>
+      </c>
+      <c r="Q42">
+        <v>-7.30042493767192</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1152051212084341</v>
+      </c>
+      <c r="T42">
+        <v>1.291883947753907</v>
+      </c>
+      <c r="U42">
+        <v>0.1966</v>
+      </c>
+      <c r="V42">
+        <v>0.2035117300795244</v>
+      </c>
+      <c r="W42">
+        <v>0.1565895938663655</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8160053331175795</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1407157385906592</v>
+      </c>
+      <c r="C43">
+        <v>1060.869105734425</v>
+      </c>
+      <c r="D43">
+        <v>2860.917646766731</v>
+      </c>
+      <c r="E43">
+        <v>48.12770924619417</v>
+      </c>
+      <c r="F43">
+        <v>2601.048541032306</v>
+      </c>
+      <c r="G43">
+        <v>801</v>
+      </c>
+      <c r="H43">
+        <v>3791.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>468.7</v>
+      </c>
+      <c r="K43">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L43">
+        <v>407.1</v>
+      </c>
+      <c r="M43">
+        <v>556.1041780727071</v>
+      </c>
+      <c r="N43">
+        <v>-149.0041780727071</v>
+      </c>
+      <c r="O43">
+        <v>-37.16164201133316</v>
+      </c>
+      <c r="P43">
+        <v>-111.8425360613739</v>
+      </c>
+      <c r="Q43">
+        <v>-50.24253606137395</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1170540695662932</v>
+      </c>
+      <c r="T43">
+        <v>1.323146599601915</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1825750354041137</v>
+      </c>
+      <c r="W43">
+        <v>0.1747654574306005</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.7320570786051068</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1424657385906592</v>
+      </c>
+      <c r="C44">
+        <v>949.1332314626343</v>
+      </c>
+      <c r="D44">
+        <v>2812.621980812801</v>
+      </c>
+      <c r="E44">
+        <v>111.5679175640548</v>
+      </c>
+      <c r="F44">
+        <v>2664.488749350167</v>
+      </c>
+      <c r="G44">
+        <v>801</v>
+      </c>
+      <c r="H44">
+        <v>3791.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>468.7</v>
+      </c>
+      <c r="K44">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L44">
+        <v>407.1</v>
+      </c>
+      <c r="M44">
+        <v>569.6676946110657</v>
+      </c>
+      <c r="N44">
+        <v>-162.5676946110657</v>
+      </c>
+      <c r="O44">
+        <v>-40.54438303599979</v>
+      </c>
+      <c r="P44">
+        <v>-122.0233115750659</v>
+      </c>
+      <c r="Q44">
+        <v>-60.42331157506592</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1184032776622637</v>
+      </c>
+      <c r="T44">
+        <v>1.345959472008845</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1782280107516348</v>
+      </c>
+      <c r="W44">
+        <v>0.1756948513013005</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.7146271481621281</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1442157385906592</v>
+      </c>
+      <c r="C45">
+        <v>839.0008637743836</v>
+      </c>
+      <c r="D45">
+        <v>2765.929821442412</v>
+      </c>
+      <c r="E45">
+        <v>175.0081258819164</v>
+      </c>
+      <c r="F45">
+        <v>2727.928957668028</v>
+      </c>
+      <c r="G45">
+        <v>801</v>
+      </c>
+      <c r="H45">
+        <v>3791.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>468.7</v>
+      </c>
+      <c r="K45">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L45">
+        <v>407.1</v>
+      </c>
+      <c r="M45">
+        <v>583.2312111494244</v>
+      </c>
+      <c r="N45">
+        <v>-176.1312111494244</v>
+      </c>
+      <c r="O45">
+        <v>-43.92712406066646</v>
+      </c>
+      <c r="P45">
+        <v>-132.2040870887579</v>
+      </c>
+      <c r="Q45">
+        <v>-70.60408708875798</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1197998263931807</v>
+      </c>
+      <c r="T45">
+        <v>1.369572796079175</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.1740831732922944</v>
+      </c>
+      <c r="W45">
+        <v>0.1765810175501074</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.6980079121583577</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1459657385906592</v>
+      </c>
+      <c r="C46">
+        <v>730.393447623308</v>
+      </c>
+      <c r="D46">
+        <v>2720.762613609198</v>
+      </c>
+      <c r="E46">
+        <v>238.4483341997775</v>
+      </c>
+      <c r="F46">
+        <v>2791.36916598589</v>
+      </c>
+      <c r="G46">
+        <v>801</v>
+      </c>
+      <c r="H46">
+        <v>3791.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>468.7</v>
+      </c>
+      <c r="K46">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L46">
+        <v>407.1</v>
+      </c>
+      <c r="M46">
+        <v>596.7947276877832</v>
+      </c>
+      <c r="N46">
+        <v>-189.6947276877831</v>
+      </c>
+      <c r="O46">
+        <v>-47.30986508533313</v>
+      </c>
+      <c r="P46">
+        <v>-142.38486260245</v>
+      </c>
+      <c r="Q46">
+        <v>-80.78486260245006</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1212462518644875</v>
+      </c>
+      <c r="T46">
+        <v>1.394029453152018</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1701267375356514</v>
+      </c>
+      <c r="W46">
+        <v>0.1774269035148777</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.6821440959729405</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1477157385906592</v>
+      </c>
+      <c r="C47">
+        <v>623.2374766854027</v>
+      </c>
+      <c r="D47">
+        <v>2677.046850989153</v>
+      </c>
+      <c r="E47">
+        <v>301.8885425176386</v>
+      </c>
+      <c r="F47">
+        <v>2854.809374303751</v>
+      </c>
+      <c r="G47">
+        <v>801</v>
+      </c>
+      <c r="H47">
+        <v>3791.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>468.7</v>
+      </c>
+      <c r="K47">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L47">
+        <v>407.1</v>
+      </c>
+      <c r="M47">
+        <v>610.3582442261419</v>
+      </c>
+      <c r="N47">
+        <v>-203.2582442261419</v>
+      </c>
+      <c r="O47">
+        <v>-50.69260610999979</v>
+      </c>
+      <c r="P47">
+        <v>-152.5656381161421</v>
+      </c>
+      <c r="Q47">
+        <v>-90.96563811614212</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1227452746256599</v>
+      </c>
+      <c r="T47">
+        <v>1.419375443209327</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1663461433681925</v>
+      </c>
+      <c r="W47">
+        <v>0.1782351945478804</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6669853382846529</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1494657385906592</v>
+      </c>
+      <c r="C48">
+        <v>517.4640941720504</v>
+      </c>
+      <c r="D48">
+        <v>2634.713676793662</v>
+      </c>
+      <c r="E48">
+        <v>365.3287508354997</v>
+      </c>
+      <c r="F48">
+        <v>2918.249582621612</v>
+      </c>
+      <c r="G48">
+        <v>801</v>
+      </c>
+      <c r="H48">
+        <v>3791.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>468.7</v>
+      </c>
+      <c r="K48">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L48">
+        <v>407.1</v>
+      </c>
+      <c r="M48">
+        <v>623.9217607645006</v>
+      </c>
+      <c r="N48">
+        <v>-216.8217607645006</v>
+      </c>
+      <c r="O48">
+        <v>-54.07534713466647</v>
+      </c>
+      <c r="P48">
+        <v>-162.7464136298341</v>
+      </c>
+      <c r="Q48">
+        <v>-101.1464136298342</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1242998167483574</v>
+      </c>
+      <c r="T48">
+        <v>1.445660173639129</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1627299228601883</v>
+      </c>
+      <c r="W48">
+        <v>0.1790083424924917</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.6524856570175952</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1512157385906592</v>
+      </c>
+      <c r="C49">
+        <v>413.0087309284354</v>
+      </c>
+      <c r="D49">
+        <v>2593.698521867908</v>
+      </c>
+      <c r="E49">
+        <v>428.7689591533608</v>
+      </c>
+      <c r="F49">
+        <v>2981.689790939473</v>
+      </c>
+      <c r="G49">
+        <v>801</v>
+      </c>
+      <c r="H49">
+        <v>3791.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>468.7</v>
+      </c>
+      <c r="K49">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L49">
+        <v>407.1</v>
+      </c>
+      <c r="M49">
+        <v>637.4852773028592</v>
+      </c>
+      <c r="N49">
+        <v>-230.3852773028592</v>
+      </c>
+      <c r="O49">
+        <v>-57.4580881593331</v>
+      </c>
+      <c r="P49">
+        <v>-172.9271891435261</v>
+      </c>
+      <c r="Q49">
+        <v>-111.3271891435261</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.125913020837949</v>
+      </c>
+      <c r="T49">
+        <v>1.472936780688924</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.159267584075929</v>
+      </c>
+      <c r="W49">
+        <v>0.1797485905245664</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6386029834640294</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1529657385906592</v>
+      </c>
+      <c r="C50">
+        <v>309.8107768166001</v>
+      </c>
+      <c r="D50">
+        <v>2553.940776073934</v>
+      </c>
+      <c r="E50">
+        <v>492.2091674712219</v>
+      </c>
+      <c r="F50">
+        <v>3045.129999257334</v>
+      </c>
+      <c r="G50">
+        <v>801</v>
+      </c>
+      <c r="H50">
+        <v>3791.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>468.7</v>
+      </c>
+      <c r="K50">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L50">
+        <v>407.1</v>
+      </c>
+      <c r="M50">
+        <v>651.048793841218</v>
+      </c>
+      <c r="N50">
+        <v>-243.9487938412179</v>
+      </c>
+      <c r="O50">
+        <v>-60.84082918399977</v>
+      </c>
+      <c r="P50">
+        <v>-183.1079646572182</v>
+      </c>
+      <c r="Q50">
+        <v>-121.5079646572182</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1275882712386788</v>
+      </c>
+      <c r="T50">
+        <v>1.501262488009865</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1559495094076805</v>
+      </c>
+      <c r="W50">
+        <v>0.1804579948886379</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6252987546418621</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1547157385906592</v>
+      </c>
+      <c r="C51">
+        <v>207.8132818656222</v>
+      </c>
+      <c r="D51">
+        <v>2515.383489440817</v>
+      </c>
+      <c r="E51">
+        <v>555.649375789083</v>
+      </c>
+      <c r="F51">
+        <v>3108.570207575195</v>
+      </c>
+      <c r="G51">
+        <v>801</v>
+      </c>
+      <c r="H51">
+        <v>3791.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>468.7</v>
+      </c>
+      <c r="K51">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L51">
+        <v>407.1</v>
+      </c>
+      <c r="M51">
+        <v>664.6123103795767</v>
+      </c>
+      <c r="N51">
+        <v>-257.5123103795767</v>
+      </c>
+      <c r="O51">
+        <v>-64.22357020866643</v>
+      </c>
+      <c r="P51">
+        <v>-193.2887401709102</v>
+      </c>
+      <c r="Q51">
+        <v>-131.6887401709103</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1293292177335549</v>
+      </c>
+      <c r="T51">
+        <v>1.530699007382608</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1527668663585441</v>
+      </c>
+      <c r="W51">
+        <v>0.1811384439725433</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.6125375555675383</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1564657385906592</v>
+      </c>
+      <c r="C52">
+        <v>106.9626840899177</v>
+      </c>
+      <c r="D52">
+        <v>2477.973099982974</v>
+      </c>
+      <c r="E52">
+        <v>619.0895841069441</v>
+      </c>
+      <c r="F52">
+        <v>3172.010415893056</v>
+      </c>
+      <c r="G52">
+        <v>801</v>
+      </c>
+      <c r="H52">
+        <v>3791.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>468.7</v>
+      </c>
+      <c r="K52">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L52">
+        <v>407.1</v>
+      </c>
+      <c r="M52">
+        <v>678.1758269179354</v>
+      </c>
+      <c r="N52">
+        <v>-271.0758269179354</v>
+      </c>
+      <c r="O52">
+        <v>-67.6063112333331</v>
+      </c>
+      <c r="P52">
+        <v>-203.4695156846023</v>
+      </c>
+      <c r="Q52">
+        <v>-141.8695156846023</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.131139802088226</v>
+      </c>
+      <c r="T52">
+        <v>1.56131298753026</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1497115290313732</v>
+      </c>
+      <c r="W52">
+        <v>0.1817916750930924</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6002868044561875</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1582157385906592</v>
+      </c>
+      <c r="C53">
+        <v>7.208561239944174</v>
+      </c>
+      <c r="D53">
+        <v>2441.659185450862</v>
+      </c>
+      <c r="E53">
+        <v>682.5297924248052</v>
+      </c>
+      <c r="F53">
+        <v>3235.450624210917</v>
+      </c>
+      <c r="G53">
+        <v>801</v>
+      </c>
+      <c r="H53">
+        <v>3791.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>468.7</v>
+      </c>
+      <c r="K53">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L53">
+        <v>407.1</v>
+      </c>
+      <c r="M53">
+        <v>691.7393434562941</v>
+      </c>
+      <c r="N53">
+        <v>-284.6393434562941</v>
+      </c>
+      <c r="O53">
+        <v>-70.98905225799977</v>
+      </c>
+      <c r="P53">
+        <v>-213.6502911982943</v>
+      </c>
+      <c r="Q53">
+        <v>-152.0502911982944</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1330242878451285</v>
+      </c>
+      <c r="T53">
+        <v>1.59317651788802</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1467760088542875</v>
+      </c>
+      <c r="W53">
+        <v>0.1824192893069533</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5885164749570466</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1599657385906592</v>
+      </c>
+      <c r="C54">
+        <v>-91.49659593424667</v>
+      </c>
+      <c r="D54">
+        <v>2406.394236594532</v>
+      </c>
+      <c r="E54">
+        <v>745.9700007426663</v>
+      </c>
+      <c r="F54">
+        <v>3298.890832528778</v>
+      </c>
+      <c r="G54">
+        <v>801</v>
+      </c>
+      <c r="H54">
+        <v>3791.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>468.7</v>
+      </c>
+      <c r="K54">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L54">
+        <v>407.1</v>
+      </c>
+      <c r="M54">
+        <v>705.3028599946527</v>
+      </c>
+      <c r="N54">
+        <v>-298.2028599946527</v>
+      </c>
+      <c r="O54">
+        <v>-74.37179328266642</v>
+      </c>
+      <c r="P54">
+        <v>-223.8310667119863</v>
+      </c>
+      <c r="Q54">
+        <v>-162.2310667119863</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1349872938419021</v>
+      </c>
+      <c r="T54">
+        <v>1.626367695344021</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1439533932993973</v>
+      </c>
+      <c r="W54">
+        <v>0.1830227645125889</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5771988504386421</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1617157385906592</v>
+      </c>
+      <c r="C55">
+        <v>-189.1975910506544</v>
+      </c>
+      <c r="D55">
+        <v>2372.133449795985</v>
+      </c>
+      <c r="E55">
+        <v>809.4102090605274</v>
+      </c>
+      <c r="F55">
+        <v>3362.33104084664</v>
+      </c>
+      <c r="G55">
+        <v>801</v>
+      </c>
+      <c r="H55">
+        <v>3791.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>468.7</v>
+      </c>
+      <c r="K55">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L55">
+        <v>407.1</v>
+      </c>
+      <c r="M55">
+        <v>718.8663765330115</v>
+      </c>
+      <c r="N55">
+        <v>-311.7663765330115</v>
+      </c>
+      <c r="O55">
+        <v>-77.75453430733307</v>
+      </c>
+      <c r="P55">
+        <v>-234.0118422256784</v>
+      </c>
+      <c r="Q55">
+        <v>-172.4118422256784</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.137033832008751</v>
+      </c>
+      <c r="T55">
+        <v>1.660971263330064</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1412372915390314</v>
+      </c>
+      <c r="W55">
+        <v>0.1836034670689551</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.566308306090743</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1634657385906592</v>
+      </c>
+      <c r="C56">
+        <v>-285.9367119973786</v>
+      </c>
+      <c r="D56">
+        <v>2338.834537167123</v>
+      </c>
+      <c r="E56">
+        <v>872.850417378389</v>
+      </c>
+      <c r="F56">
+        <v>3425.771249164501</v>
+      </c>
+      <c r="G56">
+        <v>801</v>
+      </c>
+      <c r="H56">
+        <v>3791.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>468.7</v>
+      </c>
+      <c r="K56">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L56">
+        <v>407.1</v>
+      </c>
+      <c r="M56">
+        <v>732.4298930713703</v>
+      </c>
+      <c r="N56">
+        <v>-325.3298930713703</v>
+      </c>
+      <c r="O56">
+        <v>-81.13727533199977</v>
+      </c>
+      <c r="P56">
+        <v>-244.1926177393705</v>
+      </c>
+      <c r="Q56">
+        <v>-182.5926177393706</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1391693500958978</v>
+      </c>
+      <c r="T56">
+        <v>1.697079334272022</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.1386217861401604</v>
+      </c>
+      <c r="W56">
+        <v>0.1841626621232337</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5558211152372107</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1652157385906592</v>
+      </c>
+      <c r="C57">
+        <v>-381.7539050615428</v>
+      </c>
+      <c r="D57">
+        <v>2306.457552420819</v>
+      </c>
+      <c r="E57">
+        <v>936.2906256962501</v>
+      </c>
+      <c r="F57">
+        <v>3489.211457482362</v>
+      </c>
+      <c r="G57">
+        <v>801</v>
+      </c>
+      <c r="H57">
+        <v>3791.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>468.7</v>
+      </c>
+      <c r="K57">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L57">
+        <v>407.1</v>
+      </c>
+      <c r="M57">
+        <v>745.993409609729</v>
+      </c>
+      <c r="N57">
+        <v>-338.893409609729</v>
+      </c>
+      <c r="O57">
+        <v>-84.52001635666645</v>
+      </c>
+      <c r="P57">
+        <v>-254.3733932530626</v>
+      </c>
+      <c r="Q57">
+        <v>-192.7733932530626</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1413997800980288</v>
+      </c>
+      <c r="T57">
+        <v>1.734792208366956</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1361013900285211</v>
+      </c>
+      <c r="W57">
+        <v>0.1847015228119022</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5457152767783523</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1669657385906592</v>
+      </c>
+      <c r="C58">
+        <v>-476.6869347926813</v>
+      </c>
+      <c r="D58">
+        <v>2274.964731007542</v>
+      </c>
+      <c r="E58">
+        <v>999.7308340141112</v>
+      </c>
+      <c r="F58">
+        <v>3552.651665800223</v>
+      </c>
+      <c r="G58">
+        <v>801</v>
+      </c>
+      <c r="H58">
+        <v>3791.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>468.7</v>
+      </c>
+      <c r="K58">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L58">
+        <v>407.1</v>
+      </c>
+      <c r="M58">
+        <v>759.5569261480878</v>
+      </c>
+      <c r="N58">
+        <v>-352.4569261480877</v>
+      </c>
+      <c r="O58">
+        <v>-87.9027573813331</v>
+      </c>
+      <c r="P58">
+        <v>-264.5541687667546</v>
+      </c>
+      <c r="Q58">
+        <v>-202.9541687667547</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.143731593282075</v>
+      </c>
+      <c r="T58">
+        <v>1.774219304011659</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1336710080637261</v>
+      </c>
+      <c r="W58">
+        <v>0.1852211384759753</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.535970361121596</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1687157385906592</v>
+      </c>
+      <c r="C59">
+        <v>-570.7715309457008</v>
+      </c>
+      <c r="D59">
+        <v>2244.320343172384</v>
+      </c>
+      <c r="E59">
+        <v>1063.171042331972</v>
+      </c>
+      <c r="F59">
+        <v>3616.091874118084</v>
+      </c>
+      <c r="G59">
+        <v>801</v>
+      </c>
+      <c r="H59">
+        <v>3791.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>468.7</v>
+      </c>
+      <c r="K59">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L59">
+        <v>407.1</v>
+      </c>
+      <c r="M59">
+        <v>773.1204426864464</v>
+      </c>
+      <c r="N59">
+        <v>-366.0204426864464</v>
+      </c>
+      <c r="O59">
+        <v>-91.28549840599975</v>
+      </c>
+      <c r="P59">
+        <v>-274.7349442804466</v>
+      </c>
+      <c r="Q59">
+        <v>-213.1349442804466</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.146171862893286</v>
+      </c>
+      <c r="T59">
+        <v>1.815480218058442</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1313259026590993</v>
+      </c>
+      <c r="W59">
+        <v>0.1857225220114846</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5265673723299891</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1704657385906592</v>
+      </c>
+      <c r="C60">
+        <v>-664.0415237055277</v>
+      </c>
+      <c r="D60">
+        <v>2214.490558730417</v>
+      </c>
+      <c r="E60">
+        <v>1126.611250649833</v>
+      </c>
+      <c r="F60">
+        <v>3679.532082435945</v>
+      </c>
+      <c r="G60">
+        <v>801</v>
+      </c>
+      <c r="H60">
+        <v>3791.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>468.7</v>
+      </c>
+      <c r="K60">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L60">
+        <v>407.1</v>
+      </c>
+      <c r="M60">
+        <v>786.683959224805</v>
+      </c>
+      <c r="N60">
+        <v>-379.583959224805</v>
+      </c>
+      <c r="O60">
+        <v>-94.66823943066639</v>
+      </c>
+      <c r="P60">
+        <v>-284.9157197941386</v>
+      </c>
+      <c r="Q60">
+        <v>-223.3157197941386</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1487283358193166</v>
+      </c>
+      <c r="T60">
+        <v>1.858705937536024</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.1290616629580804</v>
+      </c>
+      <c r="W60">
+        <v>0.1862066164595624</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5174886245311963</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1722157385906592</v>
+      </c>
+      <c r="C61">
+        <v>-756.5289682693942</v>
+      </c>
+      <c r="D61">
+        <v>2185.443322484412</v>
+      </c>
+      <c r="E61">
+        <v>1190.051458967694</v>
+      </c>
+      <c r="F61">
+        <v>3742.972290753806</v>
+      </c>
+      <c r="G61">
+        <v>801</v>
+      </c>
+      <c r="H61">
+        <v>3791.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>468.7</v>
+      </c>
+      <c r="K61">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L61">
+        <v>407.1</v>
+      </c>
+      <c r="M61">
+        <v>800.2474757631637</v>
+      </c>
+      <c r="N61">
+        <v>-393.1474757631637</v>
+      </c>
+      <c r="O61">
+        <v>-98.05098045533305</v>
+      </c>
+      <c r="P61">
+        <v>-295.0964953078307</v>
+      </c>
+      <c r="Q61">
+        <v>-233.4964953078307</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.151409514741739</v>
+      </c>
+      <c r="T61">
+        <v>1.904040228695439</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1268741771452316</v>
+      </c>
+      <c r="W61">
+        <v>0.1866743009263495</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5087176308950743</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1739657385906592</v>
+      </c>
+      <c r="C62">
+        <v>-848.2642597512668</v>
+      </c>
+      <c r="D62">
+        <v>2157.148239320401</v>
+      </c>
+      <c r="E62">
+        <v>1253.491667285555</v>
+      </c>
+      <c r="F62">
+        <v>3806.412499071667</v>
+      </c>
+      <c r="G62">
+        <v>801</v>
+      </c>
+      <c r="H62">
+        <v>3791.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>468.7</v>
+      </c>
+      <c r="K62">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L62">
+        <v>407.1</v>
+      </c>
+      <c r="M62">
+        <v>813.8109923015224</v>
+      </c>
+      <c r="N62">
+        <v>-406.7109923015224</v>
+      </c>
+      <c r="O62">
+        <v>-101.4337214799997</v>
+      </c>
+      <c r="P62">
+        <v>-305.2772708215227</v>
+      </c>
+      <c r="Q62">
+        <v>-243.6772708215228</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1542247526102824</v>
+      </c>
+      <c r="T62">
+        <v>1.951641234412825</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.1247596075261444</v>
+      </c>
+      <c r="W62">
+        <v>0.1871263959109103</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5002390037134896</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1913568319421412</v>
+      </c>
+      <c r="C63">
+        <v>-1157.613916537711</v>
+      </c>
+      <c r="D63">
+        <v>1911.238790851818</v>
+      </c>
+      <c r="E63">
+        <v>1316.931875603416</v>
+      </c>
+      <c r="F63">
+        <v>3869.852707389528</v>
+      </c>
+      <c r="G63">
+        <v>801</v>
+      </c>
+      <c r="H63">
+        <v>3791.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>468.7</v>
+      </c>
+      <c r="K63">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L63">
+        <v>407.1</v>
+      </c>
+      <c r="M63">
+        <v>924.1208265246195</v>
+      </c>
+      <c r="N63">
+        <v>-517.0208265246195</v>
+      </c>
+      <c r="O63">
+        <v>-128.9449941352401</v>
+      </c>
+      <c r="P63">
+        <v>-388.0758323893793</v>
+      </c>
+      <c r="Q63">
+        <v>-326.4758323893794</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1581871651169102</v>
+      </c>
+      <c r="T63">
+        <v>2.01863906166222</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.1098673864778386</v>
+      </c>
+      <c r="W63">
+        <v>0.2125636681090921</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4405268102559687</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1933568319421412</v>
+      </c>
+      <c r="C64">
+        <v>-1245.785982604407</v>
+      </c>
+      <c r="D64">
+        <v>1886.506933102983</v>
+      </c>
+      <c r="E64">
+        <v>1380.372083921277</v>
+      </c>
+      <c r="F64">
+        <v>3933.29291570739</v>
+      </c>
+      <c r="G64">
+        <v>801</v>
+      </c>
+      <c r="H64">
+        <v>3791.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>468.7</v>
+      </c>
+      <c r="K64">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L64">
+        <v>407.1</v>
+      </c>
+      <c r="M64">
+        <v>939.2703482709246</v>
+      </c>
+      <c r="N64">
+        <v>-532.1703482709246</v>
+      </c>
+      <c r="O64">
+        <v>-132.7232848587686</v>
+      </c>
+      <c r="P64">
+        <v>-399.447063412156</v>
+      </c>
+      <c r="Q64">
+        <v>-337.847063412156</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1613289326199868</v>
+      </c>
+      <c r="T64">
+        <v>2.071761142232279</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.1080953318572283</v>
+      </c>
+      <c r="W64">
+        <v>0.2129868347524939</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.433421539122808</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1953568319421412</v>
+      </c>
+      <c r="C65">
+        <v>-1333.326153979775</v>
+      </c>
+      <c r="D65">
+        <v>1862.406970045475</v>
+      </c>
+      <c r="E65">
+        <v>1443.812292239139</v>
+      </c>
+      <c r="F65">
+        <v>3996.733124025251</v>
+      </c>
+      <c r="G65">
+        <v>801</v>
+      </c>
+      <c r="H65">
+        <v>3791.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>468.7</v>
+      </c>
+      <c r="K65">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L65">
+        <v>407.1</v>
+      </c>
+      <c r="M65">
+        <v>954.41987001723</v>
+      </c>
+      <c r="N65">
+        <v>-547.31987001723</v>
+      </c>
+      <c r="O65">
+        <v>-136.5015755822972</v>
+      </c>
+      <c r="P65">
+        <v>-410.8182944349328</v>
+      </c>
+      <c r="Q65">
+        <v>-349.2182944349328</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1646405253935</v>
+      </c>
+      <c r="T65">
+        <v>2.127754686616935</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.1063795329388596</v>
+      </c>
+      <c r="W65">
+        <v>0.2133965675342003</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4265418321526047</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1973568319421412</v>
+      </c>
+      <c r="C66">
+        <v>-1420.258342393771</v>
+      </c>
+      <c r="D66">
+        <v>1838.914989949341</v>
+      </c>
+      <c r="E66">
+        <v>1507.252500557</v>
+      </c>
+      <c r="F66">
+        <v>4060.173332343112</v>
+      </c>
+      <c r="G66">
+        <v>801</v>
+      </c>
+      <c r="H66">
+        <v>3791.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>468.7</v>
+      </c>
+      <c r="K66">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L66">
+        <v>407.1</v>
+      </c>
+      <c r="M66">
+        <v>969.5693917635352</v>
+      </c>
+      <c r="N66">
+        <v>-562.4693917635352</v>
+      </c>
+      <c r="O66">
+        <v>-140.2798663058257</v>
+      </c>
+      <c r="P66">
+        <v>-422.1895254577095</v>
+      </c>
+      <c r="Q66">
+        <v>-360.5895254577095</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1681360955433194</v>
+      </c>
+      <c r="T66">
+        <v>2.186858983467405</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.1047173527366899</v>
+      </c>
+      <c r="W66">
+        <v>0.2137934961664785</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4198771160252202</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1993568319421412</v>
+      </c>
+      <c r="C67">
+        <v>-1506.605268136301</v>
+      </c>
+      <c r="D67">
+        <v>1816.008272524672</v>
+      </c>
+      <c r="E67">
+        <v>1570.692708874861</v>
+      </c>
+      <c r="F67">
+        <v>4123.613540660973</v>
+      </c>
+      <c r="G67">
+        <v>801</v>
+      </c>
+      <c r="H67">
+        <v>3791.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>468.7</v>
+      </c>
+      <c r="K67">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L67">
+        <v>407.1</v>
+      </c>
+      <c r="M67">
+        <v>984.7189135098404</v>
+      </c>
+      <c r="N67">
+        <v>-577.6189135098404</v>
+      </c>
+      <c r="O67">
+        <v>-144.0581570293542</v>
+      </c>
+      <c r="P67">
+        <v>-433.5607564804861</v>
+      </c>
+      <c r="Q67">
+        <v>-371.9607564804862</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1718314125588429</v>
+      </c>
+      <c r="T67">
+        <v>2.249340668709332</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.1031063165407409</v>
+      </c>
+      <c r="W67">
+        <v>0.2141782116100711</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.4134174680863707</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2013568319421412</v>
+      </c>
+      <c r="C68">
+        <v>-1592.388533350979</v>
+      </c>
+      <c r="D68">
+        <v>1793.665215627856</v>
+      </c>
+      <c r="E68">
+        <v>1634.132917192723</v>
+      </c>
+      <c r="F68">
+        <v>4187.053748978835</v>
+      </c>
+      <c r="G68">
+        <v>801</v>
+      </c>
+      <c r="H68">
+        <v>3791.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>468.7</v>
+      </c>
+      <c r="K68">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L68">
+        <v>407.1</v>
+      </c>
+      <c r="M68">
+        <v>999.8684352561459</v>
+      </c>
+      <c r="N68">
+        <v>-592.7684352561458</v>
+      </c>
+      <c r="O68">
+        <v>-147.8364477528828</v>
+      </c>
+      <c r="P68">
+        <v>-444.931987503263</v>
+      </c>
+      <c r="Q68">
+        <v>-383.3319875032631</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1757441011635147</v>
+      </c>
+      <c r="T68">
+        <v>2.315497747200782</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.1015440996234569</v>
+      </c>
+      <c r="W68">
+        <v>0.2145512690099185</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.4071535670547589</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2033568319421412</v>
+      </c>
+      <c r="C69">
+        <v>-1677.628689984064</v>
+      </c>
+      <c r="D69">
+        <v>1771.865267312632</v>
+      </c>
+      <c r="E69">
+        <v>1697.573125510584</v>
+      </c>
+      <c r="F69">
+        <v>4250.493957296696</v>
+      </c>
+      <c r="G69">
+        <v>801</v>
+      </c>
+      <c r="H69">
+        <v>3791.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>468.7</v>
+      </c>
+      <c r="K69">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L69">
+        <v>407.1</v>
+      </c>
+      <c r="M69">
+        <v>1015.017957002451</v>
+      </c>
+      <c r="N69">
+        <v>-607.917957002451</v>
+      </c>
+      <c r="O69">
+        <v>-151.6147384764113</v>
+      </c>
+      <c r="P69">
+        <v>-456.3032185260397</v>
+      </c>
+      <c r="Q69">
+        <v>-394.7032185260397</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1798939224108939</v>
+      </c>
+      <c r="T69">
+        <v>2.385664345600806</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.1000285160469874</v>
+      </c>
+      <c r="W69">
+        <v>0.2149131903679794</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4010766481434939</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2053568319421412</v>
+      </c>
+      <c r="C70">
+        <v>-1762.345302837863</v>
+      </c>
+      <c r="D70">
+        <v>1750.588862776694</v>
+      </c>
+      <c r="E70">
+        <v>1761.013333828445</v>
+      </c>
+      <c r="F70">
+        <v>4313.934165614557</v>
+      </c>
+      <c r="G70">
+        <v>801</v>
+      </c>
+      <c r="H70">
+        <v>3791.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>468.7</v>
+      </c>
+      <c r="K70">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L70">
+        <v>407.1</v>
+      </c>
+      <c r="M70">
+        <v>1030.167478748756</v>
+      </c>
+      <c r="N70">
+        <v>-623.0674787487563</v>
+      </c>
+      <c r="O70">
+        <v>-155.3930291999399</v>
+      </c>
+      <c r="P70">
+        <v>-467.6744495488165</v>
+      </c>
+      <c r="Q70">
+        <v>-406.0744495488165</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1843031074862344</v>
+      </c>
+      <c r="T70">
+        <v>2.460216356400831</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.0985575084580611</v>
+      </c>
+      <c r="W70">
+        <v>0.215264466980215</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3951784621413836</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2073568319421412</v>
+      </c>
+      <c r="C71">
+        <v>-1846.557008135183</v>
+      </c>
+      <c r="D71">
+        <v>1729.817365797235</v>
+      </c>
+      <c r="E71">
+        <v>1824.453542146306</v>
+      </c>
+      <c r="F71">
+        <v>4377.374373932418</v>
+      </c>
+      <c r="G71">
+        <v>801</v>
+      </c>
+      <c r="H71">
+        <v>3791.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>468.7</v>
+      </c>
+      <c r="K71">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L71">
+        <v>407.1</v>
+      </c>
+      <c r="M71">
+        <v>1045.317000495062</v>
+      </c>
+      <c r="N71">
+        <v>-638.2170004950616</v>
+      </c>
+      <c r="O71">
+        <v>-159.1713199234684</v>
+      </c>
+      <c r="P71">
+        <v>-479.0456805715932</v>
+      </c>
+      <c r="Q71">
+        <v>-417.4456805715932</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1889967561148226</v>
+      </c>
+      <c r="T71">
+        <v>2.539578174349245</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.09712913877026311</v>
+      </c>
+      <c r="W71">
+        <v>0.2156055616616612</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.389451238052378</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2093568319421412</v>
+      </c>
+      <c r="C72">
+        <v>-1930.281567963326</v>
+      </c>
+      <c r="D72">
+        <v>1709.533014286953</v>
+      </c>
+      <c r="E72">
+        <v>1887.893750464167</v>
+      </c>
+      <c r="F72">
+        <v>4440.814582250279</v>
+      </c>
+      <c r="G72">
+        <v>801</v>
+      </c>
+      <c r="H72">
+        <v>3791.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>468.7</v>
+      </c>
+      <c r="K72">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L72">
+        <v>407.1</v>
+      </c>
+      <c r="M72">
+        <v>1060.466522241367</v>
+      </c>
+      <c r="N72">
+        <v>-653.3665222413666</v>
+      </c>
+      <c r="O72">
+        <v>-162.9496106469969</v>
+      </c>
+      <c r="P72">
+        <v>-490.4169115943697</v>
+      </c>
+      <c r="Q72">
+        <v>-428.8169115943697</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1940033146519833</v>
+      </c>
+      <c r="T72">
+        <v>2.624230780160887</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.09574157964497367</v>
+      </c>
+      <c r="W72">
+        <v>0.2159369107807803</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3838876489373442</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2113568319421412</v>
+      </c>
+      <c r="C73">
+        <v>-2013.53592093192</v>
+      </c>
+      <c r="D73">
+        <v>1689.718869636219</v>
+      </c>
+      <c r="E73">
+        <v>1951.333958782027</v>
+      </c>
+      <c r="F73">
+        <v>4504.254790568139</v>
+      </c>
+      <c r="G73">
+        <v>801</v>
+      </c>
+      <c r="H73">
+        <v>3791.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>468.7</v>
+      </c>
+      <c r="K73">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L73">
+        <v>407.1</v>
+      </c>
+      <c r="M73">
+        <v>1075.616043987672</v>
+      </c>
+      <c r="N73">
+        <v>-668.5160439876717</v>
+      </c>
+      <c r="O73">
+        <v>-166.7279013705254</v>
+      </c>
+      <c r="P73">
+        <v>-501.7881426171463</v>
+      </c>
+      <c r="Q73">
+        <v>-440.1881426171463</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1993551530882586</v>
+      </c>
+      <c r="T73">
+        <v>2.714721496718158</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.09439310669222757</v>
+      </c>
+      <c r="W73">
+        <v>0.2162589261218961</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3784807806424521</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2133568319421412</v>
+      </c>
+      <c r="C74">
+        <v>-2096.336229348256</v>
+      </c>
+      <c r="D74">
+        <v>1670.358769537745</v>
+      </c>
+      <c r="E74">
+        <v>2014.774167099888</v>
+      </c>
+      <c r="F74">
+        <v>4567.694998886001</v>
+      </c>
+      <c r="G74">
+        <v>801</v>
+      </c>
+      <c r="H74">
+        <v>3791.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>468.7</v>
+      </c>
+      <c r="K74">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L74">
+        <v>407.1</v>
+      </c>
+      <c r="M74">
+        <v>1090.765565733977</v>
+      </c>
+      <c r="N74">
+        <v>-683.6655657339769</v>
+      </c>
+      <c r="O74">
+        <v>-170.5061920940539</v>
+      </c>
+      <c r="P74">
+        <v>-513.159373639923</v>
+      </c>
+      <c r="Q74">
+        <v>-451.5593736399231</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2050892656985535</v>
+      </c>
+      <c r="T74">
+        <v>2.811675835886664</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.09308209132150218</v>
+      </c>
+      <c r="W74">
+        <v>0.2165719965924253</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3732241031335291</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2153568319421412</v>
+      </c>
+      <c r="C75">
+        <v>-2178.697923186259</v>
+      </c>
+      <c r="D75">
+        <v>1651.437284017602</v>
+      </c>
+      <c r="E75">
+        <v>2078.21437541775</v>
+      </c>
+      <c r="F75">
+        <v>4631.135207203862</v>
+      </c>
+      <c r="G75">
+        <v>801</v>
+      </c>
+      <c r="H75">
+        <v>3791.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>468.7</v>
+      </c>
+      <c r="K75">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L75">
+        <v>407.1</v>
+      </c>
+      <c r="M75">
+        <v>1105.915087480282</v>
+      </c>
+      <c r="N75">
+        <v>-698.8150874802822</v>
+      </c>
+      <c r="O75">
+        <v>-174.2844828175824</v>
+      </c>
+      <c r="P75">
+        <v>-524.5306046626997</v>
+      </c>
+      <c r="Q75">
+        <v>-462.9306046626997</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2112481273910926</v>
+      </c>
+      <c r="T75">
+        <v>2.91581197795654</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.09180699418011173</v>
+      </c>
+      <c r="W75">
+        <v>0.2168764897897893</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3681114441864944</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2173568319421412</v>
+      </c>
+      <c r="C76">
+        <v>-2260.635741100518</v>
+      </c>
+      <c r="D76">
+        <v>1632.939674421205</v>
+      </c>
+      <c r="E76">
+        <v>2141.654583735611</v>
+      </c>
+      <c r="F76">
+        <v>4694.575415521723</v>
+      </c>
+      <c r="G76">
+        <v>801</v>
+      </c>
+      <c r="H76">
+        <v>3791.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>468.7</v>
+      </c>
+      <c r="K76">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L76">
+        <v>407.1</v>
+      </c>
+      <c r="M76">
+        <v>1121.064609226587</v>
+      </c>
+      <c r="N76">
+        <v>-713.9646092265874</v>
+      </c>
+      <c r="O76">
+        <v>-178.0627735411109</v>
+      </c>
+      <c r="P76">
+        <v>-535.9018356854765</v>
+      </c>
+      <c r="Q76">
+        <v>-474.3018356854765</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2178807476753653</v>
+      </c>
+      <c r="T76">
+        <v>3.02795859249333</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.09056635912362374</v>
+      </c>
+      <c r="W76">
+        <v>0.2171727534412786</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3631369652110013</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2193568319421412</v>
+      </c>
+      <c r="C77">
+        <v>-2342.163768714462</v>
+      </c>
+      <c r="D77">
+        <v>1614.851855125123</v>
+      </c>
+      <c r="E77">
+        <v>2205.094792053473</v>
+      </c>
+      <c r="F77">
+        <v>4758.015623839585</v>
+      </c>
+      <c r="G77">
+        <v>801</v>
+      </c>
+      <c r="H77">
+        <v>3791.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>468.7</v>
+      </c>
+      <c r="K77">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L77">
+        <v>407.1</v>
+      </c>
+      <c r="M77">
+        <v>1136.214130972893</v>
+      </c>
+      <c r="N77">
+        <v>-729.1141309728929</v>
+      </c>
+      <c r="O77">
+        <v>-181.8410642646395</v>
+      </c>
+      <c r="P77">
+        <v>-547.2730667082534</v>
+      </c>
+      <c r="Q77">
+        <v>-485.6730667082534</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.22504397758238</v>
+      </c>
+      <c r="T77">
+        <v>3.149076936193064</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.08935880766864207</v>
+      </c>
+      <c r="W77">
+        <v>0.2174611167287283</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3582951390081879</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2213568319421412</v>
+      </c>
+      <c r="C78">
+        <v>-2423.295474391752</v>
+      </c>
+      <c r="D78">
+        <v>1597.160357765694</v>
+      </c>
+      <c r="E78">
+        <v>2268.535000371334</v>
+      </c>
+      <c r="F78">
+        <v>4821.455832157446</v>
+      </c>
+      <c r="G78">
+        <v>801</v>
+      </c>
+      <c r="H78">
+        <v>3791.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>468.7</v>
+      </c>
+      <c r="K78">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L78">
+        <v>407.1</v>
+      </c>
+      <c r="M78">
+        <v>1151.363652719198</v>
+      </c>
+      <c r="N78">
+        <v>-744.2636527191981</v>
+      </c>
+      <c r="O78">
+        <v>-185.6193549881681</v>
+      </c>
+      <c r="P78">
+        <v>-558.6442977310301</v>
+      </c>
+      <c r="Q78">
+        <v>-497.0442977310301</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2328041433149791</v>
+      </c>
+      <c r="T78">
+        <v>3.280288475201108</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.08818303388352836</v>
+      </c>
+      <c r="W78">
+        <v>0.2177418915086134</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3535807292843959</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2233568319421412</v>
+      </c>
+      <c r="C79">
+        <v>-2504.043742681799</v>
+      </c>
+      <c r="D79">
+        <v>1579.852297793508</v>
+      </c>
+      <c r="E79">
+        <v>2331.975208689195</v>
+      </c>
+      <c r="F79">
+        <v>4884.896040475307</v>
+      </c>
+      <c r="G79">
+        <v>801</v>
+      </c>
+      <c r="H79">
+        <v>3791.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>468.7</v>
+      </c>
+      <c r="K79">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L79">
+        <v>407.1</v>
+      </c>
+      <c r="M79">
+        <v>1166.513174465503</v>
+      </c>
+      <c r="N79">
+        <v>-759.4131744655034</v>
+      </c>
+      <c r="O79">
+        <v>-189.3976457116966</v>
+      </c>
+      <c r="P79">
+        <v>-570.0155287538068</v>
+      </c>
+      <c r="Q79">
+        <v>-508.4155287538069</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2412391060678043</v>
+      </c>
+      <c r="T79">
+        <v>3.42290971325333</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.08703779967724877</v>
+      </c>
+      <c r="W79">
+        <v>0.218015373437073</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3489887717612219</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2253568319421412</v>
+      </c>
+      <c r="C80">
+        <v>-2584.420905613936</v>
+      </c>
+      <c r="D80">
+        <v>1562.915343179232</v>
+      </c>
+      <c r="E80">
+        <v>2395.415417007056</v>
+      </c>
+      <c r="F80">
+        <v>4948.336248793168</v>
+      </c>
+      <c r="G80">
+        <v>801</v>
+      </c>
+      <c r="H80">
+        <v>3791.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>468.7</v>
+      </c>
+      <c r="K80">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L80">
+        <v>407.1</v>
+      </c>
+      <c r="M80">
+        <v>1181.662696211809</v>
+      </c>
+      <c r="N80">
+        <v>-774.5626962118087</v>
+      </c>
+      <c r="O80">
+        <v>-193.1759364352251</v>
+      </c>
+      <c r="P80">
+        <v>-581.3867597765835</v>
+      </c>
+      <c r="Q80">
+        <v>-519.7867597765835</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2504408836163409</v>
+      </c>
+      <c r="T80">
+        <v>3.578496518401209</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.08592193045061738</v>
+      </c>
+      <c r="W80">
+        <v>0.2182818430083926</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3445145567386422</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2273568319421412</v>
+      </c>
+      <c r="C81">
+        <v>-2664.43877199999</v>
+      </c>
+      <c r="D81">
+        <v>1546.337685111039</v>
+      </c>
+      <c r="E81">
+        <v>2458.855625324917</v>
+      </c>
+      <c r="F81">
+        <v>5011.776457111029</v>
+      </c>
+      <c r="G81">
+        <v>801</v>
+      </c>
+      <c r="H81">
+        <v>3791.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>468.7</v>
+      </c>
+      <c r="K81">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L81">
+        <v>407.1</v>
+      </c>
+      <c r="M81">
+        <v>1196.812217958114</v>
+      </c>
+      <c r="N81">
+        <v>-789.7122179581139</v>
+      </c>
+      <c r="O81">
+        <v>-196.9542271587537</v>
+      </c>
+      <c r="P81">
+        <v>-592.7579907993602</v>
+      </c>
+      <c r="Q81">
+        <v>-531.1579907993603</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2605190209314048</v>
+      </c>
+      <c r="T81">
+        <v>3.748901114515552</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.08483431107782474</v>
+      </c>
+      <c r="W81">
+        <v>0.2185415665146155</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3401536129824568</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2293568319421412</v>
+      </c>
+      <c r="C82">
+        <v>-2744.108654891581</v>
+      </c>
+      <c r="D82">
+        <v>1530.108010537309</v>
+      </c>
+      <c r="E82">
+        <v>2522.295833642778</v>
+      </c>
+      <c r="F82">
+        <v>5075.21666542889</v>
+      </c>
+      <c r="G82">
+        <v>801</v>
+      </c>
+      <c r="H82">
+        <v>3791.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>468.7</v>
+      </c>
+      <c r="K82">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L82">
+        <v>407.1</v>
+      </c>
+      <c r="M82">
+        <v>1211.961739704419</v>
+      </c>
+      <c r="N82">
+        <v>-804.8617397044192</v>
+      </c>
+      <c r="O82">
+        <v>-200.7325178822822</v>
+      </c>
+      <c r="P82">
+        <v>-604.129221822137</v>
+      </c>
+      <c r="Q82">
+        <v>-542.5292218221371</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.271604971977975</v>
+      </c>
+      <c r="T82">
+        <v>3.93634617024133</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.08377388218935193</v>
+      </c>
+      <c r="W82">
+        <v>0.2187947969331828</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3359016928201761</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2313568319421412</v>
+      </c>
+      <c r="C83">
+        <v>-2823.441397326301</v>
+      </c>
+      <c r="D83">
+        <v>1514.21547642045</v>
+      </c>
+      <c r="E83">
+        <v>2585.736041960639</v>
+      </c>
+      <c r="F83">
+        <v>5138.656873746751</v>
+      </c>
+      <c r="G83">
+        <v>801</v>
+      </c>
+      <c r="H83">
+        <v>3791.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>468.7</v>
+      </c>
+      <c r="K83">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L83">
+        <v>407.1</v>
+      </c>
+      <c r="M83">
+        <v>1227.111261450724</v>
+      </c>
+      <c r="N83">
+        <v>-820.0112614507242</v>
+      </c>
+      <c r="O83">
+        <v>-204.5108086058107</v>
+      </c>
+      <c r="P83">
+        <v>-615.5004528449135</v>
+      </c>
+      <c r="Q83">
+        <v>-553.9004528449136</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2838578652399737</v>
+      </c>
+      <c r="T83">
+        <v>4.143522284464559</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.08273963673022415</v>
+      </c>
+      <c r="W83">
+        <v>0.2190417747488225</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3317547583409147</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2333568319421412</v>
+      </c>
+      <c r="C84">
+        <v>-2902.447396485892</v>
+      </c>
+      <c r="D84">
+        <v>1498.649685578721</v>
+      </c>
+      <c r="E84">
+        <v>2649.1762502785</v>
+      </c>
+      <c r="F84">
+        <v>5202.097082064613</v>
+      </c>
+      <c r="G84">
+        <v>801</v>
+      </c>
+      <c r="H84">
+        <v>3791.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>468.7</v>
+      </c>
+      <c r="K84">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L84">
+        <v>407.1</v>
+      </c>
+      <c r="M84">
+        <v>1242.260783197029</v>
+      </c>
+      <c r="N84">
+        <v>-835.1607831970294</v>
+      </c>
+      <c r="O84">
+        <v>-208.2890993293392</v>
+      </c>
+      <c r="P84">
+        <v>-626.8716838676903</v>
+      </c>
+      <c r="Q84">
+        <v>-565.2716838676904</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2974721910866389</v>
+      </c>
+      <c r="T84">
+        <v>4.373717966934811</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.08173061677009946</v>
+      </c>
+      <c r="W84">
+        <v>0.2192827287153002</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3277089686050499</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2353568319421412</v>
+      </c>
+      <c r="C85">
+        <v>-2981.136626379558</v>
+      </c>
+      <c r="D85">
+        <v>1483.400664002916</v>
+      </c>
+      <c r="E85">
+        <v>2712.616458596362</v>
+      </c>
+      <c r="F85">
+        <v>5265.537290382474</v>
+      </c>
+      <c r="G85">
+        <v>801</v>
+      </c>
+      <c r="H85">
+        <v>3791.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>468.7</v>
+      </c>
+      <c r="K85">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L85">
+        <v>407.1</v>
+      </c>
+      <c r="M85">
+        <v>1257.410304943335</v>
+      </c>
+      <c r="N85">
+        <v>-850.3103049433347</v>
+      </c>
+      <c r="O85">
+        <v>-212.0673900528677</v>
+      </c>
+      <c r="P85">
+        <v>-638.242914890467</v>
+      </c>
+      <c r="Q85">
+        <v>-576.642914890467</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3126882023270295</v>
+      </c>
+      <c r="T85">
+        <v>4.630995494401566</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.08074591054395368</v>
+      </c>
+      <c r="W85">
+        <v>0.2195178765621039</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.323760667778483</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2373568319421412</v>
+      </c>
+      <c r="C86">
+        <v>-3059.518659156372</v>
+      </c>
+      <c r="D86">
+        <v>1468.458839543961</v>
+      </c>
+      <c r="E86">
+        <v>2776.056666914222</v>
+      </c>
+      <c r="F86">
+        <v>5328.977498700334</v>
+      </c>
+      <c r="G86">
+        <v>801</v>
+      </c>
+      <c r="H86">
+        <v>3791.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>468.7</v>
+      </c>
+      <c r="K86">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L86">
+        <v>407.1</v>
+      </c>
+      <c r="M86">
+        <v>1272.55982668964</v>
+      </c>
+      <c r="N86">
+        <v>-865.4598266896397</v>
+      </c>
+      <c r="O86">
+        <v>-215.8456807763962</v>
+      </c>
+      <c r="P86">
+        <v>-649.6141459132435</v>
+      </c>
+      <c r="Q86">
+        <v>-588.0141459132435</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3298062149724686</v>
+      </c>
+      <c r="T86">
+        <v>4.92043271280166</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.07978464970414473</v>
+      </c>
+      <c r="W86">
+        <v>0.2197474256506502</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3199063741144536</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2393568319421412</v>
+      </c>
+      <c r="C87">
+        <v>-3137.602685142512</v>
+      </c>
+      <c r="D87">
+        <v>1453.815021875684</v>
+      </c>
+      <c r="E87">
+        <v>2839.496875232084</v>
+      </c>
+      <c r="F87">
+        <v>5392.417707018196</v>
+      </c>
+      <c r="G87">
+        <v>801</v>
+      </c>
+      <c r="H87">
+        <v>3791.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>468.7</v>
+      </c>
+      <c r="K87">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L87">
+        <v>407.1</v>
+      </c>
+      <c r="M87">
+        <v>1287.709348435945</v>
+      </c>
+      <c r="N87">
+        <v>-880.6093484359452</v>
+      </c>
+      <c r="O87">
+        <v>-219.6239714999248</v>
+      </c>
+      <c r="P87">
+        <v>-660.9853769360204</v>
+      </c>
+      <c r="Q87">
+        <v>-599.3853769360205</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3492066293039665</v>
+      </c>
+      <c r="T87">
+        <v>5.248461560321771</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0788460067664489</v>
+      </c>
+      <c r="W87">
+        <v>0.219971573584172</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.316142769713107</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2413568319421412</v>
+      </c>
+      <c r="C88">
+        <v>-3215.397531691395</v>
+      </c>
+      <c r="D88">
+        <v>1439.460383644662</v>
+      </c>
+      <c r="E88">
+        <v>2902.937083549945</v>
+      </c>
+      <c r="F88">
+        <v>5455.857915336057</v>
+      </c>
+      <c r="G88">
+        <v>801</v>
+      </c>
+      <c r="H88">
+        <v>3791.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>468.7</v>
+      </c>
+      <c r="K88">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L88">
+        <v>407.1</v>
+      </c>
+      <c r="M88">
+        <v>1302.85887018225</v>
+      </c>
+      <c r="N88">
+        <v>-895.7588701822505</v>
+      </c>
+      <c r="O88">
+        <v>-223.4022622234533</v>
+      </c>
+      <c r="P88">
+        <v>-672.3566079587971</v>
+      </c>
+      <c r="Q88">
+        <v>-610.7566079587971</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.371378531397107</v>
+      </c>
+      <c r="T88">
+        <v>5.623351671773326</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.07792919273428088</v>
+      </c>
+      <c r="W88">
+        <v>0.2201905087750537</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3124666909955127</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2433568319421412</v>
+      </c>
+      <c r="C89">
+        <v>-3292.911680928049</v>
+      </c>
+      <c r="D89">
+        <v>1425.386442725868</v>
+      </c>
+      <c r="E89">
+        <v>2966.377291867806</v>
+      </c>
+      <c r="F89">
+        <v>5519.298123653918</v>
+      </c>
+      <c r="G89">
+        <v>801</v>
+      </c>
+      <c r="H89">
+        <v>3791.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>468.7</v>
+      </c>
+      <c r="K89">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L89">
+        <v>407.1</v>
+      </c>
+      <c r="M89">
+        <v>1318.008391928556</v>
+      </c>
+      <c r="N89">
+        <v>-910.9083919285557</v>
+      </c>
+      <c r="O89">
+        <v>-227.1805529469819</v>
+      </c>
+      <c r="P89">
+        <v>-683.7278389815739</v>
+      </c>
+      <c r="Q89">
+        <v>-622.1278389815739</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3969614953507307</v>
+      </c>
+      <c r="T89">
+        <v>6.05591718498666</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.07703345488676042</v>
+      </c>
+      <c r="W89">
+        <v>0.2204044109730416</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3088751198346447</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2453568319421412</v>
+      </c>
+      <c r="C90">
+        <v>-3370.153286462587</v>
+      </c>
+      <c r="D90">
+        <v>1411.585045509192</v>
+      </c>
+      <c r="E90">
+        <v>3029.817500185667</v>
+      </c>
+      <c r="F90">
+        <v>5582.738331971779</v>
+      </c>
+      <c r="G90">
+        <v>801</v>
+      </c>
+      <c r="H90">
+        <v>3791.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>468.7</v>
+      </c>
+      <c r="K90">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L90">
+        <v>407.1</v>
+      </c>
+      <c r="M90">
+        <v>1333.157913674861</v>
+      </c>
+      <c r="N90">
+        <v>-926.057913674861</v>
+      </c>
+      <c r="O90">
+        <v>-230.9588436705104</v>
+      </c>
+      <c r="P90">
+        <v>-695.0990700043506</v>
+      </c>
+      <c r="Q90">
+        <v>-633.4990700043506</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4268082866299583</v>
+      </c>
+      <c r="T90">
+        <v>6.560576950402216</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.07615807471759269</v>
+      </c>
+      <c r="W90">
+        <v>0.2206134517574389</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3053651752910692</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2473568319421412</v>
+      </c>
+      <c r="C91">
+        <v>-3447.13018914202</v>
+      </c>
+      <c r="D91">
+        <v>1398.04835114762</v>
+      </c>
+      <c r="E91">
+        <v>3093.257708503528</v>
+      </c>
+      <c r="F91">
+        <v>5646.17854028964</v>
+      </c>
+      <c r="G91">
+        <v>801</v>
+      </c>
+      <c r="H91">
+        <v>3791.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>468.7</v>
+      </c>
+      <c r="K91">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L91">
+        <v>407.1</v>
+      </c>
+      <c r="M91">
+        <v>1348.307435421166</v>
+      </c>
+      <c r="N91">
+        <v>-941.2074354211662</v>
+      </c>
+      <c r="O91">
+        <v>-234.7371343940389</v>
+      </c>
+      <c r="P91">
+        <v>-706.4703010271273</v>
+      </c>
+      <c r="Q91">
+        <v>-644.8703010271274</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4620817672326817</v>
+      </c>
+      <c r="T91">
+        <v>7.156993036802417</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.07530236601290063</v>
+      </c>
+      <c r="W91">
+        <v>0.2208177949961193</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3019341059057763</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2493568319421412</v>
+      </c>
+      <c r="C92">
+        <v>-3523.849931904356</v>
+      </c>
+      <c r="D92">
+        <v>1384.768816703145</v>
+      </c>
+      <c r="E92">
+        <v>3156.697916821389</v>
+      </c>
+      <c r="F92">
+        <v>5709.618748607501</v>
+      </c>
+      <c r="G92">
+        <v>801</v>
+      </c>
+      <c r="H92">
+        <v>3791.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>468.7</v>
+      </c>
+      <c r="K92">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L92">
+        <v>407.1</v>
+      </c>
+      <c r="M92">
+        <v>1363.456957167472</v>
+      </c>
+      <c r="N92">
+        <v>-956.3569571674715</v>
+      </c>
+      <c r="O92">
+        <v>-238.5154251175674</v>
+      </c>
+      <c r="P92">
+        <v>-717.841532049904</v>
+      </c>
+      <c r="Q92">
+        <v>-656.241532049904</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.50440994395595</v>
+      </c>
+      <c r="T92">
+        <v>7.872692340482661</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.07446567305720173</v>
+      </c>
+      <c r="W92">
+        <v>0.2210175972739402</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2985792825068232</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2513568319421412</v>
+      </c>
+      <c r="C93">
+        <v>-3600.3197737941</v>
+      </c>
+      <c r="D93">
+        <v>1371.739183131263</v>
+      </c>
+      <c r="E93">
+        <v>3220.13812513925</v>
+      </c>
+      <c r="F93">
+        <v>5773.058956925363</v>
+      </c>
+      <c r="G93">
+        <v>801</v>
+      </c>
+      <c r="H93">
+        <v>3791.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>468.7</v>
+      </c>
+      <c r="K93">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L93">
+        <v>407.1</v>
+      </c>
+      <c r="M93">
+        <v>1378.606478913777</v>
+      </c>
+      <c r="N93">
+        <v>-971.5064789137765</v>
+      </c>
+      <c r="O93">
+        <v>-242.2937158410959</v>
+      </c>
+      <c r="P93">
+        <v>-729.2127630726806</v>
+      </c>
+      <c r="Q93">
+        <v>-667.6127630726805</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5561443821732779</v>
+      </c>
+      <c r="T93">
+        <v>8.747435933869623</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.07364736895767206</v>
+      </c>
+      <c r="W93">
+        <v>0.2212130082929079</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2952981914902647</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2533568319421412</v>
+      </c>
+      <c r="C94">
+        <v>-3676.546703193872</v>
+      </c>
+      <c r="D94">
+        <v>1358.952462049352</v>
+      </c>
+      <c r="E94">
+        <v>3283.578333457112</v>
+      </c>
+      <c r="F94">
+        <v>5836.499165243224</v>
+      </c>
+      <c r="G94">
+        <v>801</v>
+      </c>
+      <c r="H94">
+        <v>3791.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>468.7</v>
+      </c>
+      <c r="K94">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L94">
+        <v>407.1</v>
+      </c>
+      <c r="M94">
+        <v>1393.756000660082</v>
+      </c>
+      <c r="N94">
+        <v>-986.6560006600818</v>
+      </c>
+      <c r="O94">
+        <v>-246.0720065646244</v>
+      </c>
+      <c r="P94">
+        <v>-740.5839940954573</v>
+      </c>
+      <c r="Q94">
+        <v>-678.9839940954573</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6208124299449376</v>
+      </c>
+      <c r="T94">
+        <v>9.840865425603328</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.07284685407769735</v>
+      </c>
+      <c r="W94">
+        <v>0.2214041712462459</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2920884285392836</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2553568319421412</v>
+      </c>
+      <c r="C95">
+        <v>-3752.537450322833</v>
+      </c>
+      <c r="D95">
+        <v>1346.401923238252</v>
+      </c>
+      <c r="E95">
+        <v>3347.018541774973</v>
+      </c>
+      <c r="F95">
+        <v>5899.939373561085</v>
+      </c>
+      <c r="G95">
+        <v>801</v>
+      </c>
+      <c r="H95">
+        <v>3791.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>468.7</v>
+      </c>
+      <c r="K95">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L95">
+        <v>407.1</v>
+      </c>
+      <c r="M95">
+        <v>1408.905522406387</v>
+      </c>
+      <c r="N95">
+        <v>-1001.805522406387</v>
+      </c>
+      <c r="O95">
+        <v>-249.850297288153</v>
+      </c>
+      <c r="P95">
+        <v>-751.955225118234</v>
+      </c>
+      <c r="Q95">
+        <v>-690.3552251182341</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7039570627942144</v>
+      </c>
+      <c r="T95">
+        <v>11.24670334354666</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.07206355457148554</v>
+      </c>
+      <c r="W95">
+        <v>0.2215912231683293</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2889476927485386</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2573568319421412</v>
+      </c>
+      <c r="C96">
+        <v>-3828.298499048874</v>
+      </c>
+      <c r="D96">
+        <v>1334.081082830072</v>
+      </c>
+      <c r="E96">
+        <v>3410.458750092834</v>
+      </c>
+      <c r="F96">
+        <v>5963.379581878946</v>
+      </c>
+      <c r="G96">
+        <v>801</v>
+      </c>
+      <c r="H96">
+        <v>3791.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>468.7</v>
+      </c>
+      <c r="K96">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L96">
+        <v>407.1</v>
+      </c>
+      <c r="M96">
+        <v>1424.055044152692</v>
+      </c>
+      <c r="N96">
+        <v>-1016.955044152692</v>
+      </c>
+      <c r="O96">
+        <v>-253.6285880116815</v>
+      </c>
+      <c r="P96">
+        <v>-763.3264561410108</v>
+      </c>
+      <c r="Q96">
+        <v>-701.7264561410109</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8148165732599173</v>
+      </c>
+      <c r="T96">
+        <v>13.12115390080444</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.07129692101221442</v>
+      </c>
+      <c r="W96">
+        <v>0.2217742952622832</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2858737811235542</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2593568319421412</v>
+      </c>
+      <c r="C97">
+        <v>-3903.836098058129</v>
+      </c>
+      <c r="D97">
+        <v>1321.983692138678</v>
+      </c>
+      <c r="E97">
+        <v>3473.898958410695</v>
+      </c>
+      <c r="F97">
+        <v>6026.819790196807</v>
+      </c>
+      <c r="G97">
+        <v>801</v>
+      </c>
+      <c r="H97">
+        <v>3791.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>468.7</v>
+      </c>
+      <c r="K97">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L97">
+        <v>407.1</v>
+      </c>
+      <c r="M97">
+        <v>1439.204565898998</v>
+      </c>
+      <c r="N97">
+        <v>-1032.104565898997</v>
+      </c>
+      <c r="O97">
+        <v>-257.40687873521</v>
+      </c>
+      <c r="P97">
+        <v>-774.6976871637874</v>
+      </c>
+      <c r="Q97">
+        <v>-713.0976871637874</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9700198879119011</v>
+      </c>
+      <c r="T97">
+        <v>15.74538468096534</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0705464271068227</v>
+      </c>
+      <c r="W97">
+        <v>0.2219535132068907</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2828645834275169</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2613568319421412</v>
+      </c>
+      <c r="C98">
+        <v>-3979.156271422242</v>
+      </c>
+      <c r="D98">
+        <v>1310.103727092426</v>
+      </c>
+      <c r="E98">
+        <v>3537.339166728556</v>
+      </c>
+      <c r="F98">
+        <v>6090.259998514668</v>
+      </c>
+      <c r="G98">
+        <v>801</v>
+      </c>
+      <c r="H98">
+        <v>3791.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>468.7</v>
+      </c>
+      <c r="K98">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L98">
+        <v>407.1</v>
+      </c>
+      <c r="M98">
+        <v>1454.354087645303</v>
+      </c>
+      <c r="N98">
+        <v>-1047.254087645303</v>
+      </c>
+      <c r="O98">
+        <v>-261.1851694587385</v>
+      </c>
+      <c r="P98">
+        <v>-786.0689181865641</v>
+      </c>
+      <c r="Q98">
+        <v>-724.4689181865642</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.202824859889874</v>
+      </c>
+      <c r="T98">
+        <v>19.68173085120663</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.06981156849112663</v>
+      </c>
+      <c r="W98">
+        <v>0.222128997444319</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2799180773501468</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2633568319421412</v>
+      </c>
+      <c r="C99">
+        <v>-4054.264828600938</v>
+      </c>
+      <c r="D99">
+        <v>1298.435378231591</v>
+      </c>
+      <c r="E99">
+        <v>3600.779375046417</v>
+      </c>
+      <c r="F99">
+        <v>6153.700206832529</v>
+      </c>
+      <c r="G99">
+        <v>801</v>
+      </c>
+      <c r="H99">
+        <v>3791.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>468.7</v>
+      </c>
+      <c r="K99">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L99">
+        <v>407.1</v>
+      </c>
+      <c r="M99">
+        <v>1469.503609391608</v>
+      </c>
+      <c r="N99">
+        <v>-1062.403609391608</v>
+      </c>
+      <c r="O99">
+        <v>-264.9634601822671</v>
+      </c>
+      <c r="P99">
+        <v>-797.4401492093409</v>
+      </c>
+      <c r="Q99">
+        <v>-735.840149209341</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.590833146519832</v>
+      </c>
+      <c r="T99">
+        <v>26.24230780160884</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.06909186159946552</v>
+      </c>
+      <c r="W99">
+        <v>0.2223008634500476</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2770323239754031</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2653568319421412</v>
+      </c>
+      <c r="C100">
+        <v>-4129.167373914783</v>
+      </c>
+      <c r="D100">
+        <v>1286.973041235608</v>
+      </c>
+      <c r="E100">
+        <v>3664.219583364278</v>
+      </c>
+      <c r="F100">
+        <v>6217.14041515039</v>
+      </c>
+      <c r="G100">
+        <v>801</v>
+      </c>
+      <c r="H100">
+        <v>3791.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>468.7</v>
+      </c>
+      <c r="K100">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L100">
+        <v>407.1</v>
+      </c>
+      <c r="M100">
+        <v>1484.653131137913</v>
+      </c>
+      <c r="N100">
+        <v>-1077.553131137913</v>
+      </c>
+      <c r="O100">
+        <v>-268.7417509057956</v>
+      </c>
+      <c r="P100">
+        <v>-808.8113802321175</v>
+      </c>
+      <c r="Q100">
+        <v>-747.2113802321176</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.366849719779748</v>
+      </c>
+      <c r="T100">
+        <v>39.36346170241326</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06838684260355261</v>
+      </c>
+      <c r="W100">
+        <v>0.2224692219862716</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2742054635266745</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2673568319421412</v>
+      </c>
+      <c r="C101">
+        <v>-4203.869315520594</v>
+      </c>
+      <c r="D101">
+        <v>1275.711307947657</v>
+      </c>
+      <c r="E101">
+        <v>3727.659791682139</v>
+      </c>
+      <c r="F101">
+        <v>6280.580623468251</v>
+      </c>
+      <c r="G101">
+        <v>801</v>
+      </c>
+      <c r="H101">
+        <v>3791.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>468.7</v>
+      </c>
+      <c r="K101">
+        <v>61.59999999999997</v>
+      </c>
+      <c r="L101">
+        <v>407.1</v>
+      </c>
+      <c r="M101">
+        <v>1499.802652884219</v>
+      </c>
+      <c r="N101">
+        <v>-1092.702652884218</v>
+      </c>
+      <c r="O101">
+        <v>-272.5200416293242</v>
+      </c>
+      <c r="P101">
+        <v>-820.1826112548943</v>
+      </c>
+      <c r="Q101">
+        <v>-758.5826112548943</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.694899439559496</v>
+      </c>
+      <c r="T101">
+        <v>78.72692340482652</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06769606641563794</v>
+      </c>
+      <c r="W101">
+        <v>0.2226341793399457</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2714357113698393</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_apparel.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_apparel.xlsx
@@ -647,10 +647,10 @@
         <v>0.3071935782648966</v>
       </c>
       <c r="X2">
-        <v>0.09466403655545128</v>
+        <v>0.09463262132447356</v>
       </c>
       <c r="Y2">
-        <v>0.2125295417094453</v>
+        <v>0.212560956940423</v>
       </c>
       <c r="Z2">
         <v>1.677854640637447</v>
@@ -659,10 +659,10 @@
         <v>0.2124241575143968</v>
       </c>
       <c r="AB2">
-        <v>0.07623574109231945</v>
+        <v>0.07621622518933774</v>
       </c>
       <c r="AC2">
-        <v>0.1361884164220774</v>
+        <v>0.1362079323250591</v>
       </c>
       <c r="AD2">
         <v>2379.8</v>
@@ -781,10 +781,10 @@
         <v>0.3071935782648966</v>
       </c>
       <c r="X3">
-        <v>0.09466403655545128</v>
+        <v>0.09463262132447356</v>
       </c>
       <c r="Y3">
-        <v>0.2125295417094453</v>
+        <v>0.212560956940423</v>
       </c>
       <c r="Z3">
         <v>1.677854640637447</v>
@@ -793,10 +793,10 @@
         <v>0.2124241575143968</v>
       </c>
       <c r="AB3">
-        <v>0.07623574109231945</v>
+        <v>0.07621622518933774</v>
       </c>
       <c r="AC3">
-        <v>0.1361884164220774</v>
+        <v>0.1362079323250591</v>
       </c>
       <c r="AD3">
         <v>2379.8</v>
@@ -1133,49 +1133,49 @@
         <v>4.67329762815608</v>
       </c>
       <c r="F2">
-        <v>4.5139831657871</v>
+        <v>4.60502886881104</v>
       </c>
       <c r="G2">
         <v>3.50152597562483</v>
       </c>
       <c r="H2">
-        <v>3.51284324522303</v>
+        <v>3.60528648851837</v>
       </c>
       <c r="I2">
         <v>0.378775760218403</v>
       </c>
       <c r="J2">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="K2">
         <v>3907.4</v>
       </c>
       <c r="L2">
-        <v>3988.82000186512</v>
+        <v>4007.28552913785</v>
       </c>
       <c r="M2">
         <v>5607.53827381513</v>
       </c>
       <c r="N2">
-        <v>5696.65854591487</v>
+        <v>5778.02245592575</v>
       </c>
       <c r="O2">
         <v>2382.43827381513</v>
       </c>
       <c r="P2">
-        <v>2390.13854404975</v>
+        <v>2453.0369267879</v>
       </c>
       <c r="Q2">
-        <v>0.0762357410923195</v>
+        <v>0.0762162251893377</v>
       </c>
       <c r="R2">
-        <v>0.0752559899641945</v>
+        <v>0.07436841887429479</v>
       </c>
       <c r="S2">
         <v>0.04601178</v>
       </c>
       <c r="T2">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0946640365554513</v>
+        <v>0.0946326213244736</v>
       </c>
       <c r="X2">
-        <v>0.0947440141357976</v>
+        <v>0.095377424056221</v>
       </c>
       <c r="Y2">
         <v>1.1277741645375</v>
       </c>
       <c r="Z2">
-        <v>1.12962003432671</v>
+        <v>1.14497515141388</v>
       </c>
       <c r="AA2">
         <v>2379.8</v>
@@ -1230,7 +1230,7 @@
         <v>3907.4</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07932226042963156</v>
+        <v>0.07930070859665728</v>
       </c>
       <c r="C2">
-        <v>6026.454769334697</v>
+        <v>6026.615798250753</v>
       </c>
       <c r="D2">
-        <v>5344.154769334697</v>
+        <v>5344.315798250753</v>
       </c>
       <c r="E2">
         <v>-2382.438273815133</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07932226042963156</v>
+        <v>0.07930070859665728</v>
       </c>
       <c r="T2">
         <v>0.7736884202461267</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.2494</v>
       </c>
       <c r="W2">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07916871611212005</v>
+        <v>0.07913670962941723</v>
       </c>
       <c r="C3">
-        <v>5976.072689094695</v>
+        <v>5977.089120196127</v>
       </c>
       <c r="D3">
-        <v>5356.671071832847</v>
+        <v>5357.687502934278</v>
       </c>
       <c r="E3">
         <v>-2319.539891076981</v>
@@ -1533,37 +1533,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M3">
-        <v>3.251846387562424</v>
+        <v>3.163788651729011</v>
       </c>
       <c r="N3">
-        <v>621.4338678981518</v>
+        <v>621.5219256339852</v>
       </c>
       <c r="O3">
-        <v>154.9856066537991</v>
+        <v>155.0075682531159</v>
       </c>
       <c r="P3">
-        <v>466.4482612443527</v>
+        <v>466.5143573808693</v>
       </c>
       <c r="Q3">
-        <v>536.0482612443527</v>
+        <v>536.1143573808694</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07957642011325258</v>
+        <v>0.07955470487819921</v>
       </c>
       <c r="T3">
         <v>0.7795543851778109</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.2494</v>
       </c>
       <c r="W3">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>192.1018522507692</v>
+        <v>197.4486234863771</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07901517179460855</v>
+        <v>0.07897271066217716</v>
       </c>
       <c r="C4">
-        <v>5925.749374215173</v>
+        <v>5927.629523124911</v>
       </c>
       <c r="D4">
-        <v>5369.246139691475</v>
+        <v>5371.126288601213</v>
       </c>
       <c r="E4">
         <v>-2256.64150833883</v>
@@ -1615,37 +1615,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M4">
-        <v>6.503692775124848</v>
+        <v>6.327577303458023</v>
       </c>
       <c r="N4">
-        <v>618.1820215105894</v>
+        <v>618.3581369822562</v>
       </c>
       <c r="O4">
-        <v>154.174596164741</v>
+        <v>154.2185193633747</v>
       </c>
       <c r="P4">
-        <v>464.0074253458484</v>
+        <v>464.1396176188815</v>
       </c>
       <c r="Q4">
-        <v>533.6074253458485</v>
+        <v>533.7396176188815</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.0798357667291924</v>
+        <v>0.07981388475732364</v>
       </c>
       <c r="T4">
         <v>0.7855400636795297</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.2494</v>
       </c>
       <c r="W4">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.05092612538459</v>
+        <v>98.72431174318854</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07886162747709705</v>
+        <v>0.0788087116949371</v>
       </c>
       <c r="C5">
-        <v>5875.485239534334</v>
+        <v>5878.237513087814</v>
       </c>
       <c r="D5">
-        <v>5381.880387748788</v>
+        <v>5384.632661302267</v>
       </c>
       <c r="E5">
         <v>-2193.743125600678</v>
@@ -1697,37 +1697,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M5">
-        <v>9.755539162687271</v>
+        <v>9.491365955187034</v>
       </c>
       <c r="N5">
-        <v>614.930175123027</v>
+        <v>615.1943483305272</v>
       </c>
       <c r="O5">
-        <v>153.3635856756829</v>
+        <v>153.4294704736335</v>
       </c>
       <c r="P5">
-        <v>461.566589447344</v>
+        <v>461.7648778568937</v>
       </c>
       <c r="Q5">
-        <v>531.166589447344</v>
+        <v>531.3648778568937</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.0801004606980382</v>
+        <v>0.08007840855148154</v>
       </c>
       <c r="T5">
         <v>0.79164915823283</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.2494</v>
       </c>
       <c r="W5">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.03395075025639</v>
+        <v>65.81620782879237</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07870808315958554</v>
+        <v>0.07864471272769703</v>
       </c>
       <c r="C6">
-        <v>5825.280703804177</v>
+        <v>5828.913601238497</v>
       </c>
       <c r="D6">
-        <v>5394.574234756783</v>
+        <v>5398.207132191102</v>
       </c>
       <c r="E6">
         <v>-2130.844742862527</v>
@@ -1779,37 +1779,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M6">
-        <v>13.0073855502497</v>
+        <v>12.65515460691605</v>
       </c>
       <c r="N6">
-        <v>611.6783287354644</v>
+        <v>612.0305596787981</v>
       </c>
       <c r="O6">
-        <v>152.5525751866248</v>
+        <v>152.6404215838922</v>
       </c>
       <c r="P6">
-        <v>459.1257535488396</v>
+        <v>459.3901380949059</v>
       </c>
       <c r="Q6">
-        <v>528.7257535488396</v>
+        <v>528.9901380949059</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08037066912456828</v>
+        <v>0.08034844325801774</v>
       </c>
       <c r="T6">
         <v>0.7978855255893242</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.2494</v>
       </c>
       <c r="W6">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.02546306269229</v>
+        <v>49.36215587159427</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.07855453884207406</v>
+        <v>0.07848071376045697</v>
       </c>
       <c r="C7">
-        <v>5775.136189736756</v>
+        <v>5779.658303898044</v>
       </c>
       <c r="D7">
-        <v>5407.328103427512</v>
+        <v>5411.850217588801</v>
       </c>
       <c r="E7">
         <v>-2067.946360124376</v>
@@ -1861,37 +1861,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M7">
-        <v>16.25923193781212</v>
+        <v>15.81894325864506</v>
       </c>
       <c r="N7">
-        <v>608.426482347902</v>
+        <v>608.8667710270691</v>
       </c>
       <c r="O7">
-        <v>151.7415646975668</v>
+        <v>151.8513726941511</v>
       </c>
       <c r="P7">
-        <v>456.6849176503353</v>
+        <v>457.0153983329181</v>
       </c>
       <c r="Q7">
-        <v>526.2849176503353</v>
+        <v>526.6153983329182</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08064656614955164</v>
+        <v>0.08062416290574417</v>
       </c>
       <c r="T7">
         <v>0.8042531848901658</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.2494</v>
       </c>
       <c r="W7">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.42037045015383</v>
+        <v>39.48972469727541</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07840099452456255</v>
+        <v>0.0783167147932169</v>
       </c>
       <c r="C8">
-        <v>5725.052124051113</v>
+        <v>5730.472142620439</v>
       </c>
       <c r="D8">
-        <v>5420.142420480021</v>
+        <v>5425.562439049347</v>
       </c>
       <c r="E8">
         <v>-2005.047977386225</v>
@@ -1943,37 +1943,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M8">
-        <v>19.51107832537454</v>
+        <v>18.98273191037407</v>
       </c>
       <c r="N8">
-        <v>605.1746359603396</v>
+        <v>605.7029823753402</v>
       </c>
       <c r="O8">
-        <v>150.9305542085087</v>
+        <v>151.0623238044099</v>
       </c>
       <c r="P8">
-        <v>454.2440817518309</v>
+        <v>454.6406585709303</v>
       </c>
       <c r="Q8">
-        <v>523.8440817518309</v>
+        <v>524.2406585709303</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0809283333240027</v>
+        <v>0.08090574892895415</v>
       </c>
       <c r="T8">
         <v>0.810756326303791</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.2494</v>
       </c>
       <c r="W8">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.0169753751282</v>
+        <v>32.90810391439619</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07824745020705105</v>
+        <v>0.07815271582597684</v>
       </c>
       <c r="C9">
-        <v>5675.028937520857</v>
+        <v>5681.355644259015</v>
       </c>
       <c r="D9">
-        <v>5433.017616687916</v>
+        <v>5439.344323426074</v>
       </c>
       <c r="E9">
         <v>-1942.149594648073</v>
@@ -2025,37 +2025,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M9">
-        <v>22.76292471293697</v>
+        <v>22.14652056210308</v>
       </c>
       <c r="N9">
-        <v>601.9227895727772</v>
+        <v>602.5391937236111</v>
       </c>
       <c r="O9">
-        <v>150.1195437194506</v>
+        <v>150.2732749146686</v>
       </c>
       <c r="P9">
-        <v>451.8032458533266</v>
+        <v>452.2659188089425</v>
       </c>
       <c r="Q9">
-        <v>521.4032458533266</v>
+        <v>521.8659188089425</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08121616000758178</v>
+        <v>0.0811933905655665</v>
       </c>
       <c r="T9">
         <v>0.8173993202209354</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.2494</v>
       </c>
       <c r="W9">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.44312175010988</v>
+        <v>28.20694621233958</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07809390588953956</v>
+        <v>0.07798871685873679</v>
       </c>
       <c r="C10">
-        <v>5625.067065022446</v>
+        <v>5632.309341033943</v>
       </c>
       <c r="D10">
-        <v>5445.954126927656</v>
+        <v>5453.196402939154</v>
       </c>
       <c r="E10">
         <v>-1879.251211909922</v>
@@ -2107,37 +2107,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M10">
-        <v>26.01477110049939</v>
+        <v>25.31030921383209</v>
       </c>
       <c r="N10">
-        <v>598.6709431852148</v>
+        <v>599.3754050718821</v>
       </c>
       <c r="O10">
-        <v>149.3085332303926</v>
+        <v>149.4842260249274</v>
       </c>
       <c r="P10">
-        <v>449.3624099548222</v>
+        <v>449.8911790469547</v>
       </c>
       <c r="Q10">
-        <v>518.9624099548223</v>
+        <v>519.4911790469548</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08151024379297778</v>
+        <v>0.08148728528123564</v>
       </c>
       <c r="T10">
         <v>0.8241867270493218</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.2494</v>
       </c>
       <c r="W10">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.01273153134614</v>
+        <v>24.68107793579714</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07794036157202806</v>
+        <v>0.07782471789149673</v>
       </c>
       <c r="C11">
-        <v>5575.166945584144</v>
+        <v>5583.333770600742</v>
       </c>
       <c r="D11">
-        <v>5458.952390227506</v>
+        <v>5467.119215244104</v>
       </c>
       <c r="E11">
         <v>-1816.352829171771</v>
@@ -2189,37 +2189,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M11">
-        <v>29.26661748806181</v>
+        <v>28.4740978655611</v>
       </c>
       <c r="N11">
-        <v>595.4190967976524</v>
+        <v>596.2116164201531</v>
       </c>
       <c r="O11">
-        <v>148.4975227413345</v>
+        <v>148.6951771351862</v>
       </c>
       <c r="P11">
-        <v>446.9215740563179</v>
+        <v>447.5164392849669</v>
       </c>
       <c r="Q11">
-        <v>516.5215740563179</v>
+        <v>517.1164392849669</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08181079095827259</v>
+        <v>0.08178763922142497</v>
       </c>
       <c r="T11">
         <v>0.8311233076541563</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.2494</v>
       </c>
       <c r="W11">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.34465025008547</v>
+        <v>21.93873594293079</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.07778681725451654</v>
+        <v>0.07766071892425666</v>
       </c>
       <c r="C12">
-        <v>5525.329022435693</v>
+        <v>5534.429476119833</v>
       </c>
       <c r="D12">
-        <v>5472.012849817206</v>
+        <v>5481.113303501346</v>
       </c>
       <c r="E12">
         <v>-1753.454446433619</v>
@@ -2271,37 +2271,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M12">
-        <v>32.51846387562424</v>
+        <v>31.63788651729012</v>
       </c>
       <c r="N12">
-        <v>592.16725041009</v>
+        <v>593.0478277684241</v>
       </c>
       <c r="O12">
-        <v>147.6865122522765</v>
+        <v>147.906128245445</v>
       </c>
       <c r="P12">
-        <v>444.4807381578136</v>
+        <v>445.1416995229791</v>
       </c>
       <c r="Q12">
-        <v>514.0807381578136</v>
+        <v>514.7416995229792</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08211801694946283</v>
+        <v>0.08209466769361851</v>
       </c>
       <c r="T12">
         <v>0.8382140344946536</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.2494</v>
       </c>
       <c r="W12">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.21018522507692</v>
+        <v>19.74486234863771</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07763327293700505</v>
+        <v>0.0774967199570166</v>
       </c>
       <c r="C13">
-        <v>5475.553743058679</v>
+        <v>5485.597006327188</v>
       </c>
       <c r="D13">
-        <v>5485.135953178344</v>
+        <v>5495.179216446852</v>
       </c>
       <c r="E13">
         <v>-1690.556063695468</v>
@@ -2353,37 +2353,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M13">
-        <v>35.77031026318666</v>
+        <v>34.80167516901913</v>
       </c>
       <c r="N13">
-        <v>588.9154040225276</v>
+        <v>589.884039116695</v>
       </c>
       <c r="O13">
-        <v>146.8755017632184</v>
+        <v>147.1170793557037</v>
       </c>
       <c r="P13">
-        <v>442.0399022593092</v>
+        <v>442.7669597609913</v>
       </c>
       <c r="Q13">
-        <v>511.6399022593092</v>
+        <v>512.3669597609913</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08243214689551129</v>
+        <v>0.08240859568204112</v>
       </c>
       <c r="T13">
         <v>0.845464103511342</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.2494</v>
       </c>
       <c r="W13">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.46380475006993</v>
+        <v>17.94987486239792</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07747972861949354</v>
+        <v>0.0773327209897765</v>
       </c>
       <c r="C14">
-        <v>5425.84155923766</v>
+        <v>5436.836915606046</v>
       </c>
       <c r="D14">
-        <v>5498.322152095475</v>
+        <v>5509.317508463861</v>
       </c>
       <c r="E14">
         <v>-1627.657680957317</v>
@@ -2435,37 +2435,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M14">
-        <v>39.02215665074908</v>
+        <v>37.96546382074813</v>
       </c>
       <c r="N14">
-        <v>585.6635576349652</v>
+        <v>586.7202504649661</v>
       </c>
       <c r="O14">
-        <v>146.0644912741603</v>
+        <v>146.3280304659625</v>
       </c>
       <c r="P14">
-        <v>439.5990663608048</v>
+        <v>440.3922199990035</v>
       </c>
       <c r="Q14">
-        <v>509.1990663608049</v>
+        <v>509.9922199990035</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08275341615851539</v>
+        <v>0.08272965839747332</v>
       </c>
       <c r="T14">
         <v>0.8528789468238643</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.2494</v>
       </c>
       <c r="W14">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.0084876875641</v>
+        <v>16.45405195719809</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07732618430198204</v>
+        <v>0.07716872202253645</v>
       </c>
       <c r="C15">
-        <v>5376.19292711199</v>
+        <v>5388.149764059744</v>
       </c>
       <c r="D15">
-        <v>5511.571902707957</v>
+        <v>5523.528739655711</v>
       </c>
       <c r="E15">
         <v>-1564.759298219165</v>
@@ -2517,37 +2517,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M15">
-        <v>42.27400303831151</v>
+        <v>41.12925247247715</v>
       </c>
       <c r="N15">
-        <v>582.4117112474026</v>
+        <v>583.5564618132371</v>
       </c>
       <c r="O15">
-        <v>145.2534807851022</v>
+        <v>145.5389815762213</v>
       </c>
       <c r="P15">
-        <v>437.1582304623004</v>
+        <v>438.0174802370158</v>
       </c>
       <c r="Q15">
-        <v>506.7582304623004</v>
+        <v>507.6174802370158</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08308207092181844</v>
+        <v>0.08305810186498444</v>
       </c>
       <c r="T15">
         <v>0.8604642463044906</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.2494</v>
       </c>
       <c r="W15">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.77706555775148</v>
+        <v>15.18835565279824</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07717263998447055</v>
+        <v>0.07700472305529639</v>
       </c>
       <c r="C16">
-        <v>5326.608307228436</v>
+        <v>5339.536117585702</v>
       </c>
       <c r="D16">
-        <v>5524.885665562555</v>
+        <v>5537.81347591982</v>
       </c>
       <c r="E16">
         <v>-1501.860915481014</v>
@@ -2599,37 +2599,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M16">
-        <v>45.52584942587394</v>
+        <v>44.29304112420616</v>
       </c>
       <c r="N16">
-        <v>579.1598648598402</v>
+        <v>580.392673161508</v>
       </c>
       <c r="O16">
-        <v>144.4424702960441</v>
+        <v>144.7499326864801</v>
       </c>
       <c r="P16">
-        <v>434.7173945637961</v>
+        <v>435.6427404750279</v>
       </c>
       <c r="Q16">
-        <v>504.3173945637961</v>
+        <v>505.242740475028</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08341836881915179</v>
+        <v>0.08339418355267023</v>
       </c>
       <c r="T16">
         <v>0.8682259480986197</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.72156087505494</v>
+        <v>14.10347310616979</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07701909566695905</v>
+        <v>0.07684072408805633</v>
       </c>
       <c r="C17">
-        <v>5277.088164594528</v>
+        <v>5290.996547950519</v>
       </c>
       <c r="D17">
-        <v>5538.263905666798</v>
+        <v>5552.172289022788</v>
       </c>
       <c r="E17">
         <v>-1438.962532742863</v>
@@ -2681,37 +2681,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M17">
-        <v>48.77769581343635</v>
+        <v>47.45682977593517</v>
       </c>
       <c r="N17">
-        <v>575.9080184722778</v>
+        <v>577.228884509779</v>
       </c>
       <c r="O17">
-        <v>143.6314598069861</v>
+        <v>143.9608837967389</v>
       </c>
       <c r="P17">
-        <v>432.2765586652918</v>
+        <v>433.2680007130401</v>
       </c>
       <c r="Q17">
-        <v>501.8765586652918</v>
+        <v>502.8680007130401</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08376257960818712</v>
+        <v>0.08373817304477216</v>
       </c>
       <c r="T17">
         <v>0.8761702781702577</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.2494</v>
       </c>
       <c r="W17">
-        <v>0.03880602</v>
+        <v>0.03775517999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.80679015005128</v>
+        <v>13.16324156575847</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07699765694944755</v>
+        <v>0.07685686912081628</v>
       </c>
       <c r="C18">
-        <v>5216.062883088392</v>
+        <v>5226.681294811111</v>
       </c>
       <c r="D18">
-        <v>5540.137006898813</v>
+        <v>5550.755418621532</v>
       </c>
       <c r="E18">
         <v>-1376.064150004711</v>
@@ -2763,37 +2763,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M18">
-        <v>53.13655373719024</v>
+        <v>52.13017961337982</v>
       </c>
       <c r="N18">
-        <v>571.549160548524</v>
+        <v>572.5555346723344</v>
       </c>
       <c r="O18">
-        <v>142.5443606408019</v>
+        <v>142.7953503472802</v>
       </c>
       <c r="P18">
-        <v>429.0047999077221</v>
+        <v>429.7601843250542</v>
       </c>
       <c r="Q18">
-        <v>498.6047999077222</v>
+        <v>499.3601843250542</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08411498589219946</v>
+        <v>0.08409035276287652</v>
       </c>
       <c r="T18">
         <v>0.8843037589578872</v>
       </c>
       <c r="U18">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.2494</v>
       </c>
       <c r="W18">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.75623314555489</v>
+        <v>11.98318745338413</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07685236923193603</v>
+        <v>0.07670412915357622</v>
       </c>
       <c r="C19">
-        <v>5165.891755758119</v>
+        <v>5177.216214981912</v>
       </c>
       <c r="D19">
-        <v>5552.864262306691</v>
+        <v>5564.188721530485</v>
       </c>
       <c r="E19">
         <v>-1313.16576726656</v>
@@ -2845,37 +2845,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M19">
-        <v>56.45758834576463</v>
+        <v>55.38831583921605</v>
       </c>
       <c r="N19">
-        <v>568.2281259399496</v>
+        <v>569.2973984464982</v>
       </c>
       <c r="O19">
-        <v>141.7160946094234</v>
+        <v>141.9827711725567</v>
       </c>
       <c r="P19">
-        <v>426.5120313305262</v>
+        <v>427.3146272739415</v>
       </c>
       <c r="Q19">
-        <v>496.1120313305262</v>
+        <v>496.9146272739415</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08447588389389885</v>
+        <v>0.08445101873924846</v>
       </c>
       <c r="T19">
         <v>0.8926332272343753</v>
       </c>
       <c r="U19">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.06469001934578</v>
+        <v>11.2782940737733</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07670708151442454</v>
+        <v>0.07655138918633615</v>
       </c>
       <c r="C20">
-        <v>5115.779239255517</v>
+        <v>5127.816312371332</v>
       </c>
       <c r="D20">
-        <v>5565.650128542241</v>
+        <v>5577.687201658056</v>
       </c>
       <c r="E20">
         <v>-1250.267384528409</v>
@@ -2927,37 +2927,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M20">
-        <v>59.77862295433901</v>
+        <v>58.64645206505229</v>
       </c>
       <c r="N20">
-        <v>564.9070913313752</v>
+        <v>566.039262220662</v>
       </c>
       <c r="O20">
-        <v>140.887828578045</v>
+        <v>141.1701919978331</v>
       </c>
       <c r="P20">
-        <v>424.0192627533303</v>
+        <v>424.8690702228289</v>
       </c>
       <c r="Q20">
-        <v>493.6192627533303</v>
+        <v>494.4690702228289</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08484558428588358</v>
+        <v>0.08482048144675139</v>
       </c>
       <c r="T20">
         <v>0.9011658532737044</v>
       </c>
       <c r="U20">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.2494</v>
       </c>
       <c r="W20">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.44998501827101</v>
+        <v>10.6517221807859</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07656179379691305</v>
+        <v>0.07639864921909609</v>
       </c>
       <c r="C21">
-        <v>5065.725739381818</v>
+        <v>5078.482062484225</v>
       </c>
       <c r="D21">
-        <v>5578.495011406693</v>
+        <v>5591.2513345091</v>
       </c>
       <c r="E21">
         <v>-1187.369001790257</v>
@@ -3009,37 +3009,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M21">
-        <v>63.09965756291341</v>
+        <v>61.90458829088853</v>
       </c>
       <c r="N21">
-        <v>561.5860567228008</v>
+        <v>562.7811259948256</v>
       </c>
       <c r="O21">
-        <v>140.0595625466665</v>
+        <v>140.3576128231095</v>
       </c>
       <c r="P21">
-        <v>421.5264941761343</v>
+        <v>422.4235131717161</v>
       </c>
       <c r="Q21">
-        <v>491.1264941761343</v>
+        <v>492.0235131717161</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.0852244130826087</v>
+        <v>0.08519906669024208</v>
       </c>
       <c r="T21">
         <v>0.9099091614374614</v>
       </c>
       <c r="U21">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.899985806783061</v>
+        <v>10.09110522390243</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07674677007940155</v>
+        <v>0.07650111325185602</v>
       </c>
       <c r="C22">
-        <v>4986.483888924369</v>
+        <v>5006.477049120947</v>
       </c>
       <c r="D22">
-        <v>5562.151543687395</v>
+        <v>5582.144703883974</v>
       </c>
       <c r="E22">
         <v>-1124.470619052106</v>
@@ -3091,37 +3091,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M22">
-        <v>69.18822101196646</v>
+        <v>67.30126952982192</v>
       </c>
       <c r="N22">
-        <v>555.4974932737478</v>
+        <v>557.3844447558922</v>
       </c>
       <c r="O22">
-        <v>138.5410748224727</v>
+        <v>139.0116805221195</v>
       </c>
       <c r="P22">
-        <v>416.9564184512751</v>
+        <v>418.3727642337727</v>
       </c>
       <c r="Q22">
-        <v>486.5564184512751</v>
+        <v>487.9727642337728</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08561271259925193</v>
+        <v>0.08558711656482003</v>
       </c>
       <c r="T22">
         <v>0.9188710523053125</v>
       </c>
       <c r="U22">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.2494</v>
       </c>
       <c r="W22">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.028787055786152</v>
+        <v>9.281930618097912</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07661799556189006</v>
+        <v>0.07636113348461597</v>
       </c>
       <c r="C23">
-        <v>4934.953152311886</v>
+        <v>4956.02699455525</v>
       </c>
       <c r="D23">
-        <v>5573.519189813063</v>
+        <v>5594.593032056428</v>
       </c>
       <c r="E23">
         <v>-1061.572236313955</v>
@@ -3173,37 +3173,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M23">
-        <v>72.64763206256478</v>
+        <v>70.66633300631301</v>
       </c>
       <c r="N23">
-        <v>552.0380822231494</v>
+        <v>554.0193812794012</v>
       </c>
       <c r="O23">
-        <v>137.6782977064535</v>
+        <v>138.1724336910827</v>
       </c>
       <c r="P23">
-        <v>414.359784516696</v>
+        <v>415.8469475883185</v>
       </c>
       <c r="Q23">
-        <v>483.959784516696</v>
+        <v>485.4469475883185</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.08601084248340513</v>
+        <v>0.08598499048685565</v>
       </c>
       <c r="T23">
         <v>0.9280598264862736</v>
       </c>
       <c r="U23">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.2494</v>
       </c>
       <c r="W23">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.598844815034431</v>
+        <v>8.839933921998012</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07648922104437854</v>
+        <v>0.07622115371737591</v>
       </c>
       <c r="C24">
-        <v>4883.468976106304</v>
+        <v>4905.63258427026</v>
       </c>
       <c r="D24">
-        <v>5584.933396345633</v>
+        <v>5607.097004509589</v>
       </c>
       <c r="E24">
         <v>-998.6738535758034</v>
@@ -3255,37 +3255,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M24">
-        <v>76.1070431131631</v>
+        <v>74.03139648280411</v>
       </c>
       <c r="N24">
-        <v>548.5786711725511</v>
+        <v>550.6543178029101</v>
       </c>
       <c r="O24">
-        <v>136.8155205904343</v>
+        <v>137.3331868600458</v>
       </c>
       <c r="P24">
-        <v>411.7631505821169</v>
+        <v>413.3211309428643</v>
       </c>
       <c r="Q24">
-        <v>481.3631505821169</v>
+        <v>482.9211309428644</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.08641918082612633</v>
+        <v>0.08639306630432808</v>
       </c>
       <c r="T24">
         <v>0.9374842102616183</v>
       </c>
       <c r="U24">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.207988232532866</v>
+        <v>8.438118743725376</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07636044652686703</v>
+        <v>0.07608117395013583</v>
       </c>
       <c r="C25">
-        <v>4832.03164695275</v>
+        <v>4855.294192198324</v>
       </c>
       <c r="D25">
-        <v>5596.39444993023</v>
+        <v>5619.656995175804</v>
       </c>
       <c r="E25">
         <v>-935.7754708376522</v>
@@ -3337,37 +3337,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M25">
-        <v>79.56645416376142</v>
+        <v>77.3964599592952</v>
       </c>
       <c r="N25">
-        <v>545.1192601219527</v>
+        <v>547.289254326419</v>
       </c>
       <c r="O25">
-        <v>135.952743474415</v>
+        <v>136.4939400290089</v>
       </c>
       <c r="P25">
-        <v>409.1665166475377</v>
+        <v>410.7953142974101</v>
       </c>
       <c r="Q25">
-        <v>478.7665166475377</v>
+        <v>480.3953142974102</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.08683812535956759</v>
+        <v>0.0868117414936829</v>
       </c>
       <c r="T25">
         <v>0.947153383225933</v>
       </c>
       <c r="U25">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.2494</v>
       </c>
       <c r="W25">
-        <v>0.04128299999999999</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.851119178944479</v>
+        <v>8.071244015737317</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07650188800935555</v>
+        <v>0.07594119418289577</v>
       </c>
       <c r="C26">
-        <v>4756.547374171546</v>
+        <v>4805.012195629765</v>
       </c>
       <c r="D26">
-        <v>5583.808559887178</v>
+        <v>5632.273381345397</v>
       </c>
       <c r="E26">
         <v>-872.877088099501</v>
@@ -3419,45 +3419,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M26">
-        <v>85.29020699293319</v>
+        <v>80.76152343578629</v>
       </c>
       <c r="N26">
-        <v>539.395507292781</v>
+        <v>543.9241908499279</v>
       </c>
       <c r="O26">
-        <v>134.5252395188196</v>
+        <v>135.654693197972</v>
       </c>
       <c r="P26">
-        <v>404.8702677739614</v>
+        <v>408.2694976519558</v>
       </c>
       <c r="Q26">
-        <v>474.4702677739614</v>
+        <v>477.8694976519558</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.08726809474915202</v>
+        <v>0.08724143445117864</v>
       </c>
       <c r="T26">
         <v>0.9570770081103613</v>
       </c>
       <c r="U26">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.0424089</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.324237287142158</v>
+        <v>7.734942181748262</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07638437249184402</v>
+        <v>0.0759513344156557</v>
       </c>
       <c r="C27">
-        <v>4704.101891393424</v>
+        <v>4741.197970116047</v>
       </c>
       <c r="D27">
-        <v>5594.261459847206</v>
+        <v>5631.35753856983</v>
       </c>
       <c r="E27">
         <v>-809.9787053613495</v>
@@ -3501,37 +3501,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M27">
-        <v>88.84396561763874</v>
+        <v>85.38455456704042</v>
       </c>
       <c r="N27">
-        <v>535.8417486680754</v>
+        <v>539.3011597186737</v>
       </c>
       <c r="O27">
-        <v>133.638932117818</v>
+        <v>134.5017092338372</v>
       </c>
       <c r="P27">
-        <v>402.2028165502574</v>
+        <v>404.7994504848365</v>
       </c>
       <c r="Q27">
-        <v>471.8028165502574</v>
+        <v>474.3994504848365</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.08770952998912537</v>
+        <v>0.08768258588754094</v>
       </c>
       <c r="T27">
         <v>0.9672652629917076</v>
       </c>
       <c r="U27">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.2494</v>
       </c>
       <c r="W27">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.031267795656472</v>
+        <v>7.316144207266863</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07626685697433253</v>
+        <v>0.07581735944841562</v>
       </c>
       <c r="C28">
-        <v>4651.695617710945</v>
+        <v>4690.423982243657</v>
       </c>
       <c r="D28">
-        <v>5604.753568902879</v>
+        <v>5643.481933435591</v>
       </c>
       <c r="E28">
         <v>-747.0803226231981</v>
@@ -3583,37 +3583,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M28">
-        <v>92.3977242423443</v>
+        <v>88.79993674972205</v>
       </c>
       <c r="N28">
-        <v>532.2879900433699</v>
+        <v>535.8857775359921</v>
       </c>
       <c r="O28">
-        <v>132.7526247168165</v>
+        <v>133.6499129174765</v>
       </c>
       <c r="P28">
-        <v>399.5353653265534</v>
+        <v>402.2358646185157</v>
       </c>
       <c r="Q28">
-        <v>469.1353653265534</v>
+        <v>471.8358646185157</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08816289591126018</v>
+        <v>0.08813566033569681</v>
       </c>
       <c r="T28">
         <v>0.9777288761130905</v>
       </c>
       <c r="U28">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.2494</v>
       </c>
       <c r="W28">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.760834418900454</v>
+        <v>7.034754045448906</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07614934145682103</v>
+        <v>0.07568338448117558</v>
       </c>
       <c r="C29">
-        <v>4599.328774150135</v>
+        <v>4639.702315016127</v>
       </c>
       <c r="D29">
-        <v>5615.285108080221</v>
+        <v>5655.658648946212</v>
       </c>
       <c r="E29">
         <v>-684.1819398850469</v>
@@ -3665,37 +3665,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M29">
-        <v>95.95148286704985</v>
+        <v>92.21531893240366</v>
       </c>
       <c r="N29">
-        <v>528.7342314186643</v>
+        <v>532.4703953533106</v>
       </c>
       <c r="O29">
-        <v>131.8663173158149</v>
+        <v>132.7981166011157</v>
       </c>
       <c r="P29">
-        <v>396.8679141028495</v>
+        <v>399.6722787521949</v>
       </c>
       <c r="Q29">
-        <v>466.4679141028495</v>
+        <v>469.2722787521949</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08862868281756306</v>
+        <v>0.0886011477824323</v>
       </c>
       <c r="T29">
         <v>0.9884791635665657</v>
       </c>
       <c r="U29">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.510433144126362</v>
+        <v>6.774207599321169</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07603182593930953</v>
+        <v>0.07554940951393552</v>
       </c>
       <c r="C30">
-        <v>4547.001583401408</v>
+        <v>4589.033307836275</v>
       </c>
       <c r="D30">
-        <v>5625.856300069646</v>
+        <v>5667.888024504511</v>
       </c>
       <c r="E30">
         <v>-621.2835571468954</v>
@@ -3747,37 +3747,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M30">
-        <v>99.5052414917554</v>
+        <v>95.63070111508527</v>
       </c>
       <c r="N30">
-        <v>525.1804727939588</v>
+        <v>529.055013170629</v>
       </c>
       <c r="O30">
-        <v>130.9800099148133</v>
+        <v>131.9463202847549</v>
       </c>
       <c r="P30">
-        <v>394.2004628791454</v>
+        <v>397.1086928858741</v>
       </c>
       <c r="Q30">
-        <v>463.8004628791455</v>
+        <v>466.7086928858741</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08910740824904101</v>
+        <v>0.08907956543602155</v>
       </c>
       <c r="T30">
         <v>0.9995280701159711</v>
       </c>
       <c r="U30">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.2494</v>
       </c>
       <c r="W30">
-        <v>0.0424089</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.277917674693279</v>
+        <v>6.532271613631129</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07621905402179802</v>
+        <v>0.07541543454669544</v>
       </c>
       <c r="C31">
-        <v>4467.279718132223</v>
+        <v>4538.417303048869</v>
       </c>
       <c r="D31">
-        <v>5609.032817538611</v>
+        <v>5680.170402455257</v>
       </c>
       <c r="E31">
         <v>-558.3851744087444</v>
@@ -3829,45 +3829,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M31">
-        <v>105.6126744556299</v>
+        <v>99.04608329776688</v>
       </c>
       <c r="N31">
-        <v>519.0730398300843</v>
+        <v>525.6396309879473</v>
       </c>
       <c r="O31">
-        <v>129.4568161336231</v>
+        <v>131.094523968394</v>
       </c>
       <c r="P31">
-        <v>389.6162236964612</v>
+        <v>394.5451070195533</v>
       </c>
       <c r="Q31">
-        <v>459.2162236964613</v>
+        <v>464.1451070195533</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08959961890394089</v>
+        <v>0.08957145964323303</v>
       </c>
       <c r="T31">
         <v>1.010888213469585</v>
       </c>
       <c r="U31">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.2494</v>
       </c>
       <c r="W31">
-        <v>0.04345974</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>5.914874493100332</v>
+        <v>6.307020868333503</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07611204690428651</v>
+        <v>0.07550663957945539</v>
       </c>
       <c r="C32">
-        <v>4413.984178071036</v>
+        <v>4467.151771420777</v>
       </c>
       <c r="D32">
-        <v>5618.635660215576</v>
+        <v>5671.803253565316</v>
       </c>
       <c r="E32">
         <v>-495.486791670593</v>
@@ -3911,37 +3911,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M32">
-        <v>109.2544908161688</v>
+        <v>104.348416962593</v>
       </c>
       <c r="N32">
-        <v>515.4312234695453</v>
+        <v>520.3372973231212</v>
       </c>
       <c r="O32">
-        <v>128.5485471333046</v>
+        <v>129.7721219523864</v>
       </c>
       <c r="P32">
-        <v>386.8826763362407</v>
+        <v>390.5651753707348</v>
       </c>
       <c r="Q32">
-        <v>456.4826763362407</v>
+        <v>460.1651753707348</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09010589272040932</v>
+        <v>0.09007740797065056</v>
       </c>
       <c r="T32">
         <v>1.022572932347588</v>
       </c>
       <c r="U32">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.2494</v>
       </c>
       <c r="W32">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.717712009996988</v>
+        <v>5.986537529454352</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07600503978677502</v>
+        <v>0.07538017061221532</v>
       </c>
       <c r="C33">
-        <v>4360.721575143768</v>
+        <v>4415.862272142615</v>
       </c>
       <c r="D33">
-        <v>5628.271440026459</v>
+        <v>5683.412137025306</v>
       </c>
       <c r="E33">
         <v>-432.5884089324416</v>
@@ -3993,37 +3993,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M33">
-        <v>112.8963071767078</v>
+        <v>107.8266975280128</v>
       </c>
       <c r="N33">
-        <v>511.7894071090064</v>
+        <v>516.8590167577014</v>
       </c>
       <c r="O33">
-        <v>127.6402781329862</v>
+        <v>128.9046387793707</v>
       </c>
       <c r="P33">
-        <v>384.1491289760202</v>
+        <v>387.9543779783306</v>
       </c>
       <c r="Q33">
-        <v>453.7491289760202</v>
+        <v>457.5543779783306</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09062684114025367</v>
+        <v>0.09059802146697873</v>
       </c>
       <c r="T33">
         <v>1.034596338729301</v>
       </c>
       <c r="U33">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.2494</v>
       </c>
       <c r="W33">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.533269687093859</v>
+        <v>5.793423415600985</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07589803266926351</v>
+        <v>0.07525370164497526</v>
       </c>
       <c r="C34">
-        <v>4307.492079099919</v>
+        <v>4364.620391785776</v>
       </c>
       <c r="D34">
-        <v>5637.940326720761</v>
+        <v>5695.068639406618</v>
       </c>
       <c r="E34">
         <v>-369.6900261942901</v>
@@ -4075,37 +4075,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M34">
-        <v>116.5381235372468</v>
+        <v>111.3049780934326</v>
       </c>
       <c r="N34">
-        <v>508.1475907484675</v>
+        <v>513.3807361922816</v>
       </c>
       <c r="O34">
-        <v>126.7320091326678</v>
+        <v>128.037155606355</v>
       </c>
       <c r="P34">
-        <v>381.4155816157997</v>
+        <v>385.3435805859265</v>
       </c>
       <c r="Q34">
-        <v>451.0155816157997</v>
+        <v>454.9435805859266</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09116311157244636</v>
+        <v>0.09113394712496362</v>
       </c>
       <c r="T34">
         <v>1.046973374710476</v>
       </c>
       <c r="U34">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.2494</v>
       </c>
       <c r="W34">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.360355009372176</v>
+        <v>5.612378933863453</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07579102555175202</v>
+        <v>0.0751272326777352</v>
       </c>
       <c r="C35">
-        <v>4254.29586085745</v>
+        <v>4313.426423947218</v>
       </c>
       <c r="D35">
-        <v>5647.642491216444</v>
+        <v>5706.773054306211</v>
       </c>
       <c r="E35">
         <v>-306.7916434561389</v>
@@ -4157,37 +4157,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M35">
-        <v>120.1799398977857</v>
+        <v>114.7832586588523</v>
       </c>
       <c r="N35">
-        <v>504.5057743879285</v>
+        <v>509.9024556268619</v>
       </c>
       <c r="O35">
-        <v>125.8237401323494</v>
+        <v>127.1696724333394</v>
       </c>
       <c r="P35">
-        <v>378.6820342555791</v>
+        <v>382.7327831935225</v>
       </c>
       <c r="Q35">
-        <v>448.2820342555791</v>
+        <v>452.3327831935225</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09171539007724183</v>
+        <v>0.09168587056378388</v>
       </c>
       <c r="T35">
         <v>1.059719874452284</v>
       </c>
       <c r="U35">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.2494</v>
       </c>
       <c r="W35">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.19792000908817</v>
+        <v>5.442306844958501</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07568401843424051</v>
+        <v>0.07500076371049513</v>
       </c>
       <c r="C36">
-        <v>4201.133092512869</v>
+        <v>4262.280664642453</v>
       </c>
       <c r="D36">
-        <v>5657.378105610013</v>
+        <v>5718.525677739598</v>
       </c>
       <c r="E36">
         <v>-243.8932607179877</v>
@@ -4239,37 +4239,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M36">
-        <v>123.8217562583247</v>
+        <v>118.2615392242721</v>
       </c>
       <c r="N36">
-        <v>500.8639580273895</v>
+        <v>506.4241750614421</v>
       </c>
       <c r="O36">
-        <v>124.9154711320309</v>
+        <v>126.3021892603237</v>
       </c>
       <c r="P36">
-        <v>375.9484868953585</v>
+        <v>380.1219858011185</v>
       </c>
       <c r="Q36">
-        <v>445.5484868953586</v>
+        <v>449.7219858011185</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09228440429430382</v>
+        <v>0.09225451895529566</v>
       </c>
       <c r="T36">
         <v>1.072852631762024</v>
       </c>
       <c r="U36">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.2494</v>
       </c>
       <c r="W36">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.045040008820872</v>
+        <v>5.282238996577369</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07557701131672902</v>
+        <v>0.07487429474325506</v>
       </c>
       <c r="C37">
-        <v>4148.003947351389</v>
+        <v>4211.183412330508</v>
       </c>
       <c r="D37">
-        <v>5667.147343186685</v>
+        <v>5730.326808165804</v>
       </c>
       <c r="E37">
         <v>-180.994877979836</v>
@@ -4321,37 +4321,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M37">
-        <v>127.4635726188637</v>
+        <v>121.7398197896919</v>
       </c>
       <c r="N37">
-        <v>497.2221416668505</v>
+        <v>502.9458944960223</v>
       </c>
       <c r="O37">
-        <v>124.0072021317125</v>
+        <v>125.434706087308</v>
       </c>
       <c r="P37">
-        <v>373.214939535138</v>
+        <v>377.5111884087143</v>
       </c>
       <c r="Q37">
-        <v>442.814939535138</v>
+        <v>447.1111884087143</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09287092664112158</v>
+        <v>0.09284066422039242</v>
       </c>
       <c r="T37">
         <v>1.086389473912065</v>
       </c>
       <c r="U37">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.2494</v>
       </c>
       <c r="W37">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.900896008568846</v>
+        <v>5.131317882389443</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07547000419921752</v>
+        <v>0.07474782577601502</v>
       </c>
       <c r="C38">
-        <v>4094.908599857227</v>
+        <v>4160.134967939174</v>
       </c>
       <c r="D38">
-        <v>5676.950378430674</v>
+        <v>5742.176746512621</v>
       </c>
       <c r="E38">
         <v>-118.0964952416853</v>
@@ -4403,37 +4403,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M38">
-        <v>131.1053889794026</v>
+        <v>125.2181003551116</v>
       </c>
       <c r="N38">
-        <v>493.5803253063116</v>
+        <v>499.4676139306026</v>
       </c>
       <c r="O38">
-        <v>123.0989331313941</v>
+        <v>124.5672229142923</v>
       </c>
       <c r="P38">
-        <v>370.4813921749175</v>
+        <v>374.9003910163103</v>
       </c>
       <c r="Q38">
-        <v>440.0813921749175</v>
+        <v>444.5003910163103</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09347577781127737</v>
+        <v>0.09344512652502346</v>
       </c>
       <c r="T38">
         <v>1.100349342379294</v>
       </c>
       <c r="U38">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.2494</v>
       </c>
       <c r="W38">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.764760008330824</v>
+        <v>4.988781274545293</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07536299708170602</v>
+        <v>0.07462135680877495</v>
       </c>
       <c r="C39">
-        <v>4041.847225723979</v>
+        <v>4109.135634890607</v>
       </c>
       <c r="D39">
-        <v>5686.787387035578</v>
+        <v>5754.075796202205</v>
       </c>
       <c r="E39">
         <v>-55.19811250353359</v>
@@ -4485,37 +4485,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M39">
-        <v>134.7472053399416</v>
+        <v>128.6963809205314</v>
       </c>
       <c r="N39">
-        <v>489.9385089457726</v>
+        <v>495.9893333651828</v>
       </c>
       <c r="O39">
-        <v>122.1906641310757</v>
+        <v>123.6997397412766</v>
       </c>
       <c r="P39">
-        <v>367.7478448146969</v>
+        <v>372.2895936239062</v>
       </c>
       <c r="Q39">
-        <v>437.3478448146969</v>
+        <v>441.8895936239062</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09409983060588256</v>
+        <v>0.09406877810916658</v>
       </c>
       <c r="T39">
         <v>1.114752381274055</v>
       </c>
       <c r="U39">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.2494</v>
       </c>
       <c r="W39">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.635982710808368</v>
+        <v>4.85394934820623</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07525598996419451</v>
+        <v>0.07449488784153488</v>
       </c>
       <c r="C40">
-        <v>3988.820001865125</v>
+        <v>4058.185719127207</v>
       </c>
       <c r="D40">
-        <v>5696.658545914875</v>
+        <v>5766.024263176957</v>
       </c>
       <c r="E40">
         <v>7.700270234617619</v>
@@ -4567,37 +4567,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M40">
-        <v>138.3890217004805</v>
+        <v>132.1746614859512</v>
       </c>
       <c r="N40">
-        <v>486.2966925852337</v>
+        <v>492.511052799763</v>
       </c>
       <c r="O40">
-        <v>121.2823951307573</v>
+        <v>122.8322565682609</v>
       </c>
       <c r="P40">
-        <v>365.0142974544764</v>
+        <v>369.6787962315021</v>
       </c>
       <c r="Q40">
-        <v>434.6142974544764</v>
+        <v>439.2787962315021</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09474401413579761</v>
+        <v>0.09471254748634658</v>
       </c>
       <c r="T40">
         <v>1.129620034326711</v>
       </c>
       <c r="U40">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.2494</v>
       </c>
       <c r="W40">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.513983165787096</v>
+        <v>4.726213839042908</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07591009124668302</v>
+        <v>0.07436841887429482</v>
       </c>
       <c r="C41">
-        <v>3866.112157476053</v>
+        <v>4007.285529137847</v>
       </c>
       <c r="D41">
-        <v>5636.849084263955</v>
+        <v>5778.022455925749</v>
       </c>
       <c r="E41">
         <v>70.59865297276929</v>
@@ -4649,45 +4649,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M41">
-        <v>148.4087340706681</v>
+        <v>135.652942051371</v>
       </c>
       <c r="N41">
-        <v>476.2769802150461</v>
+        <v>489.0327722343432</v>
       </c>
       <c r="O41">
-        <v>118.7834788656325</v>
+        <v>121.9647733952452</v>
       </c>
       <c r="P41">
-        <v>357.4935013494136</v>
+        <v>367.067998839098</v>
       </c>
       <c r="Q41">
-        <v>427.0935013494137</v>
+        <v>436.667998839098</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.09540931843718528</v>
+        <v>0.09537742405622102</v>
       </c>
       <c r="T41">
         <v>1.14497515141388</v>
       </c>
       <c r="U41">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.04541129999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.209224734632238</v>
+        <v>4.605028868811038</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07582259972917151</v>
+        <v>0.07499254990705476</v>
       </c>
       <c r="C42">
-        <v>3811.140930359924</v>
+        <v>3885.655342294694</v>
       </c>
       <c r="D42">
-        <v>5644.776239885977</v>
+        <v>5719.290651820746</v>
       </c>
       <c r="E42">
         <v>133.4970357109205</v>
@@ -4731,37 +4731,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M42">
-        <v>152.2140862263262</v>
+        <v>145.4210608906059</v>
       </c>
       <c r="N42">
-        <v>472.471628059388</v>
+        <v>479.2646533951083</v>
       </c>
       <c r="O42">
-        <v>117.8344240380114</v>
+        <v>119.52860455674</v>
       </c>
       <c r="P42">
-        <v>354.6372040213766</v>
+        <v>359.7360488383683</v>
       </c>
       <c r="Q42">
-        <v>424.2372040213766</v>
+        <v>429.3360488383684</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.09609679954861919</v>
+        <v>0.09606446317842458</v>
       </c>
       <c r="T42">
         <v>1.160842105737288</v>
       </c>
       <c r="U42">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.2494</v>
       </c>
       <c r="W42">
-        <v>0.04541129999999999</v>
+        <v>0.04338468</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.103994116266433</v>
+        <v>4.295703183981301</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07573510821166002</v>
+        <v>0.07488484593981469</v>
       </c>
       <c r="C43">
-        <v>3756.192030715037</v>
+        <v>3832.806695828588</v>
       </c>
       <c r="D43">
-        <v>5652.725722979241</v>
+        <v>5729.340388092792</v>
       </c>
       <c r="E43">
         <v>196.3954184490717</v>
@@ -4813,37 +4813,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M43">
-        <v>156.0194383819843</v>
+        <v>149.056587412871</v>
       </c>
       <c r="N43">
-        <v>468.6662759037299</v>
+        <v>475.6291268728432</v>
       </c>
       <c r="O43">
-        <v>116.8853692103902</v>
+        <v>118.6219042420871</v>
       </c>
       <c r="P43">
-        <v>351.7809066933396</v>
+        <v>357.0072226307561</v>
       </c>
       <c r="Q43">
-        <v>421.3809066933396</v>
+        <v>426.6072226307561</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.09680758510450851</v>
+        <v>0.09677479176239778</v>
       </c>
       <c r="T43">
         <v>1.177246922919118</v>
       </c>
       <c r="U43">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.2494</v>
       </c>
       <c r="W43">
-        <v>0.04541129999999999</v>
+        <v>0.04338468</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.00389669879652</v>
+        <v>4.190929935591512</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07649879709414852</v>
+        <v>0.07477714197257462</v>
       </c>
       <c r="C44">
-        <v>3624.650918793993</v>
+        <v>3779.993429617277</v>
       </c>
       <c r="D44">
-        <v>5584.082993796348</v>
+        <v>5739.425504619632</v>
       </c>
       <c r="E44">
         <v>259.2938011872229</v>
@@ -4895,45 +4895,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M44">
-        <v>166.9574671401489</v>
+        <v>152.6921139351361</v>
       </c>
       <c r="N44">
-        <v>457.7282471455653</v>
+        <v>471.993600350578</v>
       </c>
       <c r="O44">
-        <v>114.157424838104</v>
+        <v>117.7152039274342</v>
       </c>
       <c r="P44">
-        <v>343.5708223074613</v>
+        <v>354.2783964231439</v>
       </c>
       <c r="Q44">
-        <v>413.1708223074613</v>
+        <v>423.8783964231439</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.0975428805071526</v>
+        <v>0.09750961443547349</v>
       </c>
       <c r="T44">
         <v>1.194217423452044</v>
       </c>
       <c r="U44">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.04743792</v>
+        <v>0.04338468</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.741585955908969</v>
+        <v>4.091145889506</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07643157177663701</v>
+        <v>0.07579909100533455</v>
       </c>
       <c r="C45">
-        <v>3567.727968898917</v>
+        <v>3622.808769490638</v>
       </c>
       <c r="D45">
-        <v>5590.058426639423</v>
+        <v>5645.139227231144</v>
       </c>
       <c r="E45">
         <v>322.1921839253741</v>
@@ -4977,37 +4977,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M45">
-        <v>170.9326449292001</v>
+        <v>165.7938470594931</v>
       </c>
       <c r="N45">
-        <v>453.7530693565142</v>
+        <v>458.8918672262212</v>
       </c>
       <c r="O45">
-        <v>113.1660154975146</v>
+        <v>114.4476316862196</v>
       </c>
       <c r="P45">
-        <v>340.5870538589995</v>
+        <v>344.4442355400016</v>
       </c>
       <c r="Q45">
-        <v>410.1870538589995</v>
+        <v>414.0442355400016</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.09830397574848598</v>
+        <v>0.09827022036023607</v>
       </c>
       <c r="T45">
         <v>1.21178338014402</v>
       </c>
       <c r="U45">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.2494</v>
       </c>
       <c r="W45">
-        <v>0.04743792</v>
+        <v>0.04601178</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.654572329027365</v>
+        <v>3.767846185881395</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07636434645912551</v>
+        <v>0.07571765803809451</v>
       </c>
       <c r="C46">
-        <v>3510.817821122576</v>
+        <v>3567.309754721043</v>
       </c>
       <c r="D46">
-        <v>5596.046661601235</v>
+        <v>5652.538595199701</v>
       </c>
       <c r="E46">
         <v>385.0905666635258</v>
@@ -5059,37 +5059,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M46">
-        <v>174.9078227182512</v>
+        <v>169.6495179213418</v>
       </c>
       <c r="N46">
-        <v>449.777891567463</v>
+        <v>455.0361963643725</v>
       </c>
       <c r="O46">
-        <v>112.1746061569253</v>
+        <v>113.4860273732745</v>
       </c>
       <c r="P46">
-        <v>337.6032854105377</v>
+        <v>341.550168991098</v>
       </c>
       <c r="Q46">
-        <v>407.2032854105377</v>
+        <v>411.150168991098</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.09909225296272411</v>
+        <v>0.0990579907823116</v>
       </c>
       <c r="T46">
         <v>1.229976692432139</v>
       </c>
       <c r="U46">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.04743792</v>
+        <v>0.04601178</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.571513867004015</v>
+        <v>3.682213318020453</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.077884640141614</v>
+        <v>0.07563622507085443</v>
       </c>
       <c r="C47">
-        <v>3315.55761118004</v>
+        <v>3511.830162857687</v>
       </c>
       <c r="D47">
-        <v>5463.68483439685</v>
+        <v>5659.957386074497</v>
       </c>
       <c r="E47">
         <v>447.988949401677</v>
@@ -5141,45 +5141,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M47">
-        <v>192.1860084564214</v>
+        <v>173.5051887831904</v>
       </c>
       <c r="N47">
-        <v>432.4997058292928</v>
+        <v>451.1805255025238</v>
       </c>
       <c r="O47">
-        <v>107.8654266338256</v>
+        <v>112.5244230603294</v>
       </c>
       <c r="P47">
-        <v>324.6342791954672</v>
+        <v>338.6561024421943</v>
       </c>
       <c r="Q47">
-        <v>394.2342791954672</v>
+        <v>408.2561024421943</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.09990919480293456</v>
+        <v>0.09987440740155351</v>
       </c>
       <c r="T47">
         <v>1.248831579712552</v>
       </c>
       <c r="U47">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.2494</v>
       </c>
       <c r="W47">
-        <v>0.05096574</v>
+        <v>0.04601178</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.250422438672809</v>
+        <v>3.600386355397777</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07785269302410251</v>
+        <v>0.07555479210361438</v>
       </c>
       <c r="C48">
-        <v>3255.376212982425</v>
+        <v>3456.370070477053</v>
       </c>
       <c r="D48">
-        <v>5466.401818937386</v>
+        <v>5667.395676432014</v>
       </c>
       <c r="E48">
         <v>510.8873321398282</v>
@@ -5223,45 +5223,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M48">
-        <v>196.4568086443418</v>
+        <v>177.3608596450391</v>
       </c>
       <c r="N48">
-        <v>428.2289056413724</v>
+        <v>447.3248546406751</v>
       </c>
       <c r="O48">
-        <v>106.8002890669583</v>
+        <v>111.5628187473844</v>
       </c>
       <c r="P48">
-        <v>321.4286165744141</v>
+        <v>335.7620358932907</v>
       </c>
       <c r="Q48">
-        <v>391.0286165744141</v>
+        <v>405.3620358932907</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.100756393748338</v>
+        <v>0.10072106167336</v>
       </c>
       <c r="T48">
         <v>1.2683847961515</v>
       </c>
       <c r="U48">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V48">
         <v>0.2494</v>
       </c>
       <c r="W48">
-        <v>0.05096574</v>
+        <v>0.04601178</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.179761081310357</v>
+        <v>3.522117086802173</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07782074590659101</v>
+        <v>0.0764611487363743</v>
       </c>
       <c r="C49">
-        <v>3195.197518336707</v>
+        <v>3311.769085054228</v>
       </c>
       <c r="D49">
-        <v>5469.121507029819</v>
+        <v>5585.69307374734</v>
       </c>
       <c r="E49">
         <v>573.7857148779799</v>
@@ -5305,37 +5305,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M49">
-        <v>200.7276088322623</v>
+        <v>189.4939576752285</v>
       </c>
       <c r="N49">
-        <v>423.9581054534518</v>
+        <v>435.1917566104856</v>
       </c>
       <c r="O49">
-        <v>105.7351515000909</v>
+        <v>108.5368240986551</v>
       </c>
       <c r="P49">
-        <v>318.222953953361</v>
+        <v>326.6549325118305</v>
       </c>
       <c r="Q49">
-        <v>387.822953953361</v>
+        <v>396.2549325118305</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.101635562465266</v>
+        <v>0.1015996651629704</v>
       </c>
       <c r="T49">
         <v>1.288675869814559</v>
       </c>
       <c r="U49">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.05096574</v>
+        <v>0.04811346</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.112106590218646</v>
+        <v>3.296599648609143</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.0777887987890795</v>
+        <v>0.07640073256913424</v>
       </c>
       <c r="C50">
-        <v>3135.021531280174</v>
+        <v>3254.243506585789</v>
       </c>
       <c r="D50">
-        <v>5471.843902711437</v>
+        <v>5591.065878017052</v>
       </c>
       <c r="E50">
         <v>636.6840976161307</v>
@@ -5387,37 +5387,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M50">
-        <v>204.9984090201828</v>
+        <v>193.525744008744</v>
       </c>
       <c r="N50">
-        <v>419.6873052655314</v>
+        <v>431.1599702769702</v>
       </c>
       <c r="O50">
-        <v>104.6700139332235</v>
+        <v>107.5312965870764</v>
       </c>
       <c r="P50">
-        <v>315.0172913323079</v>
+        <v>323.6286736898938</v>
       </c>
       <c r="Q50">
-        <v>384.6172913323079</v>
+        <v>393.2286736898938</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1025485453636144</v>
+        <v>0.1025120610944889</v>
       </c>
       <c r="T50">
         <v>1.309747369387735</v>
       </c>
       <c r="U50">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.2494</v>
       </c>
       <c r="W50">
-        <v>0.05096574</v>
+        <v>0.04811346</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.047271036255759</v>
+        <v>3.227920489263119</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.081177335871568</v>
+        <v>0.07634031640189419</v>
       </c>
       <c r="C51">
-        <v>2797.711180181017</v>
+        <v>3196.728274127728</v>
       </c>
       <c r="D51">
-        <v>5197.431934350432</v>
+        <v>5596.449028297143</v>
       </c>
       <c r="E51">
         <v>699.5824803542823</v>
@@ -5469,45 +5469,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M51">
-        <v>237.9320022218788</v>
+        <v>197.5575303422595</v>
       </c>
       <c r="N51">
-        <v>386.7537120638354</v>
+        <v>427.1281839434547</v>
       </c>
       <c r="O51">
-        <v>96.45637578872055</v>
+        <v>106.5257690754976</v>
       </c>
       <c r="P51">
-        <v>290.2973362751148</v>
+        <v>320.6024148679571</v>
       </c>
       <c r="Q51">
-        <v>359.8973362751149</v>
+        <v>390.2024148679571</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1034973315128784</v>
+        <v>0.1034602372586161</v>
       </c>
       <c r="T51">
         <v>1.331645202277507</v>
       </c>
       <c r="U51">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V51">
         <v>0.2494</v>
       </c>
       <c r="W51">
-        <v>0.05794631999999999</v>
+        <v>0.04811346</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.625480004590454</v>
+        <v>3.162044560910811</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.0812151945540565</v>
+        <v>0.07627990023465411</v>
       </c>
       <c r="C52">
-        <v>2731.902293813684</v>
+        <v>3139.223417592669</v>
       </c>
       <c r="D52">
-        <v>5194.52143072125</v>
+        <v>5601.842554500235</v>
       </c>
       <c r="E52">
         <v>762.4808630924335</v>
@@ -5551,45 +5551,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M52">
-        <v>242.7877573692641</v>
+        <v>201.589316675775</v>
       </c>
       <c r="N52">
-        <v>381.8979569164501</v>
+        <v>423.0963976099392</v>
       </c>
       <c r="O52">
-        <v>95.24535045496266</v>
+        <v>105.5202415639188</v>
       </c>
       <c r="P52">
-        <v>286.6526064614874</v>
+        <v>317.5761560460204</v>
       </c>
       <c r="Q52">
-        <v>356.2526064614875</v>
+        <v>387.1761560460204</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.104484069108113</v>
+        <v>0.1044463404693082</v>
       </c>
       <c r="T52">
         <v>1.354418948482869</v>
       </c>
       <c r="U52">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V52">
         <v>0.2494</v>
       </c>
       <c r="W52">
-        <v>0.05794631999999999</v>
+        <v>0.04811346</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.572970404498645</v>
+        <v>3.098803669692595</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.081253053236545</v>
+        <v>0.07621948406741405</v>
       </c>
       <c r="C53">
-        <v>2666.096665320798</v>
+        <v>3081.728967008647</v>
       </c>
       <c r="D53">
-        <v>5191.614184966515</v>
+        <v>5607.246486654364</v>
       </c>
       <c r="E53">
         <v>825.3792458305848</v>
@@ -5633,45 +5633,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M53">
-        <v>247.6435125166493</v>
+        <v>205.6211030092905</v>
       </c>
       <c r="N53">
-        <v>377.0422017690648</v>
+        <v>419.0646112764237</v>
       </c>
       <c r="O53">
-        <v>94.03432512120477</v>
+        <v>104.5147140523401</v>
       </c>
       <c r="P53">
-        <v>283.00787664786</v>
+        <v>314.5498972240836</v>
       </c>
       <c r="Q53">
-        <v>352.6078766478601</v>
+        <v>384.1498972240836</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1055110817072347</v>
+        <v>0.1054726927906409</v>
       </c>
       <c r="T53">
         <v>1.378122235349675</v>
       </c>
       <c r="U53">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.05794631999999999</v>
+        <v>0.04811346</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.522520004410436</v>
+        <v>3.038042813424113</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08312537831903349</v>
+        <v>0.079203501500174</v>
       </c>
       <c r="C54">
-        <v>2463.369412575382</v>
+        <v>2763.817637223286</v>
       </c>
       <c r="D54">
-        <v>5051.785314959251</v>
+        <v>5352.233539607155</v>
       </c>
       <c r="E54">
         <v>888.2776285687364</v>
@@ -5715,45 +5715,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M54">
-        <v>267.8716324052389</v>
+        <v>235.1644733814002</v>
       </c>
       <c r="N54">
-        <v>356.8140818804753</v>
+        <v>389.521240904314</v>
       </c>
       <c r="O54">
-        <v>88.98943202099055</v>
+        <v>97.14659748153592</v>
       </c>
       <c r="P54">
-        <v>267.8246498594848</v>
+        <v>292.3746434227781</v>
       </c>
       <c r="Q54">
-        <v>337.4246498594848</v>
+        <v>361.9746434227781</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1065808864979865</v>
+        <v>0.1065418097920292</v>
       </c>
       <c r="T54">
         <v>1.402813159169265</v>
       </c>
       <c r="U54">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.2494</v>
       </c>
       <c r="W54">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.332033850231231</v>
+        <v>2.656377918413599</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08319851520152199</v>
+        <v>0.07920163213293394</v>
       </c>
       <c r="C55">
-        <v>2395.161722822786</v>
+        <v>2701.071748670096</v>
       </c>
       <c r="D55">
-        <v>5046.476007944806</v>
+        <v>5352.386033792116</v>
       </c>
       <c r="E55">
         <v>951.1760113068876</v>
@@ -5797,45 +5797,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M55">
-        <v>273.0230099514935</v>
+        <v>239.6868671002733</v>
       </c>
       <c r="N55">
-        <v>351.6627043342207</v>
+        <v>384.9988471854409</v>
       </c>
       <c r="O55">
-        <v>87.70467846095465</v>
+        <v>96.01871248804898</v>
       </c>
       <c r="P55">
-        <v>263.9580258732661</v>
+        <v>288.9801346973919</v>
       </c>
       <c r="Q55">
-        <v>333.5580258732661</v>
+        <v>358.5801346973919</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1076962148968553</v>
+        <v>0.107656421133902</v>
       </c>
       <c r="T55">
         <v>1.428554760598199</v>
       </c>
       <c r="U55">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.2494</v>
       </c>
       <c r="W55">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.288033211547623</v>
+        <v>2.606257580330324</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08327165208401049</v>
+        <v>0.07919976276569386</v>
       </c>
       <c r="C56">
-        <v>2326.965181266173</v>
+        <v>2638.325868806789</v>
       </c>
       <c r="D56">
-        <v>5041.177849126344</v>
+        <v>5352.53853666696</v>
       </c>
       <c r="E56">
         <v>1014.074394045039</v>
@@ -5879,45 +5879,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M56">
-        <v>278.1743874977481</v>
+        <v>244.2092608191464</v>
       </c>
       <c r="N56">
-        <v>346.5113267879661</v>
+        <v>380.4764534665678</v>
       </c>
       <c r="O56">
-        <v>86.41992490091876</v>
+        <v>94.89082749456202</v>
       </c>
       <c r="P56">
-        <v>260.0914018870474</v>
+        <v>285.5856259720058</v>
       </c>
       <c r="Q56">
-        <v>329.6914018870474</v>
+        <v>355.1856259720058</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1088600358348054</v>
+        <v>0.1088194938384649</v>
       </c>
       <c r="T56">
         <v>1.455415562089259</v>
       </c>
       <c r="U56">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.2494</v>
       </c>
       <c r="W56">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.245662226148593</v>
+        <v>2.557993551064948</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08334478896649899</v>
+        <v>0.0791978933984538</v>
       </c>
       <c r="C57">
-        <v>2258.779752829797</v>
+        <v>2575.579997634105</v>
       </c>
       <c r="D57">
-        <v>5035.890803428119</v>
+        <v>5352.691048232428</v>
       </c>
       <c r="E57">
         <v>1076.972776783191</v>
@@ -5961,45 +5961,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M57">
-        <v>283.3257650440027</v>
+        <v>248.7316545380195</v>
       </c>
       <c r="N57">
-        <v>341.3599492417115</v>
+        <v>375.9540597476947</v>
       </c>
       <c r="O57">
-        <v>85.13517134088286</v>
+        <v>93.76294250107506</v>
       </c>
       <c r="P57">
-        <v>256.2247779008287</v>
+        <v>282.1911172466197</v>
       </c>
       <c r="Q57">
-        <v>325.8247779008287</v>
+        <v>351.7911172466197</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1100755821477755</v>
+        <v>0.1100342586632307</v>
       </c>
       <c r="T57">
         <v>1.483470176979923</v>
       </c>
       <c r="U57">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V57">
         <v>0.2494</v>
       </c>
       <c r="W57">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.204832003854982</v>
+        <v>2.511484577409221</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0834179258489875</v>
+        <v>0.08083533443121374</v>
       </c>
       <c r="C58">
-        <v>2190.605402584906</v>
+        <v>2382.340922967701</v>
       </c>
       <c r="D58">
-        <v>5030.61483592138</v>
+        <v>5222.350356304175</v>
       </c>
       <c r="E58">
         <v>1139.871159521342</v>
@@ -6043,37 +6043,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M58">
-        <v>288.4771425902572</v>
+        <v>266.9910550469048</v>
       </c>
       <c r="N58">
-        <v>336.208571695457</v>
+        <v>357.6946592388094</v>
       </c>
       <c r="O58">
-        <v>83.85041778084697</v>
+        <v>89.20904801415908</v>
       </c>
       <c r="P58">
-        <v>252.35815391461</v>
+        <v>268.4856112246504</v>
       </c>
       <c r="Q58">
-        <v>321.95815391461</v>
+        <v>338.0856112246504</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1113463805658807</v>
+        <v>0.1113042400709403</v>
       </c>
       <c r="T58">
         <v>1.512800001638345</v>
       </c>
       <c r="U58">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.2494</v>
       </c>
       <c r="W58">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.165460003786143</v>
+        <v>2.339725254750463</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.083491062731476</v>
+        <v>0.08086273846397368</v>
       </c>
       <c r="C59">
-        <v>2122.442095748972</v>
+        <v>2317.315157116817</v>
       </c>
       <c r="D59">
-        <v>5025.349911823598</v>
+        <v>5220.222973191443</v>
       </c>
       <c r="E59">
         <v>1202.769542259493</v>
@@ -6125,37 +6125,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M59">
-        <v>293.6285201365119</v>
+        <v>271.7587524584567</v>
       </c>
       <c r="N59">
-        <v>331.0571941492023</v>
+        <v>352.9269618272575</v>
       </c>
       <c r="O59">
-        <v>82.56566422081106</v>
+        <v>88.01998427971803</v>
       </c>
       <c r="P59">
-        <v>248.4915299283912</v>
+        <v>264.9069775475395</v>
       </c>
       <c r="Q59">
-        <v>318.0915299283913</v>
+        <v>334.5069775475395</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1126762858871535</v>
+        <v>0.1126332903813342</v>
       </c>
       <c r="T59">
         <v>1.543494004187856</v>
       </c>
       <c r="U59">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.2494</v>
       </c>
       <c r="W59">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.127469477403929</v>
+        <v>2.298677443263613</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.0835641996139645</v>
+        <v>0.0808901424967336</v>
       </c>
       <c r="C60">
-        <v>2054.289797684922</v>
+        <v>2252.291123787017</v>
       </c>
       <c r="D60">
-        <v>5020.095996497698</v>
+        <v>5218.097322599793</v>
       </c>
       <c r="E60">
         <v>1265.667924997644</v>
@@ -6207,37 +6207,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M60">
-        <v>298.7798976827664</v>
+        <v>276.5264498700085</v>
       </c>
       <c r="N60">
-        <v>325.9058166029478</v>
+        <v>348.1592644157057</v>
       </c>
       <c r="O60">
-        <v>81.28091066077519</v>
+        <v>86.83092054527701</v>
       </c>
       <c r="P60">
-        <v>244.6249059421726</v>
+        <v>261.3283438704287</v>
       </c>
       <c r="Q60">
-        <v>314.2249059421727</v>
+        <v>330.9283438704287</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1140695200332488</v>
+        <v>0.1140256288017467</v>
       </c>
       <c r="T60">
         <v>1.57564962590639</v>
       </c>
       <c r="U60">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.2494</v>
       </c>
       <c r="W60">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.090788969172828</v>
+        <v>2.259045073552171</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.083637336496453</v>
+        <v>0.08091754652949355</v>
       </c>
       <c r="C61">
-        <v>1986.14847390038</v>
+        <v>2187.26882086273</v>
       </c>
       <c r="D61">
-        <v>5014.853055451308</v>
+        <v>5215.973402413658</v>
       </c>
       <c r="E61">
         <v>1328.566307735795</v>
@@ -6289,37 +6289,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M61">
-        <v>303.931275229021</v>
+        <v>281.2941472815604</v>
       </c>
       <c r="N61">
-        <v>320.7544390566932</v>
+        <v>343.3915670041538</v>
       </c>
       <c r="O61">
-        <v>79.99615710073928</v>
+        <v>85.64185681083598</v>
       </c>
       <c r="P61">
-        <v>240.7582819559539</v>
+        <v>257.7497101933179</v>
       </c>
       <c r="Q61">
-        <v>310.3582819559539</v>
+        <v>327.3497101933179</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1155307168206171</v>
+        <v>0.1154858861694965</v>
       </c>
       <c r="T61">
         <v>1.609373814538025</v>
       </c>
       <c r="U61">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V61">
         <v>0.2494</v>
       </c>
       <c r="W61">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.055351868000407</v>
+        <v>2.22075617400044</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.0837104733789415</v>
+        <v>0.08094495056225348</v>
       </c>
       <c r="C62">
-        <v>1918.018090046919</v>
+        <v>2122.248246231846</v>
       </c>
       <c r="D62">
-        <v>5009.621054335998</v>
+        <v>5213.851210520925</v>
       </c>
       <c r="E62">
         <v>1391.464690473947</v>
@@ -6371,37 +6371,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M62">
-        <v>309.0826527752756</v>
+        <v>286.0618446931122</v>
       </c>
       <c r="N62">
-        <v>315.6030615104386</v>
+        <v>338.623869592602</v>
       </c>
       <c r="O62">
-        <v>78.7114035407034</v>
+        <v>84.45279307639494</v>
       </c>
       <c r="P62">
-        <v>236.8916579697352</v>
+        <v>254.1710765162071</v>
       </c>
       <c r="Q62">
-        <v>306.4916579697352</v>
+        <v>323.7710765162071</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1170649734473537</v>
+        <v>0.1170191564056337</v>
       </c>
       <c r="T62">
         <v>1.644784212601241</v>
       </c>
       <c r="U62">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
         <v>0.2494</v>
       </c>
       <c r="W62">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.021096003533734</v>
+        <v>2.183743571100432</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.09124682606142999</v>
+        <v>0.08097235459501342</v>
       </c>
       <c r="C63">
-        <v>1368.83231464824</v>
+        <v>2057.229397785675</v>
       </c>
       <c r="D63">
-        <v>4523.33366167547</v>
+        <v>5211.730744812905</v>
       </c>
       <c r="E63">
         <v>1454.363073212098</v>
@@ -6453,45 +6453,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M63">
-        <v>376.7738922780741</v>
+        <v>290.8295421046641</v>
       </c>
       <c r="N63">
-        <v>247.9118220076401</v>
+        <v>333.8561721810501</v>
       </c>
       <c r="O63">
-        <v>61.82920840870545</v>
+        <v>83.2637293419539</v>
       </c>
       <c r="P63">
-        <v>186.0826135989347</v>
+        <v>250.5924428390962</v>
       </c>
       <c r="Q63">
-        <v>255.6826135989347</v>
+        <v>320.1924428390962</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1186779099011026</v>
+        <v>0.1186310558846498</v>
       </c>
       <c r="T63">
         <v>1.682010528513852</v>
       </c>
       <c r="U63">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.2494</v>
       </c>
       <c r="W63">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.657985670155381</v>
+        <v>2.14794449616436</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.0914423107439185</v>
+        <v>0.08099975862777337</v>
       </c>
       <c r="C64">
-        <v>1294.573204494626</v>
+        <v>1992.212273418965</v>
       </c>
       <c r="D64">
-        <v>4511.972934260008</v>
+        <v>5209.612003184347</v>
       </c>
       <c r="E64">
         <v>1517.261455950249</v>
@@ -6535,45 +6535,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M64">
-        <v>382.9505134629605</v>
+        <v>295.597239516216</v>
       </c>
       <c r="N64">
-        <v>241.7352008227537</v>
+        <v>329.0884747694982</v>
       </c>
       <c r="O64">
-        <v>60.28875908519476</v>
+        <v>82.07466560751286</v>
       </c>
       <c r="P64">
-        <v>181.4464417375589</v>
+        <v>247.0138091619853</v>
       </c>
       <c r="Q64">
-        <v>251.0464417375589</v>
+        <v>316.6138091619854</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1203757377471539</v>
+        <v>0.120327792178351</v>
       </c>
       <c r="T64">
         <v>1.721196124211338</v>
       </c>
       <c r="U64">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.2494</v>
       </c>
       <c r="W64">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.631243965798037</v>
+        <v>2.113300230097193</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.09163779542640699</v>
+        <v>0.08102716266053331</v>
       </c>
       <c r="C65">
-        <v>1220.371018189164</v>
+        <v>1927.196871029885</v>
       </c>
       <c r="D65">
-        <v>4500.669130692697</v>
+        <v>5207.494983533418</v>
       </c>
       <c r="E65">
         <v>1580.159838688401</v>
@@ -6617,45 +6617,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M65">
-        <v>389.127134647847</v>
+        <v>300.3649369277679</v>
       </c>
       <c r="N65">
-        <v>235.5585796378672</v>
+        <v>324.3207773579463</v>
       </c>
       <c r="O65">
-        <v>58.74830976168408</v>
+        <v>80.88560187307182</v>
       </c>
       <c r="P65">
-        <v>176.8102698761831</v>
+        <v>243.4351754848745</v>
       </c>
       <c r="Q65">
-        <v>246.4102698761831</v>
+        <v>313.0351754848745</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1221653400713703</v>
+        <v>0.1221162439473873</v>
       </c>
       <c r="T65">
         <v>1.762499860216797</v>
       </c>
       <c r="U65">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.2494</v>
       </c>
       <c r="W65">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.605351204436163</v>
+        <v>2.079755782000412</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09183328010889549</v>
+        <v>0.08105456669329325</v>
       </c>
       <c r="C66">
-        <v>1146.225328968665</v>
+        <v>1862.183188520016</v>
       </c>
       <c r="D66">
-        <v>4489.42182421035</v>
+        <v>5205.379683761701</v>
       </c>
       <c r="E66">
         <v>1643.058221426552</v>
@@ -6699,45 +6699,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M66">
-        <v>395.3037558327335</v>
+        <v>305.1326343393197</v>
       </c>
       <c r="N66">
-        <v>229.3819584529807</v>
+        <v>319.5530799463945</v>
       </c>
       <c r="O66">
-        <v>57.20786043817339</v>
+        <v>79.69653813863079</v>
       </c>
       <c r="P66">
-        <v>172.1740980148073</v>
+        <v>239.8565418077637</v>
       </c>
       <c r="Q66">
-        <v>241.7740980148074</v>
+        <v>309.4565418077637</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1240543647469319</v>
+        <v>0.1240040541480368</v>
       </c>
       <c r="T66">
         <v>1.806098248222558</v>
       </c>
       <c r="U66">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
         <v>0.2494</v>
       </c>
       <c r="W66">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.580267591866848</v>
+        <v>2.047259597906655</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09202876479138397</v>
+        <v>0.08108197072605317</v>
       </c>
       <c r="C67">
-        <v>1072.135714325289</v>
+        <v>1797.171223794353</v>
       </c>
       <c r="D67">
-        <v>4478.230592305124</v>
+        <v>5203.266101774189</v>
       </c>
       <c r="E67">
         <v>1705.956604164704</v>
@@ -6781,45 +6781,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M67">
-        <v>401.48037701762</v>
+        <v>309.9003317508716</v>
       </c>
       <c r="N67">
-        <v>223.2053372680942</v>
+        <v>314.7853825348426</v>
       </c>
       <c r="O67">
-        <v>55.66741111466271</v>
+        <v>78.50747440418975</v>
       </c>
       <c r="P67">
-        <v>167.5379261534315</v>
+        <v>236.2779081306529</v>
       </c>
       <c r="Q67">
-        <v>237.1379261534316</v>
+        <v>305.8779081306529</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1260513336896685</v>
+        <v>0.1259997392172948</v>
       </c>
       <c r="T67">
         <v>1.852187972685792</v>
       </c>
       <c r="U67">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
         <v>0.2494</v>
       </c>
       <c r="W67">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.555955782761204</v>
+        <v>2.015763296400399</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09222424947387248</v>
+        <v>0.0881439979588131</v>
       </c>
       <c r="C68">
-        <v>998.1017559536213</v>
+        <v>1241.396018294735</v>
       </c>
       <c r="D68">
-        <v>4467.095016671608</v>
+        <v>4710.389279012722</v>
       </c>
       <c r="E68">
         <v>1768.854986902855</v>
@@ -6863,37 +6863,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M68">
-        <v>407.6569982025064</v>
+        <v>373.6163934646189</v>
       </c>
       <c r="N68">
-        <v>217.0287160832078</v>
+        <v>251.0693208210953</v>
       </c>
       <c r="O68">
-        <v>54.12696179115203</v>
+        <v>62.61668861278118</v>
       </c>
       <c r="P68">
-        <v>162.9017542920558</v>
+        <v>188.4526322083142</v>
       </c>
       <c r="Q68">
-        <v>232.5017542920558</v>
+        <v>258.0526322083142</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1281657713937426</v>
+        <v>0.1281128175259209</v>
       </c>
       <c r="T68">
         <v>1.900988857411568</v>
       </c>
       <c r="U68">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.2494</v>
       </c>
       <c r="W68">
-        <v>0.07370892</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.53238069514361</v>
+        <v>1.671997602923362</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09241973415636098</v>
+        <v>0.08827798719157305</v>
       </c>
       <c r="C69">
-        <v>924.1230396985684</v>
+        <v>1170.047185362212</v>
       </c>
       <c r="D69">
-        <v>4456.014683154707</v>
+        <v>4701.938828818351</v>
       </c>
       <c r="E69">
         <v>1831.753369641006</v>
@@ -6945,37 +6945,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M69">
-        <v>413.8336193873929</v>
+        <v>379.2772479110525</v>
       </c>
       <c r="N69">
-        <v>210.8520948983213</v>
+        <v>245.4084663746617</v>
       </c>
       <c r="O69">
-        <v>52.58651246764133</v>
+        <v>61.20487151384064</v>
       </c>
       <c r="P69">
-        <v>158.26558243068</v>
+        <v>184.2035948608211</v>
       </c>
       <c r="Q69">
-        <v>227.86558243068</v>
+        <v>253.8035948608211</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1304083568374576</v>
+        <v>0.130353961186585</v>
       </c>
       <c r="T69">
         <v>1.952747371514665</v>
       </c>
       <c r="U69">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.2494</v>
       </c>
       <c r="W69">
-        <v>0.07370892</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.50950934148475</v>
+        <v>1.647042414820028</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1295813062893428</v>
+        <v>0.08841197642433296</v>
       </c>
       <c r="C70">
-        <v>-566.6385078834082</v>
+        <v>1098.72861839022</v>
       </c>
       <c r="D70">
-        <v>3028.151518310882</v>
+        <v>4693.518644584509</v>
       </c>
       <c r="E70">
         <v>1894.651752379157</v>
@@ -7027,45 +7027,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M70">
-        <v>699.7319282853858</v>
+        <v>384.9381023574861</v>
       </c>
       <c r="N70">
-        <v>-75.04621399967164</v>
+        <v>239.7476119282281</v>
       </c>
       <c r="O70">
-        <v>-18.71652577151811</v>
+        <v>59.7930544149001</v>
       </c>
       <c r="P70">
-        <v>-56.32968822815353</v>
+        <v>179.954557513328</v>
       </c>
       <c r="Q70">
-        <v>13.27031177184649</v>
+        <v>249.5545575133281</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1346965021818331</v>
+        <v>0.1327351763260406</v>
       </c>
       <c r="T70">
-        <v>2.051717081634305</v>
+        <v>2.007740792749205</v>
       </c>
       <c r="U70">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V70">
-        <v>0.222651862584889</v>
+        <v>0.2494</v>
       </c>
       <c r="W70">
-        <v>0.1271741552811121</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8927500504606616</v>
+        <v>1.62282120283738</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1307593062893429</v>
+        <v>0.08854596565709291</v>
       </c>
       <c r="C71">
-        <v>-659.9863547583982</v>
+        <v>1027.440155069488</v>
       </c>
       <c r="D71">
-        <v>2997.702054174043</v>
+        <v>4685.12856400193</v>
       </c>
       <c r="E71">
         <v>1957.550135117309</v>
@@ -7109,45 +7109,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M71">
-        <v>710.0221037013474</v>
+        <v>390.5989568039197</v>
       </c>
       <c r="N71">
-        <v>-85.33638941563322</v>
+        <v>234.0867574817945</v>
       </c>
       <c r="O71">
-        <v>-21.28289552025893</v>
+        <v>58.38123731595955</v>
       </c>
       <c r="P71">
-        <v>-64.05349389537429</v>
+        <v>175.705520165835</v>
       </c>
       <c r="Q71">
-        <v>5.546506104625735</v>
+        <v>245.305520165835</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1375641312844729</v>
+        <v>0.1352700182486868</v>
       </c>
       <c r="T71">
-        <v>2.117901503622509</v>
+        <v>2.066282176644038</v>
       </c>
       <c r="U71">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V71">
-        <v>0.2194250239967022</v>
+        <v>0.2494</v>
       </c>
       <c r="W71">
-        <v>0.1277020660741395</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.8798116439322461</v>
+        <v>1.599302054970172</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1319373062893429</v>
+        <v>0.08867995488985285</v>
       </c>
       <c r="C72">
-        <v>-752.7279310727345</v>
+        <v>956.1816342492602</v>
       </c>
       <c r="D72">
-        <v>2967.858860597859</v>
+        <v>4676.768425919853</v>
       </c>
       <c r="E72">
         <v>2020.448517855461</v>
@@ -7191,45 +7191,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M72">
-        <v>720.312279117309</v>
+        <v>396.2598112503534</v>
       </c>
       <c r="N72">
-        <v>-95.62656483159481</v>
+        <v>228.4259030353608</v>
       </c>
       <c r="O72">
-        <v>-23.84926526899974</v>
+        <v>56.96942021701899</v>
       </c>
       <c r="P72">
-        <v>-71.77729956259506</v>
+        <v>171.4564828183418</v>
       </c>
       <c r="Q72">
-        <v>-2.177299562595039</v>
+        <v>241.0564828183419</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.140622935660622</v>
+        <v>0.1379738496328429</v>
       </c>
       <c r="T72">
-        <v>2.188498220409926</v>
+        <v>2.128726319465193</v>
       </c>
       <c r="U72">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V72">
-        <v>0.2162903807967493</v>
+        <v>0.2494</v>
       </c>
       <c r="W72">
-        <v>0.1282148937016518</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.8672429061617855</v>
+        <v>1.576454882756312</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1331153062893429</v>
+        <v>0.08881394412261279</v>
       </c>
       <c r="C73">
-        <v>-844.8811652617214</v>
+        <v>884.9528959269519</v>
       </c>
       <c r="D73">
-        <v>2938.604009147023</v>
+        <v>4668.438070335696</v>
       </c>
       <c r="E73">
         <v>2083.346900593611</v>
@@ -7273,45 +7273,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M73">
-        <v>730.6024545332705</v>
+        <v>401.920665696787</v>
       </c>
       <c r="N73">
-        <v>-105.9167402475563</v>
+        <v>222.7650485889272</v>
       </c>
       <c r="O73">
-        <v>-26.41563501774054</v>
+        <v>55.55760311807845</v>
       </c>
       <c r="P73">
-        <v>-79.50110522981574</v>
+        <v>167.2074454708488</v>
       </c>
       <c r="Q73">
-        <v>-9.901105229815713</v>
+        <v>236.8074454708488</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1438926920627124</v>
+        <v>0.1408641521469406</v>
       </c>
       <c r="T73">
-        <v>2.26396367628613</v>
+        <v>2.195476954894704</v>
       </c>
       <c r="U73">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V73">
-        <v>0.2132440374052458</v>
+        <v>0.2494</v>
       </c>
       <c r="W73">
-        <v>0.1287132754805018</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8550282173426055</v>
+        <v>1.554251292858336</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1342933062893428</v>
+        <v>0.08894793335537272</v>
       </c>
       <c r="C74">
-        <v>-936.4632857622473</v>
+        <v>813.7537812379514</v>
       </c>
       <c r="D74">
-        <v>2909.920271384648</v>
+        <v>4660.137338384846</v>
       </c>
       <c r="E74">
         <v>2146.245283331762</v>
@@ -7355,45 +7355,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M74">
-        <v>740.8926299492319</v>
+        <v>407.5815201432205</v>
       </c>
       <c r="N74">
-        <v>-116.2069156635177</v>
+        <v>217.1041941424937</v>
       </c>
       <c r="O74">
-        <v>-28.98200476648133</v>
+        <v>54.14578601913794</v>
       </c>
       <c r="P74">
-        <v>-87.22491089703642</v>
+        <v>162.9584081233558</v>
       </c>
       <c r="Q74">
-        <v>-17.6249108970364</v>
+        <v>232.5584081233558</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1473960024935235</v>
+        <v>0.1439609048406169</v>
       </c>
       <c r="T74">
-        <v>2.344819521867777</v>
+        <v>2.266995492854894</v>
       </c>
       <c r="U74">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V74">
-        <v>0.2102823146635063</v>
+        <v>0.2494</v>
       </c>
       <c r="W74">
-        <v>0.1291978133210503</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8431528254350693</v>
+        <v>1.532664469346415</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1354713062893428</v>
+        <v>0.08908192258813266</v>
       </c>
       <c r="C75">
-        <v>-1027.490854845995</v>
+        <v>742.5841324455232</v>
       </c>
       <c r="D75">
-        <v>2881.791085039051</v>
+        <v>4651.866072330569</v>
       </c>
       <c r="E75">
         <v>2209.143666069914</v>
@@ -7437,45 +7437,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M75">
-        <v>751.1828053651935</v>
+        <v>413.2423745896542</v>
       </c>
       <c r="N75">
-        <v>-126.4970910794793</v>
+        <v>211.44333969606</v>
       </c>
       <c r="O75">
-        <v>-31.54837451522215</v>
+        <v>52.73396892019738</v>
       </c>
       <c r="P75">
-        <v>-94.94871656425718</v>
+        <v>158.7093707758627</v>
       </c>
       <c r="Q75">
-        <v>-25.34871656425716</v>
+        <v>228.3093707758627</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1511588174006911</v>
+        <v>0.1472870466227136</v>
       </c>
       <c r="T75">
-        <v>2.431664689344361</v>
+        <v>2.343811700293616</v>
       </c>
       <c r="U75">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
-        <v>0.2074017350105816</v>
+        <v>0.2494</v>
       </c>
       <c r="W75">
-        <v>0.1296690761522689</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8316027867304794</v>
+        <v>1.511669065656738</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1366493062893429</v>
+        <v>0.1236185572509342</v>
       </c>
       <c r="C76">
-        <v>-1117.979800509104</v>
+        <v>-780.4877075637914</v>
       </c>
       <c r="D76">
-        <v>2854.200522114094</v>
+        <v>3191.692615059407</v>
       </c>
       <c r="E76">
         <v>2272.042048808065</v>
@@ -7519,37 +7519,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M76">
-        <v>761.4729807811551</v>
+        <v>683.2777113610855</v>
       </c>
       <c r="N76">
-        <v>-136.7872664954409</v>
+        <v>-58.5919970753713</v>
       </c>
       <c r="O76">
-        <v>-34.11474426396297</v>
+        <v>-14.6128440705976</v>
       </c>
       <c r="P76">
-        <v>-102.672522231478</v>
+        <v>-43.97915300477369</v>
       </c>
       <c r="Q76">
-        <v>-33.07252223147793</v>
+        <v>25.62084699522633</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.15521107960841</v>
+        <v>0.1529081986914535</v>
       </c>
       <c r="T76">
-        <v>2.525190254319144</v>
+        <v>2.473630454767978</v>
       </c>
       <c r="U76">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2045990088617899</v>
+        <v>0.2280136093309865</v>
       </c>
       <c r="W76">
-        <v>0.1301276021502112</v>
+        <v>0.1133276021502112</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8203649112341215</v>
+        <v>0.9142486340456557</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1378273062893429</v>
+        <v>0.1246285572509342</v>
       </c>
       <c r="C77">
-        <v>-1207.945446547325</v>
+        <v>-872.4177087027138</v>
       </c>
       <c r="D77">
-        <v>2827.133258814023</v>
+        <v>3162.660996658635</v>
       </c>
       <c r="E77">
         <v>2334.940431546216</v>
@@ -7601,37 +7601,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M77">
-        <v>771.7631561971166</v>
+        <v>692.5111939470461</v>
       </c>
       <c r="N77">
-        <v>-147.0774419114024</v>
+        <v>-67.82547966133188</v>
       </c>
       <c r="O77">
-        <v>-36.68111401270376</v>
+        <v>-16.91567462753617</v>
       </c>
       <c r="P77">
-        <v>-110.3963278986986</v>
+        <v>-50.90980503379571</v>
       </c>
       <c r="Q77">
-        <v>-40.79632789869861</v>
+        <v>18.69019496620432</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1595875227927464</v>
+        <v>0.1571925266391116</v>
       </c>
       <c r="T77">
-        <v>2.62619786449191</v>
+        <v>2.572575672958698</v>
       </c>
       <c r="U77">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2018710220769661</v>
+        <v>0.2249734278732401</v>
       </c>
       <c r="W77">
-        <v>0.1305739007882084</v>
+        <v>0.1137739007882084</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8094267124176666</v>
+        <v>0.9020586522583803</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.179904993138191</v>
+        <v>0.1256385572509342</v>
       </c>
       <c r="C78">
-        <v>-1986.190377217468</v>
+        <v>-963.8243276419362</v>
       </c>
       <c r="D78">
-        <v>2111.786710882032</v>
+        <v>3134.152760457564</v>
       </c>
       <c r="E78">
         <v>2397.838814284368</v>
@@ -7683,45 +7683,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M78">
-        <v>1031.583795611872</v>
+        <v>701.7446765330067</v>
       </c>
       <c r="N78">
-        <v>-406.8980813261581</v>
+        <v>-77.05896224729247</v>
       </c>
       <c r="O78">
-        <v>-101.4803814827439</v>
+        <v>-19.21850518447474</v>
       </c>
       <c r="P78">
-        <v>-305.4176998434143</v>
+        <v>-57.84045706281773</v>
       </c>
       <c r="Q78">
-        <v>-235.8176998434143</v>
+        <v>11.7595429371823</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.169444031445978</v>
+        <v>0.1618338819157413</v>
       </c>
       <c r="T78">
-        <v>2.853684511016508</v>
+        <v>2.679766325998644</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.151026623145479</v>
+        <v>0.2220132511906974</v>
       </c>
       <c r="W78">
-        <v>0.1832084547252056</v>
+        <v>0.1142084547252056</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.6055598361887692</v>
+        <v>0.8901894594655069</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.181604993138191</v>
+        <v>0.1266485572509342</v>
       </c>
       <c r="C79">
-        <v>-2070.458546444274</v>
+        <v>-1054.721591249621</v>
       </c>
       <c r="D79">
-        <v>2090.416924393377</v>
+        <v>3106.153879588031</v>
       </c>
       <c r="E79">
         <v>2460.737197022519</v>
@@ -7765,45 +7765,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M79">
-        <v>1045.157266606765</v>
+        <v>710.9781591189674</v>
       </c>
       <c r="N79">
-        <v>-420.4715523210513</v>
+        <v>-86.29244483325317</v>
       </c>
       <c r="O79">
-        <v>-104.8656051488702</v>
+        <v>-21.52133574141334</v>
       </c>
       <c r="P79">
-        <v>-315.6059471721811</v>
+        <v>-64.77110909183983</v>
       </c>
       <c r="Q79">
-        <v>-246.005947172181</v>
+        <v>4.82889090816019</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.174819858900151</v>
+        <v>0.1668788333033822</v>
       </c>
       <c r="T79">
-        <v>2.977757750625921</v>
+        <v>2.796277905389889</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.149065238429304</v>
+        <v>0.2191299622141948</v>
       </c>
       <c r="W79">
-        <v>0.1836317215469562</v>
+        <v>0.1146317215469562</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5976954227317721</v>
+        <v>0.8786285573945262</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.183304993138191</v>
+        <v>0.1276585572509342</v>
       </c>
       <c r="C80">
-        <v>-2154.298554141317</v>
+        <v>-1145.123029597255</v>
       </c>
       <c r="D80">
-        <v>2069.475299434487</v>
+        <v>3078.650823978549</v>
       </c>
       <c r="E80">
         <v>2523.635579760671</v>
@@ -7847,45 +7847,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M80">
-        <v>1058.730737601659</v>
+        <v>720.2116417049281</v>
       </c>
       <c r="N80">
-        <v>-434.0450233159444</v>
+        <v>-95.52592741921387</v>
       </c>
       <c r="O80">
-        <v>-108.2508288149965</v>
+        <v>-23.82416629835194</v>
       </c>
       <c r="P80">
-        <v>-325.7941945009478</v>
+        <v>-71.70176112086193</v>
       </c>
       <c r="Q80">
-        <v>-256.1941945009478</v>
+        <v>-2.101761120861909</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.180684397941067</v>
+        <v>0.1723824166353541</v>
       </c>
       <c r="T80">
-        <v>3.113110375654372</v>
+        <v>2.923381446543976</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1471541456289283</v>
+        <v>0.2163206037242692</v>
       </c>
       <c r="W80">
-        <v>0.1840441353732773</v>
+        <v>0.1150441353732773</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.5900326609018776</v>
+        <v>0.8673640887099809</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.185004993138191</v>
+        <v>0.1286685572509342</v>
       </c>
       <c r="C81">
-        <v>-2237.723140539068</v>
+        <v>-1235.041697760719</v>
       </c>
       <c r="D81">
-        <v>2048.949095774886</v>
+        <v>3051.630538553236</v>
       </c>
       <c r="E81">
         <v>2586.533962498822</v>
@@ -7929,45 +7929,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M81">
-        <v>1072.304208596551</v>
+        <v>729.4451242908885</v>
       </c>
       <c r="N81">
-        <v>-447.6184943108373</v>
+        <v>-104.7594100051743</v>
       </c>
       <c r="O81">
-        <v>-111.6360524811228</v>
+        <v>-26.12699685529048</v>
       </c>
       <c r="P81">
-        <v>-335.9824418297144</v>
+        <v>-78.63241314988386</v>
       </c>
       <c r="Q81">
-        <v>-266.3824418297144</v>
+        <v>-9.032413149883837</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1871074645096892</v>
+        <v>0.1784101507608472</v>
       </c>
       <c r="T81">
-        <v>3.261353726876009</v>
+        <v>3.062590086855593</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1452914349247647</v>
+        <v>0.2135823682340887</v>
       </c>
       <c r="W81">
-        <v>0.1844461083432358</v>
+        <v>0.1154461083432358</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.5825638930423602</v>
+        <v>0.8563847964478294</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.186704993138191</v>
+        <v>0.1296785572509342</v>
       </c>
       <c r="C82">
-        <v>-2320.744545373505</v>
+        <v>-1324.490196483349</v>
       </c>
       <c r="D82">
-        <v>2028.826073678601</v>
+        <v>3025.080422568757</v>
       </c>
       <c r="E82">
         <v>2649.432345236974</v>
@@ -8011,45 +8011,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M82">
-        <v>1085.877679591445</v>
+        <v>738.6786068768492</v>
       </c>
       <c r="N82">
-        <v>-461.1919653057304</v>
+        <v>-113.992892591135</v>
       </c>
       <c r="O82">
-        <v>-115.0212761472492</v>
+        <v>-28.42982741222908</v>
       </c>
       <c r="P82">
-        <v>-346.1706891584812</v>
+        <v>-85.56306517890596</v>
       </c>
       <c r="Q82">
-        <v>-276.5706891584812</v>
+        <v>-15.96306517890594</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1941728377351737</v>
+        <v>0.1850406582988896</v>
       </c>
       <c r="T82">
-        <v>3.42442141321981</v>
+        <v>3.215719591198373</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1434752919882051</v>
+        <v>0.2109125886311625</v>
       </c>
       <c r="W82">
-        <v>0.1848380319889454</v>
+        <v>0.1158380319889454</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.5752818443793308</v>
+        <v>0.8456799864922314</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.188404993138191</v>
+        <v>0.1306885572509342</v>
       </c>
       <c r="C83">
-        <v>-2403.374532224209</v>
+        <v>-1413.480691769599</v>
       </c>
       <c r="D83">
-        <v>2009.094469566049</v>
+        <v>2998.988310020659</v>
       </c>
       <c r="E83">
         <v>2712.330727975125</v>
@@ -8093,45 +8093,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M83">
-        <v>1099.451150586338</v>
+        <v>747.9120894628099</v>
       </c>
       <c r="N83">
-        <v>-474.7654363006235</v>
+        <v>-123.2263751770957</v>
       </c>
       <c r="O83">
-        <v>-118.4064998133755</v>
+        <v>-30.73265796916768</v>
       </c>
       <c r="P83">
-        <v>-356.358936487248</v>
+        <v>-92.49371720792807</v>
       </c>
       <c r="Q83">
-        <v>-286.758936487248</v>
+        <v>-22.89371720792805</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2019819344580775</v>
+        <v>0.1923691139988311</v>
       </c>
       <c r="T83">
-        <v>3.604654119178747</v>
+        <v>3.38496799073513</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1417039920871161</v>
+        <v>0.2083087295122593</v>
       </c>
       <c r="W83">
-        <v>0.1852202785076003</v>
+        <v>0.1162202785076004</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5681795993869934</v>
+        <v>0.8352394928318334</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.190104993138191</v>
+        <v>0.1316985572509342</v>
       </c>
       <c r="C84">
-        <v>-2485.624411445944</v>
+        <v>-1502.024933473404</v>
       </c>
       <c r="D84">
-        <v>1989.742973082465</v>
+        <v>2973.342451055004</v>
       </c>
       <c r="E84">
         <v>2775.229110713276</v>
@@ -8175,45 +8175,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M84">
-        <v>1113.024621581231</v>
+        <v>757.1455720487704</v>
       </c>
       <c r="N84">
-        <v>-488.3389072955164</v>
+        <v>-132.4598577630562</v>
       </c>
       <c r="O84">
-        <v>-121.7917234795018</v>
+        <v>-33.03548852610622</v>
       </c>
       <c r="P84">
-        <v>-366.5471838160146</v>
+        <v>-99.42436923695</v>
       </c>
       <c r="Q84">
-        <v>-296.9471838160146</v>
+        <v>-29.82436923694998</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2106587085946374</v>
+        <v>0.2005118425543217</v>
       </c>
       <c r="T84">
-        <v>3.804912681355344</v>
+        <v>3.573021767998192</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1399758946226392</v>
+        <v>0.2057683791523537</v>
       </c>
       <c r="W84">
-        <v>0.1855932019404345</v>
+        <v>0.1165932019404345</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.561250579882274</v>
+        <v>0.8250536453582746</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.191804993138191</v>
+        <v>0.1327085572509342</v>
       </c>
       <c r="C85">
-        <v>-2567.505061787619</v>
+        <v>-1590.134272940881</v>
       </c>
       <c r="D85">
-        <v>1970.760705478942</v>
+        <v>2948.13149432568</v>
       </c>
       <c r="E85">
         <v>2838.127493451428</v>
@@ -8257,45 +8257,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M85">
-        <v>1126.598092576124</v>
+        <v>766.3790546347311</v>
       </c>
       <c r="N85">
-        <v>-501.9123782904095</v>
+        <v>-141.6933403490169</v>
       </c>
       <c r="O85">
-        <v>-125.1769471456281</v>
+        <v>-35.33831908304482</v>
       </c>
       <c r="P85">
-        <v>-376.7354311447814</v>
+        <v>-106.3550212659721</v>
       </c>
       <c r="Q85">
-        <v>-307.1354311447814</v>
+        <v>-36.75502126597208</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2203562796884397</v>
+        <v>0.2096125391751642</v>
       </c>
       <c r="T85">
-        <v>4.028731074376248</v>
+        <v>3.78319951905691</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1382894380609206</v>
+        <v>0.2032892420541325</v>
       </c>
       <c r="W85">
-        <v>0.1859571392664534</v>
+        <v>0.1169571392664533</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.5544885247029694</v>
+        <v>0.8151132399925122</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.193504993138191</v>
+        <v>0.1337185572509342</v>
       </c>
       <c r="C86">
-        <v>-2649.026950785458</v>
+        <v>-1677.819679762997</v>
       </c>
       <c r="D86">
-        <v>1952.137199219253</v>
+        <v>2923.344470241714</v>
       </c>
       <c r="E86">
         <v>2901.025876189578</v>
@@ -8339,45 +8339,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M86">
-        <v>1140.171563571017</v>
+        <v>775.6125372206916</v>
       </c>
       <c r="N86">
-        <v>-515.4858492853026</v>
+        <v>-150.9268229349774</v>
       </c>
       <c r="O86">
-        <v>-128.5621708117545</v>
+        <v>-37.64114963998336</v>
       </c>
       <c r="P86">
-        <v>-386.9236784735481</v>
+        <v>-113.285673294994</v>
       </c>
       <c r="Q86">
-        <v>-317.3236784735481</v>
+        <v>-43.68567329499402</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.231266047168967</v>
+        <v>0.2198508228736119</v>
       </c>
       <c r="T86">
-        <v>4.28052676652476</v>
+        <v>4.019649488997964</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.136643135226862</v>
+        <v>0.2008691320296786</v>
       </c>
       <c r="W86">
-        <v>0.1863124114180432</v>
+        <v>0.1173124114180432</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5478874708374579</v>
+        <v>0.8054095109449824</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.195204993138191</v>
+        <v>0.1821486725626448</v>
       </c>
       <c r="C87">
-        <v>-2730.200154010728</v>
+        <v>-2580.653921317167</v>
       </c>
       <c r="D87">
-        <v>1933.862378732135</v>
+        <v>2083.408611425695</v>
       </c>
       <c r="E87">
         <v>2963.92425892773</v>
@@ -8421,37 +8421,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M87">
-        <v>1153.74503456591</v>
+        <v>1073.549596574767</v>
       </c>
       <c r="N87">
-        <v>-529.0593202801957</v>
+        <v>-448.8638822890526</v>
       </c>
       <c r="O87">
-        <v>-131.9473944778808</v>
+        <v>-111.9466522428897</v>
       </c>
       <c r="P87">
-        <v>-397.1119258023149</v>
+        <v>-336.9172300461629</v>
       </c>
       <c r="Q87">
-        <v>-327.5119258023149</v>
+        <v>-267.3172300461629</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2436304503135648</v>
+        <v>0.2415883131432566</v>
       </c>
       <c r="T87">
-        <v>4.565895217626411</v>
+        <v>4.521670049497843</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1350355689300754</v>
+        <v>0.1451228873262464</v>
       </c>
       <c r="W87">
-        <v>0.1866593242248897</v>
+        <v>0.1716593242248897</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.541441735886429</v>
+        <v>0.5818880806986622</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.196904993138191</v>
+        <v>0.1836986725626447</v>
       </c>
       <c r="C88">
-        <v>-2811.034373246358</v>
+        <v>-2662.53602803269</v>
       </c>
       <c r="D88">
-        <v>1915.926542234656</v>
+        <v>2064.424887448324</v>
       </c>
       <c r="E88">
         <v>3026.822641665881</v>
@@ -8503,37 +8503,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M88">
-        <v>1167.318505560803</v>
+        <v>1086.179591828587</v>
       </c>
       <c r="N88">
-        <v>-542.6327912750886</v>
+        <v>-461.4938775428733</v>
       </c>
       <c r="O88">
-        <v>-135.3326181440071</v>
+        <v>-115.0965730591926</v>
       </c>
       <c r="P88">
-        <v>-407.3001731310815</v>
+        <v>-346.3973044836807</v>
       </c>
       <c r="Q88">
-        <v>-337.7001731310814</v>
+        <v>-276.7973044836806</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2577611967645337</v>
+        <v>0.2555731926534892</v>
       </c>
       <c r="T88">
-        <v>4.892030590314012</v>
+        <v>4.844646481604832</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1334653878960048</v>
+        <v>0.1434354118922203</v>
       </c>
       <c r="W88">
-        <v>0.1869981692920422</v>
+        <v>0.1719981692920422</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5351459017482147</v>
+        <v>0.575121940225422</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.198604993138191</v>
+        <v>0.1852486725626448</v>
       </c>
       <c r="C89">
-        <v>-2891.538953661382</v>
+        <v>-2744.075304563779</v>
       </c>
       <c r="D89">
-        <v>1898.320344557783</v>
+        <v>2045.783993655386</v>
       </c>
       <c r="E89">
         <v>3089.721024404033</v>
@@ -8585,37 +8585,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M89">
-        <v>1180.891976555696</v>
+        <v>1098.809587082408</v>
       </c>
       <c r="N89">
-        <v>-556.2062622699817</v>
+        <v>-474.1238727966942</v>
       </c>
       <c r="O89">
-        <v>-138.7178418101335</v>
+        <v>-118.2464938754955</v>
       </c>
       <c r="P89">
-        <v>-417.4884204598483</v>
+        <v>-355.8773789211987</v>
       </c>
       <c r="Q89">
-        <v>-347.8884204598482</v>
+        <v>-286.2773789211986</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2740659042079594</v>
+        <v>0.271709592088373</v>
       </c>
       <c r="T89">
-        <v>5.268340635722782</v>
+        <v>5.217311595574435</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1319313029776598</v>
+        <v>0.1417867289969074</v>
       </c>
       <c r="W89">
-        <v>0.187329224817421</v>
+        <v>0.172329224817421</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5289947994292696</v>
+        <v>0.5685113432113367</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.200304993138191</v>
+        <v>0.1867986725626448</v>
       </c>
       <c r="C90">
-        <v>-2971.72290004706</v>
+        <v>-2825.280954644348</v>
       </c>
       <c r="D90">
-        <v>1881.034780910257</v>
+        <v>2027.476726312969</v>
       </c>
       <c r="E90">
         <v>3152.619407142184</v>
@@ -8667,37 +8667,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M90">
-        <v>1194.465447550589</v>
+        <v>1111.439582336229</v>
       </c>
       <c r="N90">
-        <v>-569.7797332648748</v>
+        <v>-486.7538680505151</v>
       </c>
       <c r="O90">
-        <v>-142.1030654762598</v>
+        <v>-121.3964146917985</v>
       </c>
       <c r="P90">
-        <v>-427.6766677886151</v>
+        <v>-365.3574533587166</v>
       </c>
       <c r="Q90">
-        <v>-358.0766677886151</v>
+        <v>-295.7574533587166</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.293088062891956</v>
+        <v>0.2905353914290708</v>
       </c>
       <c r="T90">
-        <v>5.707369022033015</v>
+        <v>5.652087561872305</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.130432083625641</v>
+        <v>0.1401755161673971</v>
       </c>
       <c r="W90">
-        <v>0.1876527563535867</v>
+        <v>0.1726527563535867</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5229834948903007</v>
+        <v>0.5620509870384806</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.202004993138191</v>
+        <v>0.1883486725626448</v>
       </c>
       <c r="C91">
-        <v>-3051.594892173947</v>
+        <v>-2906.161855481623</v>
       </c>
       <c r="D91">
-        <v>1864.06117152152</v>
+        <v>2009.494208213844</v>
       </c>
       <c r="E91">
         <v>3215.517789880335</v>
@@ -8749,37 +8749,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M91">
-        <v>1208.038918545482</v>
+        <v>1124.06957759005</v>
       </c>
       <c r="N91">
-        <v>-583.3532042597677</v>
+        <v>-499.3838633043357</v>
       </c>
       <c r="O91">
-        <v>-145.4882891423861</v>
+        <v>-124.5463355081013</v>
       </c>
       <c r="P91">
-        <v>-437.8649151173817</v>
+        <v>-374.8375277962344</v>
       </c>
       <c r="Q91">
-        <v>-368.2649151173816</v>
+        <v>-305.2375277962344</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3155687958821339</v>
+        <v>0.3127840633771681</v>
       </c>
       <c r="T91">
-        <v>6.226220751308745</v>
+        <v>6.165913703860697</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1289665545961394</v>
+        <v>0.1386005103677634</v>
       </c>
       <c r="W91">
-        <v>0.1879690175181531</v>
+        <v>0.1729690175181531</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5171072758465896</v>
+        <v>0.5557358074088348</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.203704993138191</v>
+        <v>0.1898986725626448</v>
       </c>
       <c r="C92">
-        <v>-3131.16329932497</v>
+        <v>-2986.726572109345</v>
       </c>
       <c r="D92">
-        <v>1847.39114710865</v>
+        <v>1991.827874324274</v>
       </c>
       <c r="E92">
         <v>3278.416172618487</v>
@@ -8831,37 +8831,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M92">
-        <v>1221.612389540375</v>
+        <v>1136.699572843871</v>
       </c>
       <c r="N92">
-        <v>-596.9266752546608</v>
+        <v>-512.0138585581566</v>
       </c>
       <c r="O92">
-        <v>-148.8735128085124</v>
+        <v>-127.6962563244043</v>
       </c>
       <c r="P92">
-        <v>-448.0531624461484</v>
+        <v>-384.3176022337523</v>
       </c>
       <c r="Q92">
-        <v>-378.4531624461484</v>
+        <v>-314.7176022337523</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3425456754703474</v>
+        <v>0.339482469714885</v>
       </c>
       <c r="T92">
-        <v>6.84884282643962</v>
+        <v>6.782505074246767</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1275335928784045</v>
+        <v>0.1370605046970104</v>
       </c>
       <c r="W92">
-        <v>0.1882782506568403</v>
+        <v>0.1732782506568403</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.511361639448294</v>
+        <v>0.5495609651042921</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.205404993138191</v>
+        <v>0.1914486725626448</v>
       </c>
       <c r="C93">
-        <v>-3210.436194055581</v>
+        <v>-3066.98337099043</v>
       </c>
       <c r="D93">
-        <v>1831.01663511619</v>
+        <v>1974.469458181341</v>
       </c>
       <c r="E93">
         <v>3341.314555356638</v>
@@ -8913,37 +8913,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M93">
-        <v>1235.185860535268</v>
+        <v>1149.329568097692</v>
       </c>
       <c r="N93">
-        <v>-610.5001462495539</v>
+        <v>-524.6438538119775</v>
       </c>
       <c r="O93">
-        <v>-152.2587364746388</v>
+        <v>-130.8461771407072</v>
       </c>
       <c r="P93">
-        <v>-458.2414097749152</v>
+        <v>-393.7976766712703</v>
       </c>
       <c r="Q93">
-        <v>-388.6414097749151</v>
+        <v>-324.1976766712702</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3755174171892748</v>
+        <v>0.3721138552387611</v>
       </c>
       <c r="T93">
-        <v>7.609825362710688</v>
+        <v>7.536116749163075</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1261321248247957</v>
+        <v>0.1355543453047356</v>
       </c>
       <c r="W93">
-        <v>0.1885806874628091</v>
+        <v>0.1735806874628091</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5057422807730381</v>
+        <v>0.5435218336196295</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2071049931381911</v>
+        <v>0.1929986725626448</v>
       </c>
       <c r="C94">
-        <v>-3289.421365228586</v>
+        <v>-3146.940232914528</v>
       </c>
       <c r="D94">
-        <v>1814.929846681336</v>
+        <v>1957.410978995394</v>
       </c>
       <c r="E94">
         <v>3404.212938094789</v>
@@ -8995,37 +8995,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M94">
-        <v>1248.759331530161</v>
+        <v>1161.959563351512</v>
       </c>
       <c r="N94">
-        <v>-624.0736172444471</v>
+        <v>-537.2738490657981</v>
       </c>
       <c r="O94">
-        <v>-155.6439601407651</v>
+        <v>-133.9960979570101</v>
       </c>
       <c r="P94">
-        <v>-468.429657103682</v>
+        <v>-403.277751108788</v>
       </c>
       <c r="Q94">
-        <v>-398.8296571036819</v>
+        <v>-333.677751108788</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4167320943379343</v>
+        <v>0.4129030871436063</v>
       </c>
       <c r="T94">
-        <v>8.561053533049527</v>
+        <v>8.47813134280846</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1247611234680044</v>
+        <v>0.134080928507945</v>
       </c>
       <c r="W94">
-        <v>0.1888765495556047</v>
+        <v>0.1738765495556046</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5002450820689832</v>
+        <v>0.5376139876020249</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.237174605776425</v>
+        <v>0.1945486725626448</v>
       </c>
       <c r="C95">
-        <v>-3596.428182192521</v>
+        <v>-3226.604865232726</v>
       </c>
       <c r="D95">
-        <v>1570.821412455553</v>
+        <v>1940.644729415347</v>
       </c>
       <c r="E95">
         <v>3467.111320832941</v>
@@ -9077,45 +9077,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M95">
-        <v>1437.819290364497</v>
+        <v>1174.589558605333</v>
       </c>
       <c r="N95">
-        <v>-813.1335760787823</v>
+        <v>-549.903844319619</v>
       </c>
       <c r="O95">
-        <v>-202.7955138740483</v>
+        <v>-137.146018773313</v>
       </c>
       <c r="P95">
-        <v>-610.338062204734</v>
+        <v>-412.757825546306</v>
       </c>
       <c r="Q95">
-        <v>-540.738062204734</v>
+        <v>-343.157825546306</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4764311455038385</v>
+        <v>0.4653463853069788</v>
       </c>
       <c r="T95">
-        <v>9.938898105425483</v>
+        <v>9.689292963209672</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1083561878651396</v>
+        <v>0.1326391980938811</v>
       </c>
       <c r="W95">
-        <v>0.2191660490227487</v>
+        <v>0.1741660490227487</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.4344674733967105</v>
+        <v>0.5318331920364117</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.239174605776425</v>
+        <v>0.1960986725626448</v>
       </c>
       <c r="C96">
-        <v>-3673.254413231382</v>
+        <v>-3305.984713468816</v>
       </c>
       <c r="D96">
-        <v>1556.893564154842</v>
+        <v>1924.163263917409</v>
       </c>
       <c r="E96">
         <v>3530.009703571092</v>
@@ -9159,45 +9159,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M96">
-        <v>1453.279712841534</v>
+        <v>1187.219553859154</v>
       </c>
       <c r="N96">
-        <v>-828.5939985558199</v>
+        <v>-562.5338395734399</v>
       </c>
       <c r="O96">
-        <v>-206.6513432398215</v>
+        <v>-140.2959395896159</v>
       </c>
       <c r="P96">
-        <v>-621.9426553159984</v>
+        <v>-422.237899983824</v>
       </c>
       <c r="Q96">
-        <v>-552.3426553159984</v>
+        <v>-352.637899983824</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5482030030878117</v>
+        <v>0.535270782858142</v>
       </c>
       <c r="T96">
-        <v>11.5953811229964</v>
+        <v>11.30417512374462</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.107203462462319</v>
+        <v>0.13122814279501</v>
       </c>
       <c r="W96">
-        <v>0.219449388926762</v>
+        <v>0.174449388926762</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.4298454789988733</v>
+        <v>0.5261753921211307</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.241174605776425</v>
+        <v>0.1976486725626448</v>
       </c>
       <c r="C97">
-        <v>-3749.835829569154</v>
+        <v>-3385.086972343865</v>
       </c>
       <c r="D97">
-        <v>1543.210530555222</v>
+        <v>1907.95938778051</v>
       </c>
       <c r="E97">
         <v>3592.908086309243</v>
@@ -9241,45 +9241,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M97">
-        <v>1468.740135318572</v>
+        <v>1199.849549112975</v>
       </c>
       <c r="N97">
-        <v>-844.0544210328575</v>
+        <v>-575.1638348272605</v>
       </c>
       <c r="O97">
-        <v>-210.5071726055947</v>
+        <v>-143.4458604059188</v>
       </c>
       <c r="P97">
-        <v>-633.5472484272628</v>
+        <v>-431.7179744213418</v>
       </c>
       <c r="Q97">
-        <v>-563.9472484272628</v>
+        <v>-362.1179744213417</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6486836037053743</v>
+        <v>0.6331649394297707</v>
       </c>
       <c r="T97">
-        <v>13.91445734759569</v>
+        <v>13.56501014849355</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1060750049627156</v>
+        <v>0.1298467939234836</v>
       </c>
       <c r="W97">
-        <v>0.2197267637801645</v>
+        <v>0.1747267637801645</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.4253207897462535</v>
+        <v>0.5206367037830135</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2431746057764249</v>
+        <v>0.1991986725626448</v>
       </c>
       <c r="C98">
-        <v>-3826.17882976249</v>
+        <v>-3463.918596248408</v>
       </c>
       <c r="D98">
-        <v>1529.765913100036</v>
+        <v>1892.026146614119</v>
       </c>
       <c r="E98">
         <v>3655.806469047394</v>
@@ -9323,45 +9323,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M98">
-        <v>1484.200557795609</v>
+        <v>1212.479544366795</v>
       </c>
       <c r="N98">
-        <v>-859.5148435098948</v>
+        <v>-587.7938300810812</v>
       </c>
       <c r="O98">
-        <v>-214.3630019713678</v>
+        <v>-146.5957812222217</v>
       </c>
       <c r="P98">
-        <v>-645.151841538527</v>
+        <v>-441.1980488588595</v>
       </c>
       <c r="Q98">
-        <v>-575.551841538527</v>
+        <v>-371.5980488588595</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7994045046317162</v>
+        <v>0.7800061742872116</v>
       </c>
       <c r="T98">
-        <v>17.39307168449457</v>
+        <v>16.9562626856169</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.104970056994354</v>
+        <v>0.1284942231534473</v>
       </c>
       <c r="W98">
-        <v>0.2199983599907878</v>
+        <v>0.1749983599907878</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.4208903648530634</v>
+        <v>0.5152134047852739</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.245174605776425</v>
+        <v>0.2007486725626448</v>
       </c>
       <c r="C99">
-        <v>-3902.289591314216</v>
+        <v>-3542.486309194256</v>
       </c>
       <c r="D99">
-        <v>1516.553534286463</v>
+        <v>1876.356816406422</v>
       </c>
       <c r="E99">
         <v>3718.704851785546</v>
@@ -9405,45 +9405,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M99">
-        <v>1499.660980272647</v>
+        <v>1225.109539620616</v>
       </c>
       <c r="N99">
-        <v>-874.9752659869326</v>
+        <v>-600.4238253349021</v>
       </c>
       <c r="O99">
-        <v>-218.218831337141</v>
+        <v>-149.7457020385246</v>
       </c>
       <c r="P99">
-        <v>-656.7564346497916</v>
+        <v>-450.6781232963775</v>
       </c>
       <c r="Q99">
-        <v>-587.1564346497915</v>
+        <v>-381.0781232963775</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.050606006175622</v>
+        <v>1.024741565716282</v>
       </c>
       <c r="T99">
-        <v>23.19076224599276</v>
+        <v>22.6083502474892</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1038878914583297</v>
+        <v>0.1271695404405252</v>
       </c>
       <c r="W99">
-        <v>0.2202643562795426</v>
+        <v>0.1752643562795425</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.4165512889267432</v>
+        <v>0.5099019263854256</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.247174605776425</v>
+        <v>0.2022986725626447</v>
       </c>
       <c r="C100">
-        <v>-3978.174080137635</v>
+        <v>-3620.79661427586</v>
       </c>
       <c r="D100">
-        <v>1503.567428201195</v>
+        <v>1860.94489406297</v>
       </c>
       <c r="E100">
         <v>3781.603234523697</v>
@@ -9487,45 +9487,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M100">
-        <v>1515.121402749684</v>
+        <v>1237.739534874437</v>
       </c>
       <c r="N100">
-        <v>-890.4356884639702</v>
+        <v>-613.0538205887229</v>
       </c>
       <c r="O100">
-        <v>-222.0746607029142</v>
+        <v>-152.8956228548275</v>
       </c>
       <c r="P100">
-        <v>-668.361027761056</v>
+        <v>-460.1581977338955</v>
       </c>
       <c r="Q100">
-        <v>-598.761027761056</v>
+        <v>-390.5581977338954</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.553009009263433</v>
+        <v>1.514212348574423</v>
       </c>
       <c r="T100">
-        <v>34.78614336898914</v>
+        <v>33.9125253712338</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1028278109332448</v>
+        <v>0.1258718920686831</v>
       </c>
       <c r="W100">
-        <v>0.2205249240726085</v>
+        <v>0.1755249240726084</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.4123007655703478</v>
+        <v>0.5046988455039416</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.249174605776425</v>
+        <v>0.2391120574518767</v>
       </c>
       <c r="C101">
-        <v>-4053.838059538733</v>
+        <v>-3987.469648834779</v>
       </c>
       <c r="D101">
-        <v>1490.801831538248</v>
+        <v>1557.170242242201</v>
       </c>
       <c r="E101">
         <v>3844.501617261848</v>
@@ -9569,37 +9569,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M101">
-        <v>1530.581825226722</v>
+        <v>1468.312426315952</v>
       </c>
       <c r="N101">
-        <v>-905.8961109410078</v>
+        <v>-843.6267120302379</v>
       </c>
       <c r="O101">
-        <v>-225.9304900686874</v>
+        <v>-210.4005019803413</v>
       </c>
       <c r="P101">
-        <v>-679.9656208723204</v>
+        <v>-633.2262100498965</v>
       </c>
       <c r="Q101">
-        <v>-610.3656208723204</v>
+        <v>-563.6262100498965</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.060218018526865</v>
+        <v>3.043963186072048</v>
       </c>
       <c r="T101">
-        <v>69.57228673797827</v>
+        <v>69.24164402013967</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.1017891461763433</v>
+        <v>0.1061059038598184</v>
       </c>
       <c r="W101">
-        <v>0.2207802278698549</v>
+        <v>0.2107802278698548</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.4081361113726676</v>
+        <v>0.4254446826777002</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_apparel.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_apparel.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07930070859665728</v>
+        <v>0.07913670962941723</v>
       </c>
       <c r="C2">
-        <v>6026.615798250753</v>
+        <v>5977.089120196127</v>
       </c>
       <c r="D2">
-        <v>5344.315798250753</v>
+        <v>5357.687502934278</v>
       </c>
       <c r="E2">
-        <v>-2382.438273815133</v>
+        <v>-2319.539891076981</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>62.89838273815133</v>
       </c>
       <c r="G2">
         <v>682.3</v>
@@ -1451,28 +1451,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.163788651729011</v>
       </c>
       <c r="N2">
-        <v>624.6857142857142</v>
+        <v>621.5219256339852</v>
       </c>
       <c r="O2">
-        <v>155.7966171428571</v>
+        <v>155.0075682531159</v>
       </c>
       <c r="P2">
-        <v>468.8890971428571</v>
+        <v>466.5143573808693</v>
       </c>
       <c r="Q2">
-        <v>538.4890971428571</v>
+        <v>536.1143573808694</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07930070859665728</v>
+        <v>0.07955470487819921</v>
       </c>
       <c r="T2">
-        <v>0.7736884202461267</v>
+        <v>0.7795543851778109</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>197.4486234863771</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07913670962941723</v>
+        <v>0.07897271066217716</v>
       </c>
       <c r="C3">
-        <v>5977.089120196127</v>
+        <v>5927.629523124911</v>
       </c>
       <c r="D3">
-        <v>5357.687502934278</v>
+        <v>5371.126288601213</v>
       </c>
       <c r="E3">
-        <v>-2319.539891076981</v>
+        <v>-2256.64150833883</v>
       </c>
       <c r="F3">
-        <v>62.89838273815133</v>
+        <v>125.7967654763027</v>
       </c>
       <c r="G3">
         <v>682.3</v>
@@ -1533,28 +1533,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M3">
-        <v>3.163788651729011</v>
+        <v>6.327577303458023</v>
       </c>
       <c r="N3">
-        <v>621.5219256339852</v>
+        <v>618.3581369822562</v>
       </c>
       <c r="O3">
-        <v>155.0075682531159</v>
+        <v>154.2185193633747</v>
       </c>
       <c r="P3">
-        <v>466.5143573808693</v>
+        <v>464.1396176188815</v>
       </c>
       <c r="Q3">
-        <v>536.1143573808694</v>
+        <v>533.7396176188815</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07955470487819921</v>
+        <v>0.07981388475732364</v>
       </c>
       <c r="T3">
-        <v>0.7795543851778109</v>
+        <v>0.7855400636795297</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>197.4486234863771</v>
+        <v>98.72431174318854</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07897271066217716</v>
+        <v>0.0788087116949371</v>
       </c>
       <c r="C4">
-        <v>5927.629523124911</v>
+        <v>5878.237513087814</v>
       </c>
       <c r="D4">
-        <v>5371.126288601213</v>
+        <v>5384.632661302267</v>
       </c>
       <c r="E4">
-        <v>-2256.64150833883</v>
+        <v>-2193.743125600678</v>
       </c>
       <c r="F4">
-        <v>125.7967654763027</v>
+        <v>188.695148214454</v>
       </c>
       <c r="G4">
         <v>682.3</v>
@@ -1615,28 +1615,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M4">
-        <v>6.327577303458023</v>
+        <v>9.491365955187034</v>
       </c>
       <c r="N4">
-        <v>618.3581369822562</v>
+        <v>615.1943483305272</v>
       </c>
       <c r="O4">
-        <v>154.2185193633747</v>
+        <v>153.4294704736335</v>
       </c>
       <c r="P4">
-        <v>464.1396176188815</v>
+        <v>461.7648778568937</v>
       </c>
       <c r="Q4">
-        <v>533.7396176188815</v>
+        <v>531.3648778568937</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07981388475732364</v>
+        <v>0.08007840855148154</v>
       </c>
       <c r="T4">
-        <v>0.7855400636795297</v>
+        <v>0.79164915823283</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.72431174318854</v>
+        <v>65.81620782879237</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0788087116949371</v>
+        <v>0.07864471272769703</v>
       </c>
       <c r="C5">
-        <v>5878.237513087814</v>
+        <v>5828.913601238497</v>
       </c>
       <c r="D5">
-        <v>5384.632661302267</v>
+        <v>5398.207132191102</v>
       </c>
       <c r="E5">
-        <v>-2193.743125600678</v>
+        <v>-2130.844742862527</v>
       </c>
       <c r="F5">
-        <v>188.695148214454</v>
+        <v>251.5935309526053</v>
       </c>
       <c r="G5">
         <v>682.3</v>
@@ -1697,28 +1697,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M5">
-        <v>9.491365955187034</v>
+        <v>12.65515460691605</v>
       </c>
       <c r="N5">
-        <v>615.1943483305272</v>
+        <v>612.0305596787981</v>
       </c>
       <c r="O5">
-        <v>153.4294704736335</v>
+        <v>152.6404215838922</v>
       </c>
       <c r="P5">
-        <v>461.7648778568937</v>
+        <v>459.3901380949059</v>
       </c>
       <c r="Q5">
-        <v>531.3648778568937</v>
+        <v>528.9901380949059</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08007840855148154</v>
+        <v>0.08034844325801774</v>
       </c>
       <c r="T5">
-        <v>0.79164915823283</v>
+        <v>0.7978855255893242</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.81620782879237</v>
+        <v>49.36215587159427</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07864471272769703</v>
+        <v>0.07848071376045697</v>
       </c>
       <c r="C6">
-        <v>5828.913601238497</v>
+        <v>5779.658303898044</v>
       </c>
       <c r="D6">
-        <v>5398.207132191102</v>
+        <v>5411.850217588801</v>
       </c>
       <c r="E6">
-        <v>-2130.844742862527</v>
+        <v>-2067.946360124376</v>
       </c>
       <c r="F6">
-        <v>251.5935309526053</v>
+        <v>314.4919136907566</v>
       </c>
       <c r="G6">
         <v>682.3</v>
@@ -1779,28 +1779,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M6">
-        <v>12.65515460691605</v>
+        <v>15.81894325864506</v>
       </c>
       <c r="N6">
-        <v>612.0305596787981</v>
+        <v>608.8667710270691</v>
       </c>
       <c r="O6">
-        <v>152.6404215838922</v>
+        <v>151.8513726941511</v>
       </c>
       <c r="P6">
-        <v>459.3901380949059</v>
+        <v>457.0153983329181</v>
       </c>
       <c r="Q6">
-        <v>528.9901380949059</v>
+        <v>526.6153983329182</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08034844325801774</v>
+        <v>0.08062416290574417</v>
       </c>
       <c r="T6">
-        <v>0.7978855255893242</v>
+        <v>0.8042531848901658</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.36215587159427</v>
+        <v>39.48972469727541</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07848071376045697</v>
+        <v>0.0783167147932169</v>
       </c>
       <c r="C7">
-        <v>5779.658303898044</v>
+        <v>5730.472142620439</v>
       </c>
       <c r="D7">
-        <v>5411.850217588801</v>
+        <v>5425.562439049347</v>
       </c>
       <c r="E7">
-        <v>-2067.946360124376</v>
+        <v>-2005.047977386225</v>
       </c>
       <c r="F7">
-        <v>314.4919136907566</v>
+        <v>377.390296428908</v>
       </c>
       <c r="G7">
         <v>682.3</v>
@@ -1861,28 +1861,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M7">
-        <v>15.81894325864506</v>
+        <v>18.98273191037407</v>
       </c>
       <c r="N7">
-        <v>608.8667710270691</v>
+        <v>605.7029823753401</v>
       </c>
       <c r="O7">
-        <v>151.8513726941511</v>
+        <v>151.0623238044098</v>
       </c>
       <c r="P7">
-        <v>457.0153983329181</v>
+        <v>454.6406585709302</v>
       </c>
       <c r="Q7">
-        <v>526.6153983329182</v>
+        <v>524.2406585709302</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08062416290574417</v>
+        <v>0.08090574892895415</v>
       </c>
       <c r="T7">
-        <v>0.8042531848901658</v>
+        <v>0.810756326303791</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.48972469727541</v>
+        <v>32.90810391439618</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0783167147932169</v>
+        <v>0.07815271582597685</v>
       </c>
       <c r="C8">
-        <v>5730.472142620439</v>
+        <v>5681.355644259014</v>
       </c>
       <c r="D8">
-        <v>5425.562439049347</v>
+        <v>5439.344323426073</v>
       </c>
       <c r="E8">
-        <v>-2005.047977386225</v>
+        <v>-1942.149594648073</v>
       </c>
       <c r="F8">
-        <v>377.3902964289079</v>
+        <v>440.2886791670592</v>
       </c>
       <c r="G8">
         <v>682.3</v>
@@ -1943,28 +1943,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M8">
-        <v>18.98273191037407</v>
+        <v>22.14652056210308</v>
       </c>
       <c r="N8">
-        <v>605.7029823753402</v>
+        <v>602.5391937236111</v>
       </c>
       <c r="O8">
-        <v>151.0623238044099</v>
+        <v>150.2732749146686</v>
       </c>
       <c r="P8">
-        <v>454.6406585709303</v>
+        <v>452.2659188089425</v>
       </c>
       <c r="Q8">
-        <v>524.2406585709303</v>
+        <v>521.8659188089425</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08090574892895415</v>
+        <v>0.0811933905655665</v>
       </c>
       <c r="T8">
-        <v>0.810756326303791</v>
+        <v>0.8173993202209354</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.90810391439619</v>
+        <v>28.20694621233959</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07815271582597684</v>
+        <v>0.07798871685873679</v>
       </c>
       <c r="C9">
-        <v>5681.355644259015</v>
+        <v>5632.309341033943</v>
       </c>
       <c r="D9">
-        <v>5439.344323426074</v>
+        <v>5453.196402939154</v>
       </c>
       <c r="E9">
-        <v>-1942.149594648073</v>
+        <v>-1879.251211909922</v>
       </c>
       <c r="F9">
-        <v>440.2886791670593</v>
+        <v>503.1870619052106</v>
       </c>
       <c r="G9">
         <v>682.3</v>
@@ -2025,28 +2025,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M9">
-        <v>22.14652056210308</v>
+        <v>25.31030921383209</v>
       </c>
       <c r="N9">
-        <v>602.5391937236111</v>
+        <v>599.3754050718821</v>
       </c>
       <c r="O9">
-        <v>150.2732749146686</v>
+        <v>149.4842260249274</v>
       </c>
       <c r="P9">
-        <v>452.2659188089425</v>
+        <v>449.8911790469547</v>
       </c>
       <c r="Q9">
-        <v>521.8659188089425</v>
+        <v>519.4911790469548</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0811933905655665</v>
+        <v>0.08148728528123564</v>
       </c>
       <c r="T9">
-        <v>0.8173993202209354</v>
+        <v>0.8241867270493218</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.20694621233958</v>
+        <v>24.68107793579714</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07798871685873679</v>
+        <v>0.07782471789149673</v>
       </c>
       <c r="C10">
-        <v>5632.309341033943</v>
+        <v>5583.333770600742</v>
       </c>
       <c r="D10">
-        <v>5453.196402939154</v>
+        <v>5467.119215244104</v>
       </c>
       <c r="E10">
-        <v>-1879.251211909922</v>
+        <v>-1816.352829171771</v>
       </c>
       <c r="F10">
-        <v>503.1870619052106</v>
+        <v>566.0854446433618</v>
       </c>
       <c r="G10">
         <v>682.3</v>
@@ -2107,28 +2107,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M10">
-        <v>25.31030921383209</v>
+        <v>28.4740978655611</v>
       </c>
       <c r="N10">
-        <v>599.3754050718821</v>
+        <v>596.2116164201531</v>
       </c>
       <c r="O10">
-        <v>149.4842260249274</v>
+        <v>148.6951771351862</v>
       </c>
       <c r="P10">
-        <v>449.8911790469547</v>
+        <v>447.5164392849669</v>
       </c>
       <c r="Q10">
-        <v>519.4911790469548</v>
+        <v>517.1164392849669</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08148728528123564</v>
+        <v>0.08178763922142497</v>
       </c>
       <c r="T10">
-        <v>0.8241867270493218</v>
+        <v>0.8311233076541563</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.68107793579714</v>
+        <v>21.93873594293079</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07782471789149673</v>
+        <v>0.07766071892425666</v>
       </c>
       <c r="C11">
-        <v>5583.333770600742</v>
+        <v>5534.429476119833</v>
       </c>
       <c r="D11">
-        <v>5467.119215244104</v>
+        <v>5481.113303501346</v>
       </c>
       <c r="E11">
-        <v>-1816.352829171771</v>
+        <v>-1753.45444643362</v>
       </c>
       <c r="F11">
-        <v>566.0854446433618</v>
+        <v>628.9838273815132</v>
       </c>
       <c r="G11">
         <v>682.3</v>
@@ -2189,28 +2189,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M11">
-        <v>28.4740978655611</v>
+        <v>31.63788651729011</v>
       </c>
       <c r="N11">
-        <v>596.2116164201531</v>
+        <v>593.0478277684241</v>
       </c>
       <c r="O11">
-        <v>148.6951771351862</v>
+        <v>147.906128245445</v>
       </c>
       <c r="P11">
-        <v>447.5164392849669</v>
+        <v>445.1416995229791</v>
       </c>
       <c r="Q11">
-        <v>517.1164392849669</v>
+        <v>514.7416995229792</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08178763922142497</v>
+        <v>0.08209466769361851</v>
       </c>
       <c r="T11">
-        <v>0.8311233076541563</v>
+        <v>0.8382140344946536</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.93873594293079</v>
+        <v>19.74486234863771</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07766071892425666</v>
+        <v>0.0774967199570166</v>
       </c>
       <c r="C12">
-        <v>5534.429476119833</v>
+        <v>5485.597006327188</v>
       </c>
       <c r="D12">
-        <v>5481.113303501346</v>
+        <v>5495.179216446852</v>
       </c>
       <c r="E12">
-        <v>-1753.454446433619</v>
+        <v>-1690.556063695468</v>
       </c>
       <c r="F12">
-        <v>628.9838273815133</v>
+        <v>691.8822101196646</v>
       </c>
       <c r="G12">
         <v>682.3</v>
@@ -2271,28 +2271,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M12">
-        <v>31.63788651729012</v>
+        <v>34.80167516901913</v>
       </c>
       <c r="N12">
-        <v>593.0478277684241</v>
+        <v>589.884039116695</v>
       </c>
       <c r="O12">
-        <v>147.906128245445</v>
+        <v>147.1170793557037</v>
       </c>
       <c r="P12">
-        <v>445.1416995229791</v>
+        <v>442.7669597609913</v>
       </c>
       <c r="Q12">
-        <v>514.7416995229792</v>
+        <v>512.3669597609913</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08209466769361851</v>
+        <v>0.08240859568204112</v>
       </c>
       <c r="T12">
-        <v>0.8382140344946536</v>
+        <v>0.845464103511342</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.74486234863771</v>
+        <v>17.94987486239792</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0774967199570166</v>
+        <v>0.0773327209897765</v>
       </c>
       <c r="C13">
-        <v>5485.597006327188</v>
+        <v>5436.836915606046</v>
       </c>
       <c r="D13">
-        <v>5495.179216446852</v>
+        <v>5509.317508463861</v>
       </c>
       <c r="E13">
-        <v>-1690.556063695468</v>
+        <v>-1627.657680957317</v>
       </c>
       <c r="F13">
-        <v>691.8822101196646</v>
+        <v>754.7805928578158</v>
       </c>
       <c r="G13">
         <v>682.3</v>
@@ -2353,28 +2353,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M13">
-        <v>34.80167516901913</v>
+        <v>37.96546382074813</v>
       </c>
       <c r="N13">
-        <v>589.884039116695</v>
+        <v>586.7202504649661</v>
       </c>
       <c r="O13">
-        <v>147.1170793557037</v>
+        <v>146.3280304659625</v>
       </c>
       <c r="P13">
-        <v>442.7669597609913</v>
+        <v>440.3922199990035</v>
       </c>
       <c r="Q13">
-        <v>512.3669597609913</v>
+        <v>509.9922199990035</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08240859568204112</v>
+        <v>0.08272965839747332</v>
       </c>
       <c r="T13">
-        <v>0.845464103511342</v>
+        <v>0.8528789468238643</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.94987486239792</v>
+        <v>16.45405195719809</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0773327209897765</v>
+        <v>0.07716872202253645</v>
       </c>
       <c r="C14">
-        <v>5436.836915606046</v>
+        <v>5388.149764059744</v>
       </c>
       <c r="D14">
-        <v>5509.317508463861</v>
+        <v>5523.528739655711</v>
       </c>
       <c r="E14">
-        <v>-1627.657680957317</v>
+        <v>-1564.759298219165</v>
       </c>
       <c r="F14">
-        <v>754.7805928578158</v>
+        <v>817.6789755959672</v>
       </c>
       <c r="G14">
         <v>682.3</v>
@@ -2435,28 +2435,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M14">
-        <v>37.96546382074813</v>
+        <v>41.12925247247715</v>
       </c>
       <c r="N14">
-        <v>586.7202504649661</v>
+        <v>583.5564618132371</v>
       </c>
       <c r="O14">
-        <v>146.3280304659625</v>
+        <v>145.5389815762213</v>
       </c>
       <c r="P14">
-        <v>440.3922199990035</v>
+        <v>438.0174802370158</v>
       </c>
       <c r="Q14">
-        <v>509.9922199990035</v>
+        <v>507.6174802370158</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08272965839747332</v>
+        <v>0.08305810186498444</v>
       </c>
       <c r="T14">
-        <v>0.8528789468238643</v>
+        <v>0.8604642463044906</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.45405195719809</v>
+        <v>15.18835565279824</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07716872202253645</v>
+        <v>0.07700472305529639</v>
       </c>
       <c r="C15">
-        <v>5388.149764059744</v>
+        <v>5339.536117585702</v>
       </c>
       <c r="D15">
-        <v>5523.528739655711</v>
+        <v>5537.81347591982</v>
       </c>
       <c r="E15">
-        <v>-1564.759298219165</v>
+        <v>-1501.860915481014</v>
       </c>
       <c r="F15">
-        <v>817.6789755959672</v>
+        <v>880.5773583341186</v>
       </c>
       <c r="G15">
         <v>682.3</v>
@@ -2517,28 +2517,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M15">
-        <v>41.12925247247715</v>
+        <v>44.29304112420616</v>
       </c>
       <c r="N15">
-        <v>583.5564618132371</v>
+        <v>580.392673161508</v>
       </c>
       <c r="O15">
-        <v>145.5389815762213</v>
+        <v>144.7499326864801</v>
       </c>
       <c r="P15">
-        <v>438.0174802370158</v>
+        <v>435.6427404750279</v>
       </c>
       <c r="Q15">
-        <v>507.6174802370158</v>
+        <v>505.242740475028</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08305810186498444</v>
+        <v>0.08339418355267023</v>
       </c>
       <c r="T15">
-        <v>0.8604642463044906</v>
+        <v>0.8682259480986197</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.18835565279824</v>
+        <v>14.10347310616979</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07700472305529639</v>
+        <v>0.07684072408805633</v>
       </c>
       <c r="C16">
-        <v>5339.536117585702</v>
+        <v>5290.996547950519</v>
       </c>
       <c r="D16">
-        <v>5537.81347591982</v>
+        <v>5552.172289022788</v>
       </c>
       <c r="E16">
-        <v>-1501.860915481014</v>
+        <v>-1438.962532742863</v>
       </c>
       <c r="F16">
-        <v>880.5773583341186</v>
+        <v>943.47574107227</v>
       </c>
       <c r="G16">
         <v>682.3</v>
@@ -2599,28 +2599,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M16">
-        <v>44.29304112420616</v>
+        <v>47.45682977593518</v>
       </c>
       <c r="N16">
-        <v>580.392673161508</v>
+        <v>577.228884509779</v>
       </c>
       <c r="O16">
-        <v>144.7499326864801</v>
+        <v>143.9608837967389</v>
       </c>
       <c r="P16">
-        <v>435.6427404750279</v>
+        <v>433.2680007130401</v>
       </c>
       <c r="Q16">
-        <v>505.242740475028</v>
+        <v>502.8680007130401</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08339418355267023</v>
+        <v>0.08373817304477216</v>
       </c>
       <c r="T16">
-        <v>0.8682259480986197</v>
+        <v>0.8761702781702577</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.10347310616979</v>
+        <v>13.16324156575847</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07684072408805633</v>
+        <v>0.07685686912081628</v>
       </c>
       <c r="C17">
-        <v>5290.996547950519</v>
+        <v>5226.681294811111</v>
       </c>
       <c r="D17">
-        <v>5552.172289022788</v>
+        <v>5550.755418621532</v>
       </c>
       <c r="E17">
-        <v>-1438.962532742863</v>
+        <v>-1376.064150004711</v>
       </c>
       <c r="F17">
-        <v>943.4757410722698</v>
+        <v>1006.374123810421</v>
       </c>
       <c r="G17">
         <v>682.3</v>
@@ -2681,45 +2681,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M17">
-        <v>47.45682977593517</v>
+        <v>52.13017961337982</v>
       </c>
       <c r="N17">
-        <v>577.228884509779</v>
+        <v>572.5555346723344</v>
       </c>
       <c r="O17">
-        <v>143.9608837967389</v>
+        <v>142.7953503472802</v>
       </c>
       <c r="P17">
-        <v>433.2680007130401</v>
+        <v>429.7601843250542</v>
       </c>
       <c r="Q17">
-        <v>502.8680007130401</v>
+        <v>499.3601843250542</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08373817304477216</v>
+        <v>0.08409035276287652</v>
       </c>
       <c r="T17">
-        <v>0.8761702781702577</v>
+        <v>0.8843037589578872</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.2494</v>
       </c>
       <c r="W17">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.16324156575847</v>
+        <v>11.98318745338413</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07685686912081628</v>
+        <v>0.07670412915357622</v>
       </c>
       <c r="C18">
-        <v>5226.681294811111</v>
+        <v>5177.216214981912</v>
       </c>
       <c r="D18">
-        <v>5550.755418621532</v>
+        <v>5564.188721530485</v>
       </c>
       <c r="E18">
-        <v>-1376.064150004711</v>
+        <v>-1313.16576726656</v>
       </c>
       <c r="F18">
-        <v>1006.374123810421</v>
+        <v>1069.272506548572</v>
       </c>
       <c r="G18">
         <v>682.3</v>
@@ -2763,28 +2763,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M18">
-        <v>52.13017961337982</v>
+        <v>55.38831583921605</v>
       </c>
       <c r="N18">
-        <v>572.5555346723344</v>
+        <v>569.2973984464982</v>
       </c>
       <c r="O18">
-        <v>142.7953503472802</v>
+        <v>141.9827711725567</v>
       </c>
       <c r="P18">
-        <v>429.7601843250542</v>
+        <v>427.3146272739415</v>
       </c>
       <c r="Q18">
-        <v>499.3601843250542</v>
+        <v>496.9146272739415</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08409035276287652</v>
+        <v>0.08445101873924846</v>
       </c>
       <c r="T18">
-        <v>0.8843037589578872</v>
+        <v>0.8926332272343753</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.98318745338413</v>
+        <v>11.2782940737733</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07670412915357622</v>
+        <v>0.07655138918633614</v>
       </c>
       <c r="C19">
-        <v>5177.216214981912</v>
+        <v>5127.816312371333</v>
       </c>
       <c r="D19">
-        <v>5564.188721530485</v>
+        <v>5577.687201658056</v>
       </c>
       <c r="E19">
-        <v>-1313.16576726656</v>
+        <v>-1250.267384528409</v>
       </c>
       <c r="F19">
-        <v>1069.272506548572</v>
+        <v>1132.170889286724</v>
       </c>
       <c r="G19">
         <v>682.3</v>
@@ -2845,28 +2845,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M19">
-        <v>55.38831583921605</v>
+        <v>58.64645206505229</v>
       </c>
       <c r="N19">
-        <v>569.2973984464982</v>
+        <v>566.039262220662</v>
       </c>
       <c r="O19">
-        <v>141.9827711725567</v>
+        <v>141.1701919978331</v>
       </c>
       <c r="P19">
-        <v>427.3146272739415</v>
+        <v>424.8690702228289</v>
       </c>
       <c r="Q19">
-        <v>496.9146272739415</v>
+        <v>494.4690702228289</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08445101873924846</v>
+        <v>0.08482048144675139</v>
       </c>
       <c r="T19">
-        <v>0.8926332272343753</v>
+        <v>0.9011658532737044</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.2782940737733</v>
+        <v>10.65172218078589</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07655138918633615</v>
+        <v>0.07639864921909609</v>
       </c>
       <c r="C20">
-        <v>5127.816312371332</v>
+        <v>5078.482062484225</v>
       </c>
       <c r="D20">
-        <v>5577.687201658056</v>
+        <v>5591.2513345091</v>
       </c>
       <c r="E20">
-        <v>-1250.267384528409</v>
+        <v>-1187.369001790257</v>
       </c>
       <c r="F20">
-        <v>1132.170889286724</v>
+        <v>1195.069272024875</v>
       </c>
       <c r="G20">
         <v>682.3</v>
@@ -2927,28 +2927,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M20">
-        <v>58.64645206505229</v>
+        <v>61.90458829088853</v>
       </c>
       <c r="N20">
-        <v>566.039262220662</v>
+        <v>562.7811259948256</v>
       </c>
       <c r="O20">
-        <v>141.1701919978331</v>
+        <v>140.3576128231095</v>
       </c>
       <c r="P20">
-        <v>424.8690702228289</v>
+        <v>422.4235131717161</v>
       </c>
       <c r="Q20">
-        <v>494.4690702228289</v>
+        <v>492.0235131717161</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08482048144675139</v>
+        <v>0.08519906669024208</v>
       </c>
       <c r="T20">
-        <v>0.9011658532737044</v>
+        <v>0.9099091614374614</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.6517221807859</v>
+        <v>10.09110522390243</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07639864921909609</v>
+        <v>0.07650111325185602</v>
       </c>
       <c r="C21">
-        <v>5078.482062484225</v>
+        <v>5006.477049120947</v>
       </c>
       <c r="D21">
-        <v>5591.2513345091</v>
+        <v>5582.144703883974</v>
       </c>
       <c r="E21">
-        <v>-1187.369001790257</v>
+        <v>-1124.470619052106</v>
       </c>
       <c r="F21">
-        <v>1195.069272024875</v>
+        <v>1257.967654763027</v>
       </c>
       <c r="G21">
         <v>682.3</v>
@@ -3009,45 +3009,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M21">
-        <v>61.90458829088853</v>
+        <v>67.30126952982192</v>
       </c>
       <c r="N21">
-        <v>562.7811259948256</v>
+        <v>557.3844447558922</v>
       </c>
       <c r="O21">
-        <v>140.3576128231095</v>
+        <v>139.0116805221195</v>
       </c>
       <c r="P21">
-        <v>422.4235131717161</v>
+        <v>418.3727642337727</v>
       </c>
       <c r="Q21">
-        <v>492.0235131717161</v>
+        <v>487.9727642337728</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08519906669024208</v>
+        <v>0.08558711656482003</v>
       </c>
       <c r="T21">
-        <v>0.9099091614374614</v>
+        <v>0.9188710523053125</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.09110522390243</v>
+        <v>9.281930618097912</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07650111325185602</v>
+        <v>0.07636113348461597</v>
       </c>
       <c r="C22">
-        <v>5006.477049120947</v>
+        <v>4956.02699455525</v>
       </c>
       <c r="D22">
-        <v>5582.144703883974</v>
+        <v>5594.593032056428</v>
       </c>
       <c r="E22">
-        <v>-1124.470619052106</v>
+        <v>-1061.572236313955</v>
       </c>
       <c r="F22">
-        <v>1257.967654763027</v>
+        <v>1320.866037501178</v>
       </c>
       <c r="G22">
         <v>682.3</v>
@@ -3091,28 +3091,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M22">
-        <v>67.30126952982192</v>
+        <v>70.66633300631302</v>
       </c>
       <c r="N22">
-        <v>557.3844447558922</v>
+        <v>554.0193812794012</v>
       </c>
       <c r="O22">
-        <v>139.0116805221195</v>
+        <v>138.1724336910827</v>
       </c>
       <c r="P22">
-        <v>418.3727642337727</v>
+        <v>415.8469475883185</v>
       </c>
       <c r="Q22">
-        <v>487.9727642337728</v>
+        <v>485.4469475883185</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08558711656482003</v>
+        <v>0.08598499048685565</v>
       </c>
       <c r="T22">
-        <v>0.9188710523053125</v>
+        <v>0.9280598264862736</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.281930618097912</v>
+        <v>8.839933921998011</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07636113348461597</v>
+        <v>0.07622115371737591</v>
       </c>
       <c r="C23">
-        <v>4956.02699455525</v>
+        <v>4905.63258427026</v>
       </c>
       <c r="D23">
-        <v>5594.593032056428</v>
+        <v>5607.097004509589</v>
       </c>
       <c r="E23">
-        <v>-1061.572236313955</v>
+        <v>-998.6738535758034</v>
       </c>
       <c r="F23">
-        <v>1320.866037501178</v>
+        <v>1383.764420239329</v>
       </c>
       <c r="G23">
         <v>682.3</v>
@@ -3173,28 +3173,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M23">
-        <v>70.66633300631301</v>
+        <v>74.03139648280411</v>
       </c>
       <c r="N23">
-        <v>554.0193812794012</v>
+        <v>550.6543178029101</v>
       </c>
       <c r="O23">
-        <v>138.1724336910827</v>
+        <v>137.3331868600458</v>
       </c>
       <c r="P23">
-        <v>415.8469475883185</v>
+        <v>413.3211309428643</v>
       </c>
       <c r="Q23">
-        <v>485.4469475883185</v>
+        <v>482.9211309428644</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08598499048685565</v>
+        <v>0.08639306630432808</v>
       </c>
       <c r="T23">
-        <v>0.9280598264862736</v>
+        <v>0.9374842102616183</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.839933921998012</v>
+        <v>8.438118743725376</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07622115371737591</v>
+        <v>0.07608117395013583</v>
       </c>
       <c r="C24">
-        <v>4905.63258427026</v>
+        <v>4855.294192198324</v>
       </c>
       <c r="D24">
-        <v>5607.097004509589</v>
+        <v>5619.656995175804</v>
       </c>
       <c r="E24">
-        <v>-998.6738535758034</v>
+        <v>-935.7754708376522</v>
       </c>
       <c r="F24">
-        <v>1383.764420239329</v>
+        <v>1446.66280297748</v>
       </c>
       <c r="G24">
         <v>682.3</v>
@@ -3255,28 +3255,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M24">
-        <v>74.03139648280411</v>
+        <v>77.3964599592952</v>
       </c>
       <c r="N24">
-        <v>550.6543178029101</v>
+        <v>547.289254326419</v>
       </c>
       <c r="O24">
-        <v>137.3331868600458</v>
+        <v>136.4939400290089</v>
       </c>
       <c r="P24">
-        <v>413.3211309428643</v>
+        <v>410.7953142974101</v>
       </c>
       <c r="Q24">
-        <v>482.9211309428644</v>
+        <v>480.3953142974102</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08639306630432808</v>
+        <v>0.0868117414936829</v>
       </c>
       <c r="T24">
-        <v>0.9374842102616183</v>
+        <v>0.947153383225933</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.438118743725376</v>
+        <v>8.071244015737317</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07608117395013583</v>
+        <v>0.07594119418289577</v>
       </c>
       <c r="C25">
-        <v>4855.294192198324</v>
+        <v>4805.012195629765</v>
       </c>
       <c r="D25">
-        <v>5619.656995175804</v>
+        <v>5632.273381345397</v>
       </c>
       <c r="E25">
-        <v>-935.7754708376522</v>
+        <v>-872.8770880995007</v>
       </c>
       <c r="F25">
-        <v>1446.66280297748</v>
+        <v>1509.561185715632</v>
       </c>
       <c r="G25">
         <v>682.3</v>
@@ -3337,28 +3337,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M25">
-        <v>77.3964599592952</v>
+        <v>80.7615234357863</v>
       </c>
       <c r="N25">
-        <v>547.289254326419</v>
+        <v>543.9241908499279</v>
       </c>
       <c r="O25">
-        <v>136.4939400290089</v>
+        <v>135.654693197972</v>
       </c>
       <c r="P25">
-        <v>410.7953142974101</v>
+        <v>408.2694976519558</v>
       </c>
       <c r="Q25">
-        <v>480.3953142974102</v>
+        <v>477.8694976519558</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0868117414936829</v>
+        <v>0.08724143445117864</v>
       </c>
       <c r="T25">
-        <v>0.947153383225933</v>
+        <v>0.9570770081103613</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.071244015737317</v>
+        <v>7.73494218174826</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07594119418289577</v>
+        <v>0.0759513344156557</v>
       </c>
       <c r="C26">
-        <v>4805.012195629765</v>
+        <v>4741.197970116047</v>
       </c>
       <c r="D26">
-        <v>5632.273381345397</v>
+        <v>5631.35753856983</v>
       </c>
       <c r="E26">
-        <v>-872.877088099501</v>
+        <v>-809.9787053613495</v>
       </c>
       <c r="F26">
-        <v>1509.561185715632</v>
+        <v>1572.459568453783</v>
       </c>
       <c r="G26">
         <v>682.3</v>
@@ -3419,45 +3419,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M26">
-        <v>80.76152343578629</v>
+        <v>85.38455456704042</v>
       </c>
       <c r="N26">
-        <v>543.9241908499279</v>
+        <v>539.3011597186737</v>
       </c>
       <c r="O26">
-        <v>135.654693197972</v>
+        <v>134.5017092338372</v>
       </c>
       <c r="P26">
-        <v>408.2694976519558</v>
+        <v>404.7994504848365</v>
       </c>
       <c r="Q26">
-        <v>477.8694976519558</v>
+        <v>474.3994504848365</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08724143445117864</v>
+        <v>0.08768258588754094</v>
       </c>
       <c r="T26">
-        <v>0.9570770081103613</v>
+        <v>0.9672652629917076</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.734942181748262</v>
+        <v>7.316144207266863</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0759513344156557</v>
+        <v>0.07581735944841562</v>
       </c>
       <c r="C27">
-        <v>4741.197970116047</v>
+        <v>4690.423982243657</v>
       </c>
       <c r="D27">
-        <v>5631.35753856983</v>
+        <v>5643.481933435591</v>
       </c>
       <c r="E27">
-        <v>-809.9787053613495</v>
+        <v>-747.0803226231981</v>
       </c>
       <c r="F27">
-        <v>1572.459568453783</v>
+        <v>1635.357951191934</v>
       </c>
       <c r="G27">
         <v>682.3</v>
@@ -3501,28 +3501,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M27">
-        <v>85.38455456704042</v>
+        <v>88.79993674972205</v>
       </c>
       <c r="N27">
-        <v>539.3011597186737</v>
+        <v>535.8857775359921</v>
       </c>
       <c r="O27">
-        <v>134.5017092338372</v>
+        <v>133.6499129174765</v>
       </c>
       <c r="P27">
-        <v>404.7994504848365</v>
+        <v>402.2358646185157</v>
       </c>
       <c r="Q27">
-        <v>474.3994504848365</v>
+        <v>471.8358646185157</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08768258588754094</v>
+        <v>0.08813566033569681</v>
       </c>
       <c r="T27">
-        <v>0.9672652629917076</v>
+        <v>0.9777288761130905</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.316144207266863</v>
+        <v>7.034754045448906</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07581735944841562</v>
+        <v>0.07568338448117558</v>
       </c>
       <c r="C28">
-        <v>4690.423982243657</v>
+        <v>4639.702315016127</v>
       </c>
       <c r="D28">
-        <v>5643.481933435591</v>
+        <v>5655.658648946212</v>
       </c>
       <c r="E28">
-        <v>-747.0803226231981</v>
+        <v>-684.1819398850469</v>
       </c>
       <c r="F28">
-        <v>1635.357951191934</v>
+        <v>1698.256333930086</v>
       </c>
       <c r="G28">
         <v>682.3</v>
@@ -3583,28 +3583,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M28">
-        <v>88.79993674972205</v>
+        <v>92.21531893240366</v>
       </c>
       <c r="N28">
-        <v>535.8857775359921</v>
+        <v>532.4703953533106</v>
       </c>
       <c r="O28">
-        <v>133.6499129174765</v>
+        <v>132.7981166011157</v>
       </c>
       <c r="P28">
-        <v>402.2358646185157</v>
+        <v>399.6722787521949</v>
       </c>
       <c r="Q28">
-        <v>471.8358646185157</v>
+        <v>469.2722787521949</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08813566033569681</v>
+        <v>0.0886011477824323</v>
       </c>
       <c r="T28">
-        <v>0.9777288761130905</v>
+        <v>0.9884791635665657</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.034754045448906</v>
+        <v>6.774207599321169</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07568338448117558</v>
+        <v>0.07554940951393552</v>
       </c>
       <c r="C29">
-        <v>4639.702315016127</v>
+        <v>4589.033307836275</v>
       </c>
       <c r="D29">
-        <v>5655.658648946212</v>
+        <v>5667.888024504511</v>
       </c>
       <c r="E29">
-        <v>-684.1819398850469</v>
+        <v>-621.2835571468954</v>
       </c>
       <c r="F29">
-        <v>1698.256333930086</v>
+        <v>1761.154716668237</v>
       </c>
       <c r="G29">
         <v>682.3</v>
@@ -3665,28 +3665,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M29">
-        <v>92.21531893240366</v>
+        <v>95.63070111508527</v>
       </c>
       <c r="N29">
-        <v>532.4703953533106</v>
+        <v>529.055013170629</v>
       </c>
       <c r="O29">
-        <v>132.7981166011157</v>
+        <v>131.9463202847549</v>
       </c>
       <c r="P29">
-        <v>399.6722787521949</v>
+        <v>397.1086928858741</v>
       </c>
       <c r="Q29">
-        <v>469.2722787521949</v>
+        <v>466.7086928858741</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0886011477824323</v>
+        <v>0.08907956543602155</v>
       </c>
       <c r="T29">
-        <v>0.9884791635665657</v>
+        <v>0.9995280701159711</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.774207599321169</v>
+        <v>6.532271613631129</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07554940951393552</v>
+        <v>0.07541543454669544</v>
       </c>
       <c r="C30">
-        <v>4589.033307836275</v>
+        <v>4538.417303048869</v>
       </c>
       <c r="D30">
-        <v>5667.888024504511</v>
+        <v>5680.170402455257</v>
       </c>
       <c r="E30">
-        <v>-621.2835571468954</v>
+        <v>-558.385174408744</v>
       </c>
       <c r="F30">
-        <v>1761.154716668237</v>
+        <v>1824.053099406389</v>
       </c>
       <c r="G30">
         <v>682.3</v>
@@ -3747,28 +3747,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M30">
-        <v>95.63070111508527</v>
+        <v>99.0460832977669</v>
       </c>
       <c r="N30">
-        <v>529.055013170629</v>
+        <v>525.6396309879473</v>
       </c>
       <c r="O30">
-        <v>131.9463202847549</v>
+        <v>131.094523968394</v>
       </c>
       <c r="P30">
-        <v>397.1086928858741</v>
+        <v>394.5451070195533</v>
       </c>
       <c r="Q30">
-        <v>466.7086928858741</v>
+        <v>464.1451070195533</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08907956543602155</v>
+        <v>0.08957145964323304</v>
       </c>
       <c r="T30">
-        <v>0.9995280701159711</v>
+        <v>1.010888213469585</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.532271613631129</v>
+        <v>6.307020868333503</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07541543454669544</v>
+        <v>0.07550663957945539</v>
       </c>
       <c r="C31">
-        <v>4538.417303048869</v>
+        <v>4467.151771420777</v>
       </c>
       <c r="D31">
-        <v>5680.170402455257</v>
+        <v>5671.803253565316</v>
       </c>
       <c r="E31">
-        <v>-558.3851744087444</v>
+        <v>-495.486791670593</v>
       </c>
       <c r="F31">
-        <v>1824.053099406388</v>
+        <v>1886.95148214454</v>
       </c>
       <c r="G31">
         <v>682.3</v>
@@ -3829,45 +3829,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M31">
-        <v>99.04608329776688</v>
+        <v>104.348416962593</v>
       </c>
       <c r="N31">
-        <v>525.6396309879473</v>
+        <v>520.3372973231212</v>
       </c>
       <c r="O31">
-        <v>131.094523968394</v>
+        <v>129.7721219523864</v>
       </c>
       <c r="P31">
-        <v>394.5451070195533</v>
+        <v>390.5651753707348</v>
       </c>
       <c r="Q31">
-        <v>464.1451070195533</v>
+        <v>460.1651753707348</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08957145964323303</v>
+        <v>0.09007740797065056</v>
       </c>
       <c r="T31">
-        <v>1.010888213469585</v>
+        <v>1.022572932347588</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.2494</v>
       </c>
       <c r="W31">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.307020868333503</v>
+        <v>5.986537529454352</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07550663957945539</v>
+        <v>0.07538017061221532</v>
       </c>
       <c r="C32">
-        <v>4467.151771420777</v>
+        <v>4415.862272142615</v>
       </c>
       <c r="D32">
-        <v>5671.803253565316</v>
+        <v>5683.412137025306</v>
       </c>
       <c r="E32">
-        <v>-495.486791670593</v>
+        <v>-432.5884089324416</v>
       </c>
       <c r="F32">
-        <v>1886.95148214454</v>
+        <v>1949.849864882691</v>
       </c>
       <c r="G32">
         <v>682.3</v>
@@ -3911,28 +3911,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M32">
-        <v>104.348416962593</v>
+        <v>107.8266975280128</v>
       </c>
       <c r="N32">
-        <v>520.3372973231212</v>
+        <v>516.8590167577014</v>
       </c>
       <c r="O32">
-        <v>129.7721219523864</v>
+        <v>128.9046387793707</v>
       </c>
       <c r="P32">
-        <v>390.5651753707348</v>
+        <v>387.9543779783306</v>
       </c>
       <c r="Q32">
-        <v>460.1651753707348</v>
+        <v>457.5543779783306</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09007740797065056</v>
+        <v>0.09059802146697873</v>
       </c>
       <c r="T32">
-        <v>1.022572932347588</v>
+        <v>1.034596338729301</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.986537529454352</v>
+        <v>5.793423415600985</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07538017061221532</v>
+        <v>0.07525370164497526</v>
       </c>
       <c r="C33">
-        <v>4415.862272142615</v>
+        <v>4364.620391785776</v>
       </c>
       <c r="D33">
-        <v>5683.412137025306</v>
+        <v>5695.068639406618</v>
       </c>
       <c r="E33">
-        <v>-432.5884089324416</v>
+        <v>-369.6900261942901</v>
       </c>
       <c r="F33">
-        <v>1949.849864882691</v>
+        <v>2012.748247620842</v>
       </c>
       <c r="G33">
         <v>682.3</v>
@@ -3993,28 +3993,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M33">
-        <v>107.8266975280128</v>
+        <v>111.3049780934326</v>
       </c>
       <c r="N33">
-        <v>516.8590167577014</v>
+        <v>513.3807361922816</v>
       </c>
       <c r="O33">
-        <v>128.9046387793707</v>
+        <v>128.037155606355</v>
       </c>
       <c r="P33">
-        <v>387.9543779783306</v>
+        <v>385.3435805859265</v>
       </c>
       <c r="Q33">
-        <v>457.5543779783306</v>
+        <v>454.9435805859266</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09059802146697873</v>
+        <v>0.09113394712496362</v>
       </c>
       <c r="T33">
-        <v>1.034596338729301</v>
+        <v>1.046973374710476</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.793423415600985</v>
+        <v>5.612378933863453</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07525370164497526</v>
+        <v>0.0751272326777352</v>
       </c>
       <c r="C34">
-        <v>4364.620391785776</v>
+        <v>4313.426423947218</v>
       </c>
       <c r="D34">
-        <v>5695.068639406618</v>
+        <v>5706.773054306211</v>
       </c>
       <c r="E34">
-        <v>-369.6900261942901</v>
+        <v>-306.7916434561389</v>
       </c>
       <c r="F34">
-        <v>2012.748247620842</v>
+        <v>2075.646630358994</v>
       </c>
       <c r="G34">
         <v>682.3</v>
@@ -4075,28 +4075,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M34">
-        <v>111.3049780934326</v>
+        <v>114.7832586588523</v>
       </c>
       <c r="N34">
-        <v>513.3807361922816</v>
+        <v>509.9024556268619</v>
       </c>
       <c r="O34">
-        <v>128.037155606355</v>
+        <v>127.1696724333394</v>
       </c>
       <c r="P34">
-        <v>385.3435805859265</v>
+        <v>382.7327831935225</v>
       </c>
       <c r="Q34">
-        <v>454.9435805859266</v>
+        <v>452.3327831935225</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09113394712496362</v>
+        <v>0.09168587056378388</v>
       </c>
       <c r="T34">
-        <v>1.046973374710476</v>
+        <v>1.059719874452284</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.612378933863453</v>
+        <v>5.442306844958501</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0751272326777352</v>
+        <v>0.07500076371049513</v>
       </c>
       <c r="C35">
-        <v>4313.426423947218</v>
+        <v>4262.280664642453</v>
       </c>
       <c r="D35">
-        <v>5706.773054306211</v>
+        <v>5718.525677739598</v>
       </c>
       <c r="E35">
-        <v>-306.7916434561389</v>
+        <v>-243.8932607179877</v>
       </c>
       <c r="F35">
-        <v>2075.646630358994</v>
+        <v>2138.545013097145</v>
       </c>
       <c r="G35">
         <v>682.3</v>
@@ -4157,28 +4157,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M35">
-        <v>114.7832586588523</v>
+        <v>118.2615392242721</v>
       </c>
       <c r="N35">
-        <v>509.9024556268619</v>
+        <v>506.4241750614421</v>
       </c>
       <c r="O35">
-        <v>127.1696724333394</v>
+        <v>126.3021892603237</v>
       </c>
       <c r="P35">
-        <v>382.7327831935225</v>
+        <v>380.1219858011185</v>
       </c>
       <c r="Q35">
-        <v>452.3327831935225</v>
+        <v>449.7219858011185</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09168587056378388</v>
+        <v>0.09225451895529566</v>
       </c>
       <c r="T35">
-        <v>1.059719874452284</v>
+        <v>1.072852631762024</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.442306844958501</v>
+        <v>5.282238996577369</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07500076371049513</v>
+        <v>0.07487429474325506</v>
       </c>
       <c r="C36">
-        <v>4262.280664642453</v>
+        <v>4211.183412330508</v>
       </c>
       <c r="D36">
-        <v>5718.525677739598</v>
+        <v>5730.326808165804</v>
       </c>
       <c r="E36">
-        <v>-243.8932607179877</v>
+        <v>-180.994877979836</v>
       </c>
       <c r="F36">
-        <v>2138.545013097145</v>
+        <v>2201.443395835297</v>
       </c>
       <c r="G36">
         <v>682.3</v>
@@ -4239,28 +4239,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M36">
-        <v>118.2615392242721</v>
+        <v>121.7398197896919</v>
       </c>
       <c r="N36">
-        <v>506.4241750614421</v>
+        <v>502.9458944960223</v>
       </c>
       <c r="O36">
-        <v>126.3021892603237</v>
+        <v>125.434706087308</v>
       </c>
       <c r="P36">
-        <v>380.1219858011185</v>
+        <v>377.5111884087143</v>
       </c>
       <c r="Q36">
-        <v>449.7219858011185</v>
+        <v>447.1111884087143</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09225451895529566</v>
+        <v>0.09284066422039242</v>
       </c>
       <c r="T36">
-        <v>1.072852631762024</v>
+        <v>1.086389473912065</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.282238996577369</v>
+        <v>5.131317882389443</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07487429474325506</v>
+        <v>0.07474782577601501</v>
       </c>
       <c r="C37">
-        <v>4211.183412330508</v>
+        <v>4160.134967939175</v>
       </c>
       <c r="D37">
-        <v>5730.326808165804</v>
+        <v>5742.176746512622</v>
       </c>
       <c r="E37">
-        <v>-180.994877979836</v>
+        <v>-118.0964952416848</v>
       </c>
       <c r="F37">
-        <v>2201.443395835297</v>
+        <v>2264.341778573448</v>
       </c>
       <c r="G37">
         <v>682.3</v>
@@ -4321,28 +4321,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M37">
-        <v>121.7398197896919</v>
+        <v>125.2181003551117</v>
       </c>
       <c r="N37">
-        <v>502.9458944960223</v>
+        <v>499.4676139306025</v>
       </c>
       <c r="O37">
-        <v>125.434706087308</v>
+        <v>124.5672229142923</v>
       </c>
       <c r="P37">
-        <v>377.5111884087143</v>
+        <v>374.9003910163102</v>
       </c>
       <c r="Q37">
-        <v>447.1111884087143</v>
+        <v>444.5003910163102</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09284066422039242</v>
+        <v>0.09344512652502346</v>
       </c>
       <c r="T37">
-        <v>1.086389473912065</v>
+        <v>1.100349342379294</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.131317882389443</v>
+        <v>4.988781274545292</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07474782577601502</v>
+        <v>0.07462135680877495</v>
       </c>
       <c r="C38">
-        <v>4160.134967939174</v>
+        <v>4109.135634890607</v>
       </c>
       <c r="D38">
-        <v>5742.176746512621</v>
+        <v>5754.075796202205</v>
       </c>
       <c r="E38">
-        <v>-118.0964952416853</v>
+        <v>-55.19811250353359</v>
       </c>
       <c r="F38">
-        <v>2264.341778573447</v>
+        <v>2327.240161311599</v>
       </c>
       <c r="G38">
         <v>682.3</v>
@@ -4403,28 +4403,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M38">
-        <v>125.2181003551116</v>
+        <v>128.6963809205314</v>
       </c>
       <c r="N38">
-        <v>499.4676139306026</v>
+        <v>495.9893333651828</v>
       </c>
       <c r="O38">
-        <v>124.5672229142923</v>
+        <v>123.6997397412766</v>
       </c>
       <c r="P38">
-        <v>374.9003910163103</v>
+        <v>372.2895936239062</v>
       </c>
       <c r="Q38">
-        <v>444.5003910163103</v>
+        <v>441.8895936239062</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09344512652502346</v>
+        <v>0.09406877810916658</v>
       </c>
       <c r="T38">
-        <v>1.100349342379294</v>
+        <v>1.114752381274055</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.988781274545293</v>
+        <v>4.85394934820623</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07462135680877495</v>
+        <v>0.07449488784153488</v>
       </c>
       <c r="C39">
-        <v>4109.135634890607</v>
+        <v>4058.185719127207</v>
       </c>
       <c r="D39">
-        <v>5754.075796202205</v>
+        <v>5766.024263176957</v>
       </c>
       <c r="E39">
-        <v>-55.19811250353359</v>
+        <v>7.700270234617619</v>
       </c>
       <c r="F39">
-        <v>2327.240161311599</v>
+        <v>2390.13854404975</v>
       </c>
       <c r="G39">
         <v>682.3</v>
@@ -4485,28 +4485,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M39">
-        <v>128.6963809205314</v>
+        <v>132.1746614859512</v>
       </c>
       <c r="N39">
-        <v>495.9893333651828</v>
+        <v>492.511052799763</v>
       </c>
       <c r="O39">
-        <v>123.6997397412766</v>
+        <v>122.8322565682609</v>
       </c>
       <c r="P39">
-        <v>372.2895936239062</v>
+        <v>369.6787962315021</v>
       </c>
       <c r="Q39">
-        <v>441.8895936239062</v>
+        <v>439.2787962315021</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09406877810916658</v>
+        <v>0.09471254748634658</v>
       </c>
       <c r="T39">
-        <v>1.114752381274055</v>
+        <v>1.129620034326711</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.85394934820623</v>
+        <v>4.726213839042908</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07449488784153488</v>
+        <v>0.07436841887429482</v>
       </c>
       <c r="C40">
-        <v>4058.185719127207</v>
+        <v>4007.285529137847</v>
       </c>
       <c r="D40">
-        <v>5766.024263176957</v>
+        <v>5778.022455925749</v>
       </c>
       <c r="E40">
-        <v>7.700270234617619</v>
+        <v>70.59865297276929</v>
       </c>
       <c r="F40">
-        <v>2390.13854404975</v>
+        <v>2453.036926787902</v>
       </c>
       <c r="G40">
         <v>682.3</v>
@@ -4567,28 +4567,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M40">
-        <v>132.1746614859512</v>
+        <v>135.652942051371</v>
       </c>
       <c r="N40">
-        <v>492.511052799763</v>
+        <v>489.0327722343432</v>
       </c>
       <c r="O40">
-        <v>122.8322565682609</v>
+        <v>121.9647733952452</v>
       </c>
       <c r="P40">
-        <v>369.6787962315021</v>
+        <v>367.067998839098</v>
       </c>
       <c r="Q40">
-        <v>439.2787962315021</v>
+        <v>436.667998839098</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09471254748634658</v>
+        <v>0.09537742405622102</v>
       </c>
       <c r="T40">
-        <v>1.129620034326711</v>
+        <v>1.14497515141388</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.726213839042908</v>
+        <v>4.605028868811038</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07436841887429482</v>
+        <v>0.07499254990705476</v>
       </c>
       <c r="C41">
-        <v>4007.285529137847</v>
+        <v>3885.655342294694</v>
       </c>
       <c r="D41">
-        <v>5778.022455925749</v>
+        <v>5719.290651820746</v>
       </c>
       <c r="E41">
-        <v>70.59865297276929</v>
+        <v>133.4970357109205</v>
       </c>
       <c r="F41">
-        <v>2453.036926787902</v>
+        <v>2515.935309526053</v>
       </c>
       <c r="G41">
         <v>682.3</v>
@@ -4649,45 +4649,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M41">
-        <v>135.652942051371</v>
+        <v>145.4210608906059</v>
       </c>
       <c r="N41">
-        <v>489.0327722343432</v>
+        <v>479.2646533951083</v>
       </c>
       <c r="O41">
-        <v>121.9647733952452</v>
+        <v>119.52860455674</v>
       </c>
       <c r="P41">
-        <v>367.067998839098</v>
+        <v>359.7360488383683</v>
       </c>
       <c r="Q41">
-        <v>436.667998839098</v>
+        <v>429.3360488383684</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09537742405622102</v>
+        <v>0.09606446317842458</v>
       </c>
       <c r="T41">
-        <v>1.14497515141388</v>
+        <v>1.160842105737288</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.605028868811038</v>
+        <v>4.295703183981301</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07499254990705476</v>
+        <v>0.07488484593981469</v>
       </c>
       <c r="C42">
-        <v>3885.655342294694</v>
+        <v>3832.806695828588</v>
       </c>
       <c r="D42">
-        <v>5719.290651820746</v>
+        <v>5729.340388092792</v>
       </c>
       <c r="E42">
-        <v>133.4970357109205</v>
+        <v>196.3954184490717</v>
       </c>
       <c r="F42">
-        <v>2515.935309526053</v>
+        <v>2578.833692264204</v>
       </c>
       <c r="G42">
         <v>682.3</v>
@@ -4731,28 +4731,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M42">
-        <v>145.4210608906059</v>
+        <v>149.056587412871</v>
       </c>
       <c r="N42">
-        <v>479.2646533951083</v>
+        <v>475.6291268728432</v>
       </c>
       <c r="O42">
-        <v>119.52860455674</v>
+        <v>118.6219042420871</v>
       </c>
       <c r="P42">
-        <v>359.7360488383683</v>
+        <v>357.0072226307561</v>
       </c>
       <c r="Q42">
-        <v>429.3360488383684</v>
+        <v>426.6072226307561</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09606446317842458</v>
+        <v>0.09677479176239778</v>
       </c>
       <c r="T42">
-        <v>1.160842105737288</v>
+        <v>1.177246922919118</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.295703183981301</v>
+        <v>4.190929935591512</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07488484593981469</v>
+        <v>0.07477714197257462</v>
       </c>
       <c r="C43">
-        <v>3832.806695828588</v>
+        <v>3779.993429617276</v>
       </c>
       <c r="D43">
-        <v>5729.340388092792</v>
+        <v>5739.425504619632</v>
       </c>
       <c r="E43">
-        <v>196.3954184490717</v>
+        <v>259.2938011872234</v>
       </c>
       <c r="F43">
-        <v>2578.833692264204</v>
+        <v>2641.732075002356</v>
       </c>
       <c r="G43">
         <v>682.3</v>
@@ -4813,28 +4813,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M43">
-        <v>149.056587412871</v>
+        <v>152.6921139351362</v>
       </c>
       <c r="N43">
-        <v>475.6291268728432</v>
+        <v>471.993600350578</v>
       </c>
       <c r="O43">
-        <v>118.6219042420871</v>
+        <v>117.7152039274342</v>
       </c>
       <c r="P43">
-        <v>357.0072226307561</v>
+        <v>354.2783964231439</v>
       </c>
       <c r="Q43">
-        <v>426.6072226307561</v>
+        <v>423.8783964231439</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09677479176239778</v>
+        <v>0.0975096144354735</v>
       </c>
       <c r="T43">
-        <v>1.177246922919118</v>
+        <v>1.194217423452044</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.190929935591512</v>
+        <v>4.091145889506</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07477714197257462</v>
+        <v>0.07579909100533455</v>
       </c>
       <c r="C44">
-        <v>3779.993429617277</v>
+        <v>3622.808769490638</v>
       </c>
       <c r="D44">
-        <v>5739.425504619632</v>
+        <v>5645.139227231144</v>
       </c>
       <c r="E44">
-        <v>259.2938011872229</v>
+        <v>322.1921839253741</v>
       </c>
       <c r="F44">
-        <v>2641.732075002355</v>
+        <v>2704.630457740507</v>
       </c>
       <c r="G44">
         <v>682.3</v>
@@ -4895,45 +4895,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M44">
-        <v>152.6921139351361</v>
+        <v>165.7938470594931</v>
       </c>
       <c r="N44">
-        <v>471.993600350578</v>
+        <v>458.8918672262212</v>
       </c>
       <c r="O44">
-        <v>117.7152039274342</v>
+        <v>114.4476316862196</v>
       </c>
       <c r="P44">
-        <v>354.2783964231439</v>
+        <v>344.4442355400016</v>
       </c>
       <c r="Q44">
-        <v>423.8783964231439</v>
+        <v>414.0442355400016</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09750961443547349</v>
+        <v>0.09827022036023607</v>
       </c>
       <c r="T44">
-        <v>1.194217423452044</v>
+        <v>1.21178338014402</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.091145889506</v>
+        <v>3.767846185881395</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07579909100533455</v>
+        <v>0.07571765803809451</v>
       </c>
       <c r="C45">
-        <v>3622.808769490638</v>
+        <v>3567.309754721043</v>
       </c>
       <c r="D45">
-        <v>5645.139227231144</v>
+        <v>5652.538595199701</v>
       </c>
       <c r="E45">
-        <v>322.1921839253741</v>
+        <v>385.0905666635258</v>
       </c>
       <c r="F45">
-        <v>2704.630457740507</v>
+        <v>2767.528840478658</v>
       </c>
       <c r="G45">
         <v>682.3</v>
@@ -4977,28 +4977,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M45">
-        <v>165.7938470594931</v>
+        <v>169.6495179213418</v>
       </c>
       <c r="N45">
-        <v>458.8918672262212</v>
+        <v>455.0361963643725</v>
       </c>
       <c r="O45">
-        <v>114.4476316862196</v>
+        <v>113.4860273732745</v>
       </c>
       <c r="P45">
-        <v>344.4442355400016</v>
+        <v>341.550168991098</v>
       </c>
       <c r="Q45">
-        <v>414.0442355400016</v>
+        <v>411.150168991098</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09827022036023607</v>
+        <v>0.0990579907823116</v>
       </c>
       <c r="T45">
-        <v>1.21178338014402</v>
+        <v>1.229976692432139</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.767846185881395</v>
+        <v>3.682213318020453</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07571765803809451</v>
+        <v>0.07563622507085443</v>
       </c>
       <c r="C46">
-        <v>3567.309754721043</v>
+        <v>3511.830162857687</v>
       </c>
       <c r="D46">
-        <v>5652.538595199701</v>
+        <v>5659.957386074497</v>
       </c>
       <c r="E46">
-        <v>385.0905666635258</v>
+        <v>447.988949401677</v>
       </c>
       <c r="F46">
-        <v>2767.528840478658</v>
+        <v>2830.42722321681</v>
       </c>
       <c r="G46">
         <v>682.3</v>
@@ -5059,28 +5059,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M46">
-        <v>169.6495179213418</v>
+        <v>173.5051887831904</v>
       </c>
       <c r="N46">
-        <v>455.0361963643725</v>
+        <v>451.1805255025238</v>
       </c>
       <c r="O46">
-        <v>113.4860273732745</v>
+        <v>112.5244230603294</v>
       </c>
       <c r="P46">
-        <v>341.550168991098</v>
+        <v>338.6561024421943</v>
       </c>
       <c r="Q46">
-        <v>411.150168991098</v>
+        <v>408.2561024421943</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0990579907823116</v>
+        <v>0.09987440740155351</v>
       </c>
       <c r="T46">
-        <v>1.229976692432139</v>
+        <v>1.248831579712552</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.682213318020453</v>
+        <v>3.600386355397777</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07563622507085443</v>
+        <v>0.07555479210361438</v>
       </c>
       <c r="C47">
-        <v>3511.830162857687</v>
+        <v>3456.370070477053</v>
       </c>
       <c r="D47">
-        <v>5659.957386074497</v>
+        <v>5667.395676432014</v>
       </c>
       <c r="E47">
-        <v>447.988949401677</v>
+        <v>510.8873321398282</v>
       </c>
       <c r="F47">
-        <v>2830.42722321681</v>
+        <v>2893.325605954961</v>
       </c>
       <c r="G47">
         <v>682.3</v>
@@ -5141,28 +5141,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M47">
-        <v>173.5051887831904</v>
+        <v>177.3608596450391</v>
       </c>
       <c r="N47">
-        <v>451.1805255025238</v>
+        <v>447.3248546406751</v>
       </c>
       <c r="O47">
-        <v>112.5244230603294</v>
+        <v>111.5628187473844</v>
       </c>
       <c r="P47">
-        <v>338.6561024421943</v>
+        <v>335.7620358932907</v>
       </c>
       <c r="Q47">
-        <v>408.2561024421943</v>
+        <v>405.3620358932907</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09987440740155351</v>
+        <v>0.10072106167336</v>
       </c>
       <c r="T47">
-        <v>1.248831579712552</v>
+        <v>1.2683847961515</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.600386355397777</v>
+        <v>3.522117086802173</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07555479210361438</v>
+        <v>0.0764611487363743</v>
       </c>
       <c r="C48">
-        <v>3456.370070477053</v>
+        <v>3311.769085054228</v>
       </c>
       <c r="D48">
-        <v>5667.395676432014</v>
+        <v>5585.69307374734</v>
       </c>
       <c r="E48">
-        <v>510.8873321398282</v>
+        <v>573.7857148779799</v>
       </c>
       <c r="F48">
-        <v>2893.325605954961</v>
+        <v>2956.223988693112</v>
       </c>
       <c r="G48">
         <v>682.3</v>
@@ -5223,45 +5223,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M48">
-        <v>177.3608596450391</v>
+        <v>189.4939576752285</v>
       </c>
       <c r="N48">
-        <v>447.3248546406751</v>
+        <v>435.1917566104856</v>
       </c>
       <c r="O48">
-        <v>111.5628187473844</v>
+        <v>108.5368240986551</v>
       </c>
       <c r="P48">
-        <v>335.7620358932907</v>
+        <v>326.6549325118305</v>
       </c>
       <c r="Q48">
-        <v>405.3620358932907</v>
+        <v>396.2549325118305</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.10072106167336</v>
+        <v>0.1015996651629704</v>
       </c>
       <c r="T48">
-        <v>1.2683847961515</v>
+        <v>1.288675869814559</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.2494</v>
       </c>
       <c r="W48">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.522117086802173</v>
+        <v>3.296599648609143</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0764611487363743</v>
+        <v>0.07640073256913424</v>
       </c>
       <c r="C49">
-        <v>3311.769085054228</v>
+        <v>3254.243506585788</v>
       </c>
       <c r="D49">
-        <v>5585.69307374734</v>
+        <v>5591.065878017052</v>
       </c>
       <c r="E49">
-        <v>573.7857148779799</v>
+        <v>636.6840976161311</v>
       </c>
       <c r="F49">
-        <v>2956.223988693112</v>
+        <v>3019.122371431264</v>
       </c>
       <c r="G49">
         <v>682.3</v>
@@ -5305,28 +5305,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M49">
-        <v>189.4939576752285</v>
+        <v>193.525744008744</v>
       </c>
       <c r="N49">
-        <v>435.1917566104856</v>
+        <v>431.1599702769702</v>
       </c>
       <c r="O49">
-        <v>108.5368240986551</v>
+        <v>107.5312965870764</v>
       </c>
       <c r="P49">
-        <v>326.6549325118305</v>
+        <v>323.6286736898938</v>
       </c>
       <c r="Q49">
-        <v>396.2549325118305</v>
+        <v>393.2286736898938</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1015996651629704</v>
+        <v>0.1025120610944889</v>
       </c>
       <c r="T49">
-        <v>1.288675869814559</v>
+        <v>1.309747369387735</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.296599648609143</v>
+        <v>3.227920489263119</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07640073256913424</v>
+        <v>0.07634031640189419</v>
       </c>
       <c r="C50">
-        <v>3254.243506585789</v>
+        <v>3196.728274127728</v>
       </c>
       <c r="D50">
-        <v>5591.065878017052</v>
+        <v>5596.449028297143</v>
       </c>
       <c r="E50">
-        <v>636.6840976161307</v>
+        <v>699.5824803542823</v>
       </c>
       <c r="F50">
-        <v>3019.122371431263</v>
+        <v>3082.020754169415</v>
       </c>
       <c r="G50">
         <v>682.3</v>
@@ -5387,28 +5387,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M50">
-        <v>193.525744008744</v>
+        <v>197.5575303422595</v>
       </c>
       <c r="N50">
-        <v>431.1599702769702</v>
+        <v>427.1281839434547</v>
       </c>
       <c r="O50">
-        <v>107.5312965870764</v>
+        <v>106.5257690754976</v>
       </c>
       <c r="P50">
-        <v>323.6286736898938</v>
+        <v>320.6024148679571</v>
       </c>
       <c r="Q50">
-        <v>393.2286736898938</v>
+        <v>390.2024148679571</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1025120610944889</v>
+        <v>0.1034602372586161</v>
       </c>
       <c r="T50">
-        <v>1.309747369387735</v>
+        <v>1.331645202277507</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.227920489263119</v>
+        <v>3.162044560910811</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07634031640189419</v>
+        <v>0.07627990023465411</v>
       </c>
       <c r="C51">
-        <v>3196.728274127728</v>
+        <v>3139.223417592669</v>
       </c>
       <c r="D51">
-        <v>5596.449028297143</v>
+        <v>5601.842554500235</v>
       </c>
       <c r="E51">
-        <v>699.5824803542823</v>
+        <v>762.4808630924335</v>
       </c>
       <c r="F51">
-        <v>3082.020754169415</v>
+        <v>3144.919136907566</v>
       </c>
       <c r="G51">
         <v>682.3</v>
@@ -5469,28 +5469,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M51">
-        <v>197.5575303422595</v>
+        <v>201.589316675775</v>
       </c>
       <c r="N51">
-        <v>427.1281839434547</v>
+        <v>423.0963976099392</v>
       </c>
       <c r="O51">
-        <v>106.5257690754976</v>
+        <v>105.5202415639188</v>
       </c>
       <c r="P51">
-        <v>320.6024148679571</v>
+        <v>317.5761560460204</v>
       </c>
       <c r="Q51">
-        <v>390.2024148679571</v>
+        <v>387.1761560460204</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1034602372586161</v>
+        <v>0.1044463404693082</v>
       </c>
       <c r="T51">
-        <v>1.331645202277507</v>
+        <v>1.354418948482869</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.162044560910811</v>
+        <v>3.098803669692595</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07627990023465411</v>
+        <v>0.07621948406741405</v>
       </c>
       <c r="C52">
-        <v>3139.223417592669</v>
+        <v>3081.728967008647</v>
       </c>
       <c r="D52">
-        <v>5601.842554500235</v>
+        <v>5607.246486654364</v>
       </c>
       <c r="E52">
-        <v>762.4808630924335</v>
+        <v>825.3792458305848</v>
       </c>
       <c r="F52">
-        <v>3144.919136907566</v>
+        <v>3207.817519645717</v>
       </c>
       <c r="G52">
         <v>682.3</v>
@@ -5551,28 +5551,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M52">
-        <v>201.589316675775</v>
+        <v>205.6211030092905</v>
       </c>
       <c r="N52">
-        <v>423.0963976099392</v>
+        <v>419.0646112764237</v>
       </c>
       <c r="O52">
-        <v>105.5202415639188</v>
+        <v>104.5147140523401</v>
       </c>
       <c r="P52">
-        <v>317.5761560460204</v>
+        <v>314.5498972240836</v>
       </c>
       <c r="Q52">
-        <v>387.1761560460204</v>
+        <v>384.1498972240836</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1044463404693082</v>
+        <v>0.1054726927906409</v>
       </c>
       <c r="T52">
-        <v>1.354418948482869</v>
+        <v>1.378122235349675</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.098803669692595</v>
+        <v>3.038042813424113</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07621948406741405</v>
+        <v>0.079203501500174</v>
       </c>
       <c r="C53">
-        <v>3081.728967008647</v>
+        <v>2763.817637223286</v>
       </c>
       <c r="D53">
-        <v>5607.246486654364</v>
+        <v>5352.233539607155</v>
       </c>
       <c r="E53">
-        <v>825.3792458305848</v>
+        <v>888.2776285687364</v>
       </c>
       <c r="F53">
-        <v>3207.817519645717</v>
+        <v>3270.715902383869</v>
       </c>
       <c r="G53">
         <v>682.3</v>
@@ -5633,45 +5633,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M53">
-        <v>205.6211030092905</v>
+        <v>235.1644733814002</v>
       </c>
       <c r="N53">
-        <v>419.0646112764237</v>
+        <v>389.521240904314</v>
       </c>
       <c r="O53">
-        <v>104.5147140523401</v>
+        <v>97.14659748153592</v>
       </c>
       <c r="P53">
-        <v>314.5498972240836</v>
+        <v>292.3746434227781</v>
       </c>
       <c r="Q53">
-        <v>384.1498972240836</v>
+        <v>361.9746434227781</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1054726927906409</v>
+        <v>0.1065418097920292</v>
       </c>
       <c r="T53">
-        <v>1.378122235349675</v>
+        <v>1.402813159169265</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.038042813424113</v>
+        <v>2.656377918413599</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.079203501500174</v>
+        <v>0.07920163213293394</v>
       </c>
       <c r="C54">
-        <v>2763.817637223286</v>
+        <v>2701.071748670096</v>
       </c>
       <c r="D54">
-        <v>5352.233539607155</v>
+        <v>5352.386033792116</v>
       </c>
       <c r="E54">
-        <v>888.2776285687364</v>
+        <v>951.1760113068876</v>
       </c>
       <c r="F54">
-        <v>3270.715902383869</v>
+        <v>3333.61428512202</v>
       </c>
       <c r="G54">
         <v>682.3</v>
@@ -5715,28 +5715,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M54">
-        <v>235.1644733814002</v>
+        <v>239.6868671002733</v>
       </c>
       <c r="N54">
-        <v>389.521240904314</v>
+        <v>384.9988471854409</v>
       </c>
       <c r="O54">
-        <v>97.14659748153592</v>
+        <v>96.01871248804898</v>
       </c>
       <c r="P54">
-        <v>292.3746434227781</v>
+        <v>288.9801346973919</v>
       </c>
       <c r="Q54">
-        <v>361.9746434227781</v>
+        <v>358.5801346973919</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1065418097920292</v>
+        <v>0.107656421133902</v>
       </c>
       <c r="T54">
-        <v>1.402813159169265</v>
+        <v>1.428554760598199</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.656377918413599</v>
+        <v>2.606257580330324</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07920163213293394</v>
+        <v>0.07919976276569386</v>
       </c>
       <c r="C55">
-        <v>2701.071748670096</v>
+        <v>2638.325868806789</v>
       </c>
       <c r="D55">
-        <v>5352.386033792116</v>
+        <v>5352.53853666696</v>
       </c>
       <c r="E55">
-        <v>951.1760113068876</v>
+        <v>1014.074394045039</v>
       </c>
       <c r="F55">
-        <v>3333.61428512202</v>
+        <v>3396.512667860171</v>
       </c>
       <c r="G55">
         <v>682.3</v>
@@ -5797,28 +5797,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M55">
-        <v>239.6868671002733</v>
+        <v>244.2092608191464</v>
       </c>
       <c r="N55">
-        <v>384.9988471854409</v>
+        <v>380.4764534665678</v>
       </c>
       <c r="O55">
-        <v>96.01871248804898</v>
+        <v>94.89082749456202</v>
       </c>
       <c r="P55">
-        <v>288.9801346973919</v>
+        <v>285.5856259720058</v>
       </c>
       <c r="Q55">
-        <v>358.5801346973919</v>
+        <v>355.1856259720058</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.107656421133902</v>
+        <v>0.1088194938384649</v>
       </c>
       <c r="T55">
-        <v>1.428554760598199</v>
+        <v>1.455415562089259</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.606257580330324</v>
+        <v>2.557993551064948</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07919976276569386</v>
+        <v>0.0791978933984538</v>
       </c>
       <c r="C56">
-        <v>2638.325868806789</v>
+        <v>2575.579997634105</v>
       </c>
       <c r="D56">
-        <v>5352.53853666696</v>
+        <v>5352.691048232428</v>
       </c>
       <c r="E56">
-        <v>1014.074394045039</v>
+        <v>1076.972776783191</v>
       </c>
       <c r="F56">
-        <v>3396.512667860171</v>
+        <v>3459.411050598323</v>
       </c>
       <c r="G56">
         <v>682.3</v>
@@ -5879,28 +5879,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M56">
-        <v>244.2092608191464</v>
+        <v>248.7316545380195</v>
       </c>
       <c r="N56">
-        <v>380.4764534665678</v>
+        <v>375.9540597476947</v>
       </c>
       <c r="O56">
-        <v>94.89082749456202</v>
+        <v>93.76294250107506</v>
       </c>
       <c r="P56">
-        <v>285.5856259720058</v>
+        <v>282.1911172466197</v>
       </c>
       <c r="Q56">
-        <v>355.1856259720058</v>
+        <v>351.7911172466197</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1088194938384649</v>
+        <v>0.1100342586632307</v>
       </c>
       <c r="T56">
-        <v>1.455415562089259</v>
+        <v>1.483470176979923</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.557993551064948</v>
+        <v>2.511484577409221</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0791978933984538</v>
+        <v>0.08083533443121374</v>
       </c>
       <c r="C57">
-        <v>2575.579997634105</v>
+        <v>2382.340922967701</v>
       </c>
       <c r="D57">
-        <v>5352.691048232428</v>
+        <v>5222.350356304175</v>
       </c>
       <c r="E57">
-        <v>1076.972776783191</v>
+        <v>1139.871159521342</v>
       </c>
       <c r="F57">
-        <v>3459.411050598323</v>
+        <v>3522.309433336474</v>
       </c>
       <c r="G57">
         <v>682.3</v>
@@ -5961,45 +5961,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M57">
-        <v>248.7316545380195</v>
+        <v>266.9910550469048</v>
       </c>
       <c r="N57">
-        <v>375.9540597476947</v>
+        <v>357.6946592388094</v>
       </c>
       <c r="O57">
-        <v>93.76294250107506</v>
+        <v>89.20904801415908</v>
       </c>
       <c r="P57">
-        <v>282.1911172466197</v>
+        <v>268.4856112246504</v>
       </c>
       <c r="Q57">
-        <v>351.7911172466197</v>
+        <v>338.0856112246504</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1100342586632307</v>
+        <v>0.1113042400709403</v>
       </c>
       <c r="T57">
-        <v>1.483470176979923</v>
+        <v>1.512800001638345</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.2494</v>
       </c>
       <c r="W57">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.511484577409221</v>
+        <v>2.339725254750463</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08083533443121374</v>
+        <v>0.08086273846397368</v>
       </c>
       <c r="C58">
-        <v>2382.340922967701</v>
+        <v>2317.315157116817</v>
       </c>
       <c r="D58">
-        <v>5222.350356304175</v>
+        <v>5220.222973191443</v>
       </c>
       <c r="E58">
-        <v>1139.871159521342</v>
+        <v>1202.769542259493</v>
       </c>
       <c r="F58">
-        <v>3522.309433336474</v>
+        <v>3585.207816074626</v>
       </c>
       <c r="G58">
         <v>682.3</v>
@@ -6043,28 +6043,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M58">
-        <v>266.9910550469048</v>
+        <v>271.7587524584567</v>
       </c>
       <c r="N58">
-        <v>357.6946592388094</v>
+        <v>352.9269618272575</v>
       </c>
       <c r="O58">
-        <v>89.20904801415908</v>
+        <v>88.01998427971803</v>
       </c>
       <c r="P58">
-        <v>268.4856112246504</v>
+        <v>264.9069775475395</v>
       </c>
       <c r="Q58">
-        <v>338.0856112246504</v>
+        <v>334.5069775475395</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1113042400709403</v>
+        <v>0.1126332903813342</v>
       </c>
       <c r="T58">
-        <v>1.512800001638345</v>
+        <v>1.543494004187856</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.339725254750463</v>
+        <v>2.298677443263613</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08086273846397368</v>
+        <v>0.08089014249673361</v>
       </c>
       <c r="C59">
-        <v>2317.315157116817</v>
+        <v>2252.291123787015</v>
       </c>
       <c r="D59">
-        <v>5220.222973191443</v>
+        <v>5218.097322599792</v>
       </c>
       <c r="E59">
-        <v>1202.769542259493</v>
+        <v>1265.667924997645</v>
       </c>
       <c r="F59">
-        <v>3585.207816074626</v>
+        <v>3648.106198812777</v>
       </c>
       <c r="G59">
         <v>682.3</v>
@@ -6125,28 +6125,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M59">
-        <v>271.7587524584567</v>
+        <v>276.5264498700085</v>
       </c>
       <c r="N59">
-        <v>352.9269618272575</v>
+        <v>348.1592644157056</v>
       </c>
       <c r="O59">
-        <v>88.01998427971803</v>
+        <v>86.830920545277</v>
       </c>
       <c r="P59">
-        <v>264.9069775475395</v>
+        <v>261.3283438704286</v>
       </c>
       <c r="Q59">
-        <v>334.5069775475395</v>
+        <v>330.9283438704286</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1126332903813342</v>
+        <v>0.1140256288017467</v>
       </c>
       <c r="T59">
-        <v>1.543494004187856</v>
+        <v>1.575649625906391</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.298677443263613</v>
+        <v>2.259045073552171</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0808901424967336</v>
+        <v>0.08091754652949355</v>
       </c>
       <c r="C60">
-        <v>2252.291123787017</v>
+        <v>2187.26882086273</v>
       </c>
       <c r="D60">
-        <v>5218.097322599793</v>
+        <v>5215.973402413658</v>
       </c>
       <c r="E60">
-        <v>1265.667924997644</v>
+        <v>1328.566307735795</v>
       </c>
       <c r="F60">
-        <v>3648.106198812776</v>
+        <v>3711.004581550928</v>
       </c>
       <c r="G60">
         <v>682.3</v>
@@ -6207,28 +6207,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M60">
-        <v>276.5264498700085</v>
+        <v>281.2941472815604</v>
       </c>
       <c r="N60">
-        <v>348.1592644157057</v>
+        <v>343.3915670041538</v>
       </c>
       <c r="O60">
-        <v>86.83092054527701</v>
+        <v>85.64185681083598</v>
       </c>
       <c r="P60">
-        <v>261.3283438704287</v>
+        <v>257.7497101933179</v>
       </c>
       <c r="Q60">
-        <v>330.9283438704287</v>
+        <v>327.3497101933179</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1140256288017467</v>
+        <v>0.1154858861694965</v>
       </c>
       <c r="T60">
-        <v>1.57564962590639</v>
+        <v>1.609373814538025</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.259045073552171</v>
+        <v>2.22075617400044</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08091754652949355</v>
+        <v>0.08094495056225348</v>
       </c>
       <c r="C61">
-        <v>2187.26882086273</v>
+        <v>2122.248246231846</v>
       </c>
       <c r="D61">
-        <v>5215.973402413658</v>
+        <v>5213.851210520925</v>
       </c>
       <c r="E61">
-        <v>1328.566307735795</v>
+        <v>1391.464690473947</v>
       </c>
       <c r="F61">
-        <v>3711.004581550928</v>
+        <v>3773.902964289079</v>
       </c>
       <c r="G61">
         <v>682.3</v>
@@ -6289,28 +6289,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M61">
-        <v>281.2941472815604</v>
+        <v>286.0618446931122</v>
       </c>
       <c r="N61">
-        <v>343.3915670041538</v>
+        <v>338.623869592602</v>
       </c>
       <c r="O61">
-        <v>85.64185681083598</v>
+        <v>84.45279307639494</v>
       </c>
       <c r="P61">
-        <v>257.7497101933179</v>
+        <v>254.1710765162071</v>
       </c>
       <c r="Q61">
-        <v>327.3497101933179</v>
+        <v>323.7710765162071</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1154858861694965</v>
+        <v>0.1170191564056337</v>
       </c>
       <c r="T61">
-        <v>1.609373814538025</v>
+        <v>1.644784212601241</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.22075617400044</v>
+        <v>2.183743571100432</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08094495056225348</v>
+        <v>0.08097235459501342</v>
       </c>
       <c r="C62">
-        <v>2122.248246231846</v>
+        <v>2057.229397785675</v>
       </c>
       <c r="D62">
-        <v>5213.851210520925</v>
+        <v>5211.730744812905</v>
       </c>
       <c r="E62">
-        <v>1391.464690473947</v>
+        <v>1454.363073212098</v>
       </c>
       <c r="F62">
-        <v>3773.902964289079</v>
+        <v>3836.80134702723</v>
       </c>
       <c r="G62">
         <v>682.3</v>
@@ -6371,28 +6371,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M62">
-        <v>286.0618446931122</v>
+        <v>290.8295421046641</v>
       </c>
       <c r="N62">
-        <v>338.623869592602</v>
+        <v>333.8561721810501</v>
       </c>
       <c r="O62">
-        <v>84.45279307639494</v>
+        <v>83.2637293419539</v>
       </c>
       <c r="P62">
-        <v>254.1710765162071</v>
+        <v>250.5924428390962</v>
       </c>
       <c r="Q62">
-        <v>323.7710765162071</v>
+        <v>320.1924428390962</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1170191564056337</v>
+        <v>0.1186310558846498</v>
       </c>
       <c r="T62">
-        <v>1.644784212601241</v>
+        <v>1.682010528513852</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.183743571100432</v>
+        <v>2.14794449616436</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08097235459501342</v>
+        <v>0.08099975862777337</v>
       </c>
       <c r="C63">
-        <v>2057.229397785675</v>
+        <v>1992.212273418965</v>
       </c>
       <c r="D63">
-        <v>5211.730744812905</v>
+        <v>5209.612003184347</v>
       </c>
       <c r="E63">
-        <v>1454.363073212098</v>
+        <v>1517.261455950249</v>
       </c>
       <c r="F63">
-        <v>3836.80134702723</v>
+        <v>3899.699729765382</v>
       </c>
       <c r="G63">
         <v>682.3</v>
@@ -6453,28 +6453,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M63">
-        <v>290.8295421046641</v>
+        <v>295.597239516216</v>
       </c>
       <c r="N63">
-        <v>333.8561721810501</v>
+        <v>329.0884747694982</v>
       </c>
       <c r="O63">
-        <v>83.2637293419539</v>
+        <v>82.07466560751286</v>
       </c>
       <c r="P63">
-        <v>250.5924428390962</v>
+        <v>247.0138091619853</v>
       </c>
       <c r="Q63">
-        <v>320.1924428390962</v>
+        <v>316.6138091619854</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1186310558846498</v>
+        <v>0.120327792178351</v>
       </c>
       <c r="T63">
-        <v>1.682010528513852</v>
+        <v>1.721196124211338</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.14794449616436</v>
+        <v>2.113300230097193</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08099975862777337</v>
+        <v>0.08102716266053331</v>
       </c>
       <c r="C64">
-        <v>1992.212273418965</v>
+        <v>1927.196871029885</v>
       </c>
       <c r="D64">
-        <v>5209.612003184347</v>
+        <v>5207.494983533418</v>
       </c>
       <c r="E64">
-        <v>1517.261455950249</v>
+        <v>1580.159838688401</v>
       </c>
       <c r="F64">
-        <v>3899.699729765382</v>
+        <v>3962.598112503533</v>
       </c>
       <c r="G64">
         <v>682.3</v>
@@ -6535,28 +6535,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M64">
-        <v>295.597239516216</v>
+        <v>300.3649369277679</v>
       </c>
       <c r="N64">
-        <v>329.0884747694982</v>
+        <v>324.3207773579463</v>
       </c>
       <c r="O64">
-        <v>82.07466560751286</v>
+        <v>80.88560187307182</v>
       </c>
       <c r="P64">
-        <v>247.0138091619853</v>
+        <v>243.4351754848745</v>
       </c>
       <c r="Q64">
-        <v>316.6138091619854</v>
+        <v>313.0351754848745</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.120327792178351</v>
+        <v>0.1221162439473873</v>
       </c>
       <c r="T64">
-        <v>1.721196124211338</v>
+        <v>1.762499860216797</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.113300230097193</v>
+        <v>2.079755782000412</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08102716266053331</v>
+        <v>0.08105456669329325</v>
       </c>
       <c r="C65">
-        <v>1927.196871029885</v>
+        <v>1862.183188520016</v>
       </c>
       <c r="D65">
-        <v>5207.494983533418</v>
+        <v>5205.379683761701</v>
       </c>
       <c r="E65">
-        <v>1580.159838688401</v>
+        <v>1643.058221426552</v>
       </c>
       <c r="F65">
-        <v>3962.598112503533</v>
+        <v>4025.496495241685</v>
       </c>
       <c r="G65">
         <v>682.3</v>
@@ -6617,28 +6617,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M65">
-        <v>300.3649369277679</v>
+        <v>305.1326343393197</v>
       </c>
       <c r="N65">
-        <v>324.3207773579463</v>
+        <v>319.5530799463945</v>
       </c>
       <c r="O65">
-        <v>80.88560187307182</v>
+        <v>79.69653813863079</v>
       </c>
       <c r="P65">
-        <v>243.4351754848745</v>
+        <v>239.8565418077637</v>
       </c>
       <c r="Q65">
-        <v>313.0351754848745</v>
+        <v>309.4565418077637</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1221162439473873</v>
+        <v>0.1240040541480368</v>
       </c>
       <c r="T65">
-        <v>1.762499860216797</v>
+        <v>1.806098248222558</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.079755782000412</v>
+        <v>2.047259597906655</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08105456669329325</v>
+        <v>0.08108197072605317</v>
       </c>
       <c r="C66">
-        <v>1862.183188520016</v>
+        <v>1797.171223794353</v>
       </c>
       <c r="D66">
-        <v>5205.379683761701</v>
+        <v>5203.266101774189</v>
       </c>
       <c r="E66">
-        <v>1643.058221426552</v>
+        <v>1705.956604164704</v>
       </c>
       <c r="F66">
-        <v>4025.496495241685</v>
+        <v>4088.394877979836</v>
       </c>
       <c r="G66">
         <v>682.3</v>
@@ -6699,28 +6699,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M66">
-        <v>305.1326343393197</v>
+        <v>309.9003317508716</v>
       </c>
       <c r="N66">
-        <v>319.5530799463945</v>
+        <v>314.7853825348426</v>
       </c>
       <c r="O66">
-        <v>79.69653813863079</v>
+        <v>78.50747440418975</v>
       </c>
       <c r="P66">
-        <v>239.8565418077637</v>
+        <v>236.2779081306529</v>
       </c>
       <c r="Q66">
-        <v>309.4565418077637</v>
+        <v>305.8779081306529</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1240040541480368</v>
+        <v>0.1259997392172948</v>
       </c>
       <c r="T66">
-        <v>1.806098248222558</v>
+        <v>1.852187972685792</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.047259597906655</v>
+        <v>2.015763296400399</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08108197072605317</v>
+        <v>0.0881439979588131</v>
       </c>
       <c r="C67">
-        <v>1797.171223794353</v>
+        <v>1241.396018294735</v>
       </c>
       <c r="D67">
-        <v>5203.266101774189</v>
+        <v>4710.389279012722</v>
       </c>
       <c r="E67">
-        <v>1705.956604164704</v>
+        <v>1768.854986902855</v>
       </c>
       <c r="F67">
-        <v>4088.394877979836</v>
+        <v>4151.293260717987</v>
       </c>
       <c r="G67">
         <v>682.3</v>
@@ -6781,45 +6781,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M67">
-        <v>309.9003317508716</v>
+        <v>373.6163934646189</v>
       </c>
       <c r="N67">
-        <v>314.7853825348426</v>
+        <v>251.0693208210953</v>
       </c>
       <c r="O67">
-        <v>78.50747440418975</v>
+        <v>62.61668861278118</v>
       </c>
       <c r="P67">
-        <v>236.2779081306529</v>
+        <v>188.4526322083142</v>
       </c>
       <c r="Q67">
-        <v>305.8779081306529</v>
+        <v>258.0526322083142</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1259997392172948</v>
+        <v>0.1281128175259209</v>
       </c>
       <c r="T67">
-        <v>1.852187972685792</v>
+        <v>1.900988857411568</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.2494</v>
       </c>
       <c r="W67">
-        <v>0.05689548</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.015763296400399</v>
+        <v>1.671997602923362</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0881439979588131</v>
+        <v>0.08827798719157305</v>
       </c>
       <c r="C68">
-        <v>1241.396018294735</v>
+        <v>1170.047185362212</v>
       </c>
       <c r="D68">
-        <v>4710.389279012722</v>
+        <v>4701.938828818351</v>
       </c>
       <c r="E68">
-        <v>1768.854986902855</v>
+        <v>1831.753369641006</v>
       </c>
       <c r="F68">
-        <v>4151.293260717987</v>
+        <v>4214.191643456139</v>
       </c>
       <c r="G68">
         <v>682.3</v>
@@ -6863,28 +6863,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M68">
-        <v>373.6163934646189</v>
+        <v>379.2772479110525</v>
       </c>
       <c r="N68">
-        <v>251.0693208210953</v>
+        <v>245.4084663746617</v>
       </c>
       <c r="O68">
-        <v>62.61668861278118</v>
+        <v>61.20487151384064</v>
       </c>
       <c r="P68">
-        <v>188.4526322083142</v>
+        <v>184.2035948608211</v>
       </c>
       <c r="Q68">
-        <v>258.0526322083142</v>
+        <v>253.8035948608211</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1281128175259209</v>
+        <v>0.130353961186585</v>
       </c>
       <c r="T68">
-        <v>1.900988857411568</v>
+        <v>1.952747371514665</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.671997602923362</v>
+        <v>1.647042414820028</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08827798719157305</v>
+        <v>0.08841197642433296</v>
       </c>
       <c r="C69">
-        <v>1170.047185362212</v>
+        <v>1098.72861839022</v>
       </c>
       <c r="D69">
-        <v>4701.938828818351</v>
+        <v>4693.518644584509</v>
       </c>
       <c r="E69">
-        <v>1831.753369641006</v>
+        <v>1894.651752379157</v>
       </c>
       <c r="F69">
-        <v>4214.191643456139</v>
+        <v>4277.09002619429</v>
       </c>
       <c r="G69">
         <v>682.3</v>
@@ -6945,28 +6945,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M69">
-        <v>379.2772479110525</v>
+        <v>384.9381023574861</v>
       </c>
       <c r="N69">
-        <v>245.4084663746617</v>
+        <v>239.7476119282281</v>
       </c>
       <c r="O69">
-        <v>61.20487151384064</v>
+        <v>59.7930544149001</v>
       </c>
       <c r="P69">
-        <v>184.2035948608211</v>
+        <v>179.954557513328</v>
       </c>
       <c r="Q69">
-        <v>253.8035948608211</v>
+        <v>249.5545575133281</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.130353961186585</v>
+        <v>0.1327351763260406</v>
       </c>
       <c r="T69">
-        <v>1.952747371514665</v>
+        <v>2.007740792749205</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.647042414820028</v>
+        <v>1.62282120283738</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08841197642433296</v>
+        <v>0.08854596565709291</v>
       </c>
       <c r="C70">
-        <v>1098.72861839022</v>
+        <v>1027.440155069488</v>
       </c>
       <c r="D70">
-        <v>4693.518644584509</v>
+        <v>4685.12856400193</v>
       </c>
       <c r="E70">
-        <v>1894.651752379157</v>
+        <v>1957.550135117309</v>
       </c>
       <c r="F70">
-        <v>4277.09002619429</v>
+        <v>4339.988408932441</v>
       </c>
       <c r="G70">
         <v>682.3</v>
@@ -7027,28 +7027,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M70">
-        <v>384.9381023574861</v>
+        <v>390.5989568039197</v>
       </c>
       <c r="N70">
-        <v>239.7476119282281</v>
+        <v>234.0867574817945</v>
       </c>
       <c r="O70">
-        <v>59.7930544149001</v>
+        <v>58.38123731595955</v>
       </c>
       <c r="P70">
-        <v>179.954557513328</v>
+        <v>175.705520165835</v>
       </c>
       <c r="Q70">
-        <v>249.5545575133281</v>
+        <v>245.305520165835</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1327351763260406</v>
+        <v>0.1352700182486868</v>
       </c>
       <c r="T70">
-        <v>2.007740792749205</v>
+        <v>2.066282176644038</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.62282120283738</v>
+        <v>1.599302054970172</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08854596565709291</v>
+        <v>0.08867995488985285</v>
       </c>
       <c r="C71">
-        <v>1027.440155069488</v>
+        <v>956.1816342492602</v>
       </c>
       <c r="D71">
-        <v>4685.12856400193</v>
+        <v>4676.768425919853</v>
       </c>
       <c r="E71">
-        <v>1957.550135117309</v>
+        <v>2020.448517855461</v>
       </c>
       <c r="F71">
-        <v>4339.988408932441</v>
+        <v>4402.886791670593</v>
       </c>
       <c r="G71">
         <v>682.3</v>
@@ -7109,28 +7109,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M71">
-        <v>390.5989568039197</v>
+        <v>396.2598112503534</v>
       </c>
       <c r="N71">
-        <v>234.0867574817945</v>
+        <v>228.4259030353608</v>
       </c>
       <c r="O71">
-        <v>58.38123731595955</v>
+        <v>56.96942021701899</v>
       </c>
       <c r="P71">
-        <v>175.705520165835</v>
+        <v>171.4564828183418</v>
       </c>
       <c r="Q71">
-        <v>245.305520165835</v>
+        <v>241.0564828183419</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1352700182486868</v>
+        <v>0.1379738496328429</v>
       </c>
       <c r="T71">
-        <v>2.066282176644038</v>
+        <v>2.128726319465193</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.599302054970172</v>
+        <v>1.576454882756312</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08867995488985285</v>
+        <v>0.08881394412261279</v>
       </c>
       <c r="C72">
-        <v>956.1816342492602</v>
+        <v>884.952895926951</v>
       </c>
       <c r="D72">
-        <v>4676.768425919853</v>
+        <v>4668.438070335696</v>
       </c>
       <c r="E72">
-        <v>2020.448517855461</v>
+        <v>2083.346900593612</v>
       </c>
       <c r="F72">
-        <v>4402.886791670593</v>
+        <v>4465.785174408745</v>
       </c>
       <c r="G72">
         <v>682.3</v>
@@ -7191,28 +7191,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M72">
-        <v>396.2598112503534</v>
+        <v>401.920665696787</v>
       </c>
       <c r="N72">
-        <v>228.4259030353608</v>
+        <v>222.7650485889272</v>
       </c>
       <c r="O72">
-        <v>56.96942021701899</v>
+        <v>55.55760311807844</v>
       </c>
       <c r="P72">
-        <v>171.4564828183418</v>
+        <v>167.2074454708487</v>
       </c>
       <c r="Q72">
-        <v>241.0564828183419</v>
+        <v>236.8074454708488</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1379738496328429</v>
+        <v>0.1408641521469407</v>
       </c>
       <c r="T72">
-        <v>2.128726319465193</v>
+        <v>2.195476954894704</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.576454882756312</v>
+        <v>1.554251292858336</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08881394412261279</v>
+        <v>0.08894793335537272</v>
       </c>
       <c r="C73">
-        <v>884.9528959269519</v>
+        <v>813.7537812379514</v>
       </c>
       <c r="D73">
-        <v>4668.438070335696</v>
+        <v>4660.137338384846</v>
       </c>
       <c r="E73">
-        <v>2083.346900593611</v>
+        <v>2146.245283331762</v>
       </c>
       <c r="F73">
-        <v>4465.785174408744</v>
+        <v>4528.683557146895</v>
       </c>
       <c r="G73">
         <v>682.3</v>
@@ -7273,28 +7273,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M73">
-        <v>401.920665696787</v>
+        <v>407.5815201432205</v>
       </c>
       <c r="N73">
-        <v>222.7650485889272</v>
+        <v>217.1041941424937</v>
       </c>
       <c r="O73">
-        <v>55.55760311807845</v>
+        <v>54.14578601913794</v>
       </c>
       <c r="P73">
-        <v>167.2074454708488</v>
+        <v>162.9584081233558</v>
       </c>
       <c r="Q73">
-        <v>236.8074454708488</v>
+        <v>232.5584081233558</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1408641521469406</v>
+        <v>0.1439609048406169</v>
       </c>
       <c r="T73">
-        <v>2.195476954894704</v>
+        <v>2.266995492854894</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.554251292858336</v>
+        <v>1.532664469346415</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08894793335537272</v>
+        <v>0.08908192258813266</v>
       </c>
       <c r="C74">
-        <v>813.7537812379514</v>
+        <v>742.5841324455232</v>
       </c>
       <c r="D74">
-        <v>4660.137338384846</v>
+        <v>4651.866072330569</v>
       </c>
       <c r="E74">
-        <v>2146.245283331762</v>
+        <v>2209.143666069914</v>
       </c>
       <c r="F74">
-        <v>4528.683557146895</v>
+        <v>4591.581939885046</v>
       </c>
       <c r="G74">
         <v>682.3</v>
@@ -7355,28 +7355,28 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M74">
-        <v>407.5815201432205</v>
+        <v>413.2423745896542</v>
       </c>
       <c r="N74">
-        <v>217.1041941424937</v>
+        <v>211.44333969606</v>
       </c>
       <c r="O74">
-        <v>54.14578601913794</v>
+        <v>52.73396892019738</v>
       </c>
       <c r="P74">
-        <v>162.9584081233558</v>
+        <v>158.7093707758627</v>
       </c>
       <c r="Q74">
-        <v>232.5584081233558</v>
+        <v>228.3093707758627</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1439609048406169</v>
+        <v>0.1472870466227136</v>
       </c>
       <c r="T74">
-        <v>2.266995492854894</v>
+        <v>2.343811700293616</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.532664469346415</v>
+        <v>1.511669065656738</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08908192258813266</v>
+        <v>0.1236185572509342</v>
       </c>
       <c r="C75">
-        <v>742.5841324455232</v>
+        <v>-780.4877075637914</v>
       </c>
       <c r="D75">
-        <v>4651.866072330569</v>
+        <v>3191.692615059407</v>
       </c>
       <c r="E75">
-        <v>2209.143666069914</v>
+        <v>2272.042048808065</v>
       </c>
       <c r="F75">
-        <v>4591.581939885046</v>
+        <v>4654.480322623198</v>
       </c>
       <c r="G75">
         <v>682.3</v>
@@ -7437,45 +7437,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M75">
-        <v>413.2423745896542</v>
+        <v>683.2777113610855</v>
       </c>
       <c r="N75">
-        <v>211.44333969606</v>
+        <v>-58.5919970753713</v>
       </c>
       <c r="O75">
-        <v>52.73396892019738</v>
+        <v>-14.6128440705976</v>
       </c>
       <c r="P75">
-        <v>158.7093707758627</v>
+        <v>-43.97915300477369</v>
       </c>
       <c r="Q75">
-        <v>228.3093707758627</v>
+        <v>25.62084699522633</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1472870466227136</v>
+        <v>0.1529081986914535</v>
       </c>
       <c r="T75">
-        <v>2.343811700293616</v>
+        <v>2.473630454767978</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2494</v>
+        <v>0.2280136093309865</v>
       </c>
       <c r="W75">
-        <v>0.06755399999999999</v>
+        <v>0.1133276021502112</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.511669065656738</v>
+        <v>0.9142486340456557</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1236185572509342</v>
+        <v>0.1246285572509342</v>
       </c>
       <c r="C76">
-        <v>-780.4877075637914</v>
+        <v>-872.4177087027138</v>
       </c>
       <c r="D76">
-        <v>3191.692615059407</v>
+        <v>3162.660996658635</v>
       </c>
       <c r="E76">
-        <v>2272.042048808065</v>
+        <v>2334.940431546216</v>
       </c>
       <c r="F76">
-        <v>4654.480322623198</v>
+        <v>4717.378705361349</v>
       </c>
       <c r="G76">
         <v>682.3</v>
@@ -7519,37 +7519,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M76">
-        <v>683.2777113610855</v>
+        <v>692.5111939470461</v>
       </c>
       <c r="N76">
-        <v>-58.5919970753713</v>
+        <v>-67.82547966133188</v>
       </c>
       <c r="O76">
-        <v>-14.6128440705976</v>
+        <v>-16.91567462753617</v>
       </c>
       <c r="P76">
-        <v>-43.97915300477369</v>
+        <v>-50.90980503379571</v>
       </c>
       <c r="Q76">
-        <v>25.62084699522633</v>
+        <v>18.69019496620432</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1529081986914535</v>
+        <v>0.1571925266391116</v>
       </c>
       <c r="T76">
-        <v>2.473630454767978</v>
+        <v>2.572575672958698</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2280136093309865</v>
+        <v>0.2249734278732401</v>
       </c>
       <c r="W76">
-        <v>0.1133276021502112</v>
+        <v>0.1137739007882084</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9142486340456557</v>
+        <v>0.9020586522583803</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1246285572509342</v>
+        <v>0.1256385572509342</v>
       </c>
       <c r="C77">
-        <v>-872.4177087027138</v>
+        <v>-963.8243276419362</v>
       </c>
       <c r="D77">
-        <v>3162.660996658635</v>
+        <v>3134.152760457564</v>
       </c>
       <c r="E77">
-        <v>2334.940431546216</v>
+        <v>2397.838814284368</v>
       </c>
       <c r="F77">
-        <v>4717.378705361349</v>
+        <v>4780.2770880995</v>
       </c>
       <c r="G77">
         <v>682.3</v>
@@ -7601,37 +7601,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M77">
-        <v>692.5111939470461</v>
+        <v>701.7446765330067</v>
       </c>
       <c r="N77">
-        <v>-67.82547966133188</v>
+        <v>-77.05896224729247</v>
       </c>
       <c r="O77">
-        <v>-16.91567462753617</v>
+        <v>-19.21850518447474</v>
       </c>
       <c r="P77">
-        <v>-50.90980503379571</v>
+        <v>-57.84045706281773</v>
       </c>
       <c r="Q77">
-        <v>18.69019496620432</v>
+        <v>11.7595429371823</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1571925266391116</v>
+        <v>0.1618338819157413</v>
       </c>
       <c r="T77">
-        <v>2.572575672958698</v>
+        <v>2.679766325998644</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2249734278732401</v>
+        <v>0.2220132511906974</v>
       </c>
       <c r="W77">
-        <v>0.1137739007882084</v>
+        <v>0.1142084547252056</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9020586522583803</v>
+        <v>0.8901894594655069</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1256385572509342</v>
+        <v>0.1266485572509342</v>
       </c>
       <c r="C78">
-        <v>-963.8243276419362</v>
+        <v>-1054.721591249621</v>
       </c>
       <c r="D78">
-        <v>3134.152760457564</v>
+        <v>3106.153879588031</v>
       </c>
       <c r="E78">
-        <v>2397.838814284368</v>
+        <v>2460.737197022519</v>
       </c>
       <c r="F78">
-        <v>4780.2770880995</v>
+        <v>4843.175470837652</v>
       </c>
       <c r="G78">
         <v>682.3</v>
@@ -7683,37 +7683,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M78">
-        <v>701.7446765330067</v>
+        <v>710.9781591189674</v>
       </c>
       <c r="N78">
-        <v>-77.05896224729247</v>
+        <v>-86.29244483325317</v>
       </c>
       <c r="O78">
-        <v>-19.21850518447474</v>
+        <v>-21.52133574141334</v>
       </c>
       <c r="P78">
-        <v>-57.84045706281773</v>
+        <v>-64.77110909183983</v>
       </c>
       <c r="Q78">
-        <v>11.7595429371823</v>
+        <v>4.82889090816019</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1618338819157413</v>
+        <v>0.1668788333033822</v>
       </c>
       <c r="T78">
-        <v>2.679766325998644</v>
+        <v>2.796277905389889</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2220132511906974</v>
+        <v>0.2191299622141948</v>
       </c>
       <c r="W78">
-        <v>0.1142084547252056</v>
+        <v>0.1146317215469562</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8901894594655069</v>
+        <v>0.8786285573945262</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1266485572509342</v>
+        <v>0.1276585572509342</v>
       </c>
       <c r="C79">
-        <v>-1054.721591249621</v>
+        <v>-1145.123029597255</v>
       </c>
       <c r="D79">
-        <v>3106.153879588031</v>
+        <v>3078.650823978549</v>
       </c>
       <c r="E79">
-        <v>2460.737197022519</v>
+        <v>2523.635579760671</v>
       </c>
       <c r="F79">
-        <v>4843.175470837652</v>
+        <v>4906.073853575804</v>
       </c>
       <c r="G79">
         <v>682.3</v>
@@ -7765,37 +7765,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M79">
-        <v>710.9781591189674</v>
+        <v>720.2116417049281</v>
       </c>
       <c r="N79">
-        <v>-86.29244483325317</v>
+        <v>-95.52592741921387</v>
       </c>
       <c r="O79">
-        <v>-21.52133574141334</v>
+        <v>-23.82416629835194</v>
       </c>
       <c r="P79">
-        <v>-64.77110909183983</v>
+        <v>-71.70176112086193</v>
       </c>
       <c r="Q79">
-        <v>4.82889090816019</v>
+        <v>-2.101761120861909</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1668788333033822</v>
+        <v>0.1723824166353541</v>
       </c>
       <c r="T79">
-        <v>2.796277905389889</v>
+        <v>2.923381446543976</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2191299622141948</v>
+        <v>0.2163206037242692</v>
       </c>
       <c r="W79">
-        <v>0.1146317215469562</v>
+        <v>0.1150441353732773</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8786285573945262</v>
+        <v>0.8673640887099809</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1276585572509342</v>
+        <v>0.1286685572509342</v>
       </c>
       <c r="C80">
-        <v>-1145.123029597255</v>
+        <v>-1235.041697760719</v>
       </c>
       <c r="D80">
-        <v>3078.650823978549</v>
+        <v>3051.630538553236</v>
       </c>
       <c r="E80">
-        <v>2523.635579760671</v>
+        <v>2586.533962498822</v>
       </c>
       <c r="F80">
-        <v>4906.073853575804</v>
+        <v>4968.972236313954</v>
       </c>
       <c r="G80">
         <v>682.3</v>
@@ -7847,37 +7847,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M80">
-        <v>720.2116417049281</v>
+        <v>729.4451242908885</v>
       </c>
       <c r="N80">
-        <v>-95.52592741921387</v>
+        <v>-104.7594100051743</v>
       </c>
       <c r="O80">
-        <v>-23.82416629835194</v>
+        <v>-26.12699685529048</v>
       </c>
       <c r="P80">
-        <v>-71.70176112086193</v>
+        <v>-78.63241314988386</v>
       </c>
       <c r="Q80">
-        <v>-2.101761120861909</v>
+        <v>-9.032413149883837</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1723824166353541</v>
+        <v>0.1784101507608472</v>
       </c>
       <c r="T80">
-        <v>2.923381446543976</v>
+        <v>3.062590086855593</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2163206037242692</v>
+        <v>0.2135823682340887</v>
       </c>
       <c r="W80">
-        <v>0.1150441353732773</v>
+        <v>0.1154461083432358</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8673640887099809</v>
+        <v>0.8563847964478294</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1286685572509342</v>
+        <v>0.1296785572509342</v>
       </c>
       <c r="C81">
-        <v>-1235.041697760719</v>
+        <v>-1324.490196483349</v>
       </c>
       <c r="D81">
-        <v>3051.630538553236</v>
+        <v>3025.080422568757</v>
       </c>
       <c r="E81">
-        <v>2586.533962498822</v>
+        <v>2649.432345236974</v>
       </c>
       <c r="F81">
-        <v>4968.972236313954</v>
+        <v>5031.870619052106</v>
       </c>
       <c r="G81">
         <v>682.3</v>
@@ -7929,37 +7929,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M81">
-        <v>729.4451242908885</v>
+        <v>738.6786068768492</v>
       </c>
       <c r="N81">
-        <v>-104.7594100051743</v>
+        <v>-113.992892591135</v>
       </c>
       <c r="O81">
-        <v>-26.12699685529048</v>
+        <v>-28.42982741222908</v>
       </c>
       <c r="P81">
-        <v>-78.63241314988386</v>
+        <v>-85.56306517890596</v>
       </c>
       <c r="Q81">
-        <v>-9.032413149883837</v>
+        <v>-15.96306517890594</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1784101507608472</v>
+        <v>0.1850406582988896</v>
       </c>
       <c r="T81">
-        <v>3.062590086855593</v>
+        <v>3.215719591198373</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2135823682340887</v>
+        <v>0.2109125886311625</v>
       </c>
       <c r="W81">
-        <v>0.1154461083432358</v>
+        <v>0.1158380319889454</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8563847964478294</v>
+        <v>0.8456799864922314</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1296785572509342</v>
+        <v>0.1306885572509342</v>
       </c>
       <c r="C82">
-        <v>-1324.490196483349</v>
+        <v>-1413.480691769599</v>
       </c>
       <c r="D82">
-        <v>3025.080422568757</v>
+        <v>2998.988310020659</v>
       </c>
       <c r="E82">
-        <v>2649.432345236974</v>
+        <v>2712.330727975125</v>
       </c>
       <c r="F82">
-        <v>5031.870619052106</v>
+        <v>5094.769001790258</v>
       </c>
       <c r="G82">
         <v>682.3</v>
@@ -8011,37 +8011,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M82">
-        <v>738.6786068768492</v>
+        <v>747.9120894628099</v>
       </c>
       <c r="N82">
-        <v>-113.992892591135</v>
+        <v>-123.2263751770957</v>
       </c>
       <c r="O82">
-        <v>-28.42982741222908</v>
+        <v>-30.73265796916768</v>
       </c>
       <c r="P82">
-        <v>-85.56306517890596</v>
+        <v>-92.49371720792807</v>
       </c>
       <c r="Q82">
-        <v>-15.96306517890594</v>
+        <v>-22.89371720792805</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1850406582988896</v>
+        <v>0.1923691139988311</v>
       </c>
       <c r="T82">
-        <v>3.215719591198373</v>
+        <v>3.38496799073513</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2109125886311625</v>
+        <v>0.2083087295122593</v>
       </c>
       <c r="W82">
-        <v>0.1158380319889454</v>
+        <v>0.1162202785076004</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8456799864922314</v>
+        <v>0.8352394928318334</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1306885572509342</v>
+        <v>0.1316985572509342</v>
       </c>
       <c r="C83">
-        <v>-1413.480691769599</v>
+        <v>-1502.024933473404</v>
       </c>
       <c r="D83">
-        <v>2998.988310020659</v>
+        <v>2973.342451055004</v>
       </c>
       <c r="E83">
-        <v>2712.330727975125</v>
+        <v>2775.229110713276</v>
       </c>
       <c r="F83">
-        <v>5094.769001790258</v>
+        <v>5157.667384528409</v>
       </c>
       <c r="G83">
         <v>682.3</v>
@@ -8093,37 +8093,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M83">
-        <v>747.9120894628099</v>
+        <v>757.1455720487704</v>
       </c>
       <c r="N83">
-        <v>-123.2263751770957</v>
+        <v>-132.4598577630562</v>
       </c>
       <c r="O83">
-        <v>-30.73265796916768</v>
+        <v>-33.03548852610622</v>
       </c>
       <c r="P83">
-        <v>-92.49371720792807</v>
+        <v>-99.42436923695</v>
       </c>
       <c r="Q83">
-        <v>-22.89371720792805</v>
+        <v>-29.82436923694998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1923691139988311</v>
+        <v>0.2005118425543217</v>
       </c>
       <c r="T83">
-        <v>3.38496799073513</v>
+        <v>3.573021767998192</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2083087295122593</v>
+        <v>0.2057683791523537</v>
       </c>
       <c r="W83">
-        <v>0.1162202785076004</v>
+        <v>0.1165932019404345</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8352394928318334</v>
+        <v>0.8250536453582746</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1316985572509342</v>
+        <v>0.1327085572509342</v>
       </c>
       <c r="C84">
-        <v>-1502.024933473404</v>
+        <v>-1590.134272940881</v>
       </c>
       <c r="D84">
-        <v>2973.342451055004</v>
+        <v>2948.13149432568</v>
       </c>
       <c r="E84">
-        <v>2775.229110713276</v>
+        <v>2838.127493451428</v>
       </c>
       <c r="F84">
-        <v>5157.667384528409</v>
+        <v>5220.56576726656</v>
       </c>
       <c r="G84">
         <v>682.3</v>
@@ -8175,37 +8175,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M84">
-        <v>757.1455720487704</v>
+        <v>766.3790546347311</v>
       </c>
       <c r="N84">
-        <v>-132.4598577630562</v>
+        <v>-141.6933403490169</v>
       </c>
       <c r="O84">
-        <v>-33.03548852610622</v>
+        <v>-35.33831908304482</v>
       </c>
       <c r="P84">
-        <v>-99.42436923695</v>
+        <v>-106.3550212659721</v>
       </c>
       <c r="Q84">
-        <v>-29.82436923694998</v>
+        <v>-36.75502126597208</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2005118425543217</v>
+        <v>0.2096125391751642</v>
       </c>
       <c r="T84">
-        <v>3.573021767998192</v>
+        <v>3.78319951905691</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2057683791523537</v>
+        <v>0.2032892420541325</v>
       </c>
       <c r="W84">
-        <v>0.1165932019404345</v>
+        <v>0.1169571392664533</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8250536453582746</v>
+        <v>0.8151132399925122</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1327085572509342</v>
+        <v>0.1337185572509342</v>
       </c>
       <c r="C85">
-        <v>-1590.134272940881</v>
+        <v>-1677.819679762998</v>
       </c>
       <c r="D85">
-        <v>2948.13149432568</v>
+        <v>2923.344470241714</v>
       </c>
       <c r="E85">
-        <v>2838.127493451428</v>
+        <v>2901.025876189579</v>
       </c>
       <c r="F85">
-        <v>5220.56576726656</v>
+        <v>5283.464150004712</v>
       </c>
       <c r="G85">
         <v>682.3</v>
@@ -8257,37 +8257,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M85">
-        <v>766.3790546347311</v>
+        <v>775.6125372206918</v>
       </c>
       <c r="N85">
-        <v>-141.6933403490169</v>
+        <v>-150.9268229349776</v>
       </c>
       <c r="O85">
-        <v>-35.33831908304482</v>
+        <v>-37.64114963998342</v>
       </c>
       <c r="P85">
-        <v>-106.3550212659721</v>
+        <v>-113.2856732949942</v>
       </c>
       <c r="Q85">
-        <v>-36.75502126597208</v>
+        <v>-43.68567329499419</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2096125391751642</v>
+        <v>0.219850822873612</v>
       </c>
       <c r="T85">
-        <v>3.78319951905691</v>
+        <v>4.019649488997968</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2032892420541325</v>
+        <v>0.2008691320296785</v>
       </c>
       <c r="W85">
-        <v>0.1169571392664533</v>
+        <v>0.1173124114180432</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8151132399925122</v>
+        <v>0.8054095109449821</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1337185572509342</v>
+        <v>0.1821486725626448</v>
       </c>
       <c r="C86">
-        <v>-1677.819679762997</v>
+        <v>-2580.653921317167</v>
       </c>
       <c r="D86">
-        <v>2923.344470241714</v>
+        <v>2083.408611425695</v>
       </c>
       <c r="E86">
-        <v>2901.025876189578</v>
+        <v>2963.92425892773</v>
       </c>
       <c r="F86">
-        <v>5283.464150004711</v>
+        <v>5346.362532742863</v>
       </c>
       <c r="G86">
         <v>682.3</v>
@@ -8339,45 +8339,45 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M86">
-        <v>775.6125372206916</v>
+        <v>1073.549596574767</v>
       </c>
       <c r="N86">
-        <v>-150.9268229349774</v>
+        <v>-448.8638822890526</v>
       </c>
       <c r="O86">
-        <v>-37.64114963998336</v>
+        <v>-111.9466522428897</v>
       </c>
       <c r="P86">
-        <v>-113.285673294994</v>
+        <v>-336.9172300461629</v>
       </c>
       <c r="Q86">
-        <v>-43.68567329499402</v>
+        <v>-267.3172300461629</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2198508228736119</v>
+        <v>0.2415883131432566</v>
       </c>
       <c r="T86">
-        <v>4.019649488997964</v>
+        <v>4.521670049497843</v>
       </c>
       <c r="U86">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.2008691320296786</v>
+        <v>0.1451228873262464</v>
       </c>
       <c r="W86">
-        <v>0.1173124114180432</v>
+        <v>0.1716593242248897</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8054095109449824</v>
+        <v>0.5818880806986622</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1821486725626448</v>
+        <v>0.1836986725626447</v>
       </c>
       <c r="C87">
-        <v>-2580.653921317167</v>
+        <v>-2662.53602803269</v>
       </c>
       <c r="D87">
-        <v>2083.408611425695</v>
+        <v>2064.424887448324</v>
       </c>
       <c r="E87">
-        <v>2963.92425892773</v>
+        <v>3026.822641665881</v>
       </c>
       <c r="F87">
-        <v>5346.362532742863</v>
+        <v>5409.260915481013</v>
       </c>
       <c r="G87">
         <v>682.3</v>
@@ -8421,37 +8421,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M87">
-        <v>1073.549596574767</v>
+        <v>1086.179591828587</v>
       </c>
       <c r="N87">
-        <v>-448.8638822890526</v>
+        <v>-461.4938775428733</v>
       </c>
       <c r="O87">
-        <v>-111.9466522428897</v>
+        <v>-115.0965730591926</v>
       </c>
       <c r="P87">
-        <v>-336.9172300461629</v>
+        <v>-346.3973044836807</v>
       </c>
       <c r="Q87">
-        <v>-267.3172300461629</v>
+        <v>-276.7973044836806</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2415883131432566</v>
+        <v>0.2555731926534892</v>
       </c>
       <c r="T87">
-        <v>4.521670049497843</v>
+        <v>4.844646481604832</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1451228873262464</v>
+        <v>0.1434354118922203</v>
       </c>
       <c r="W87">
-        <v>0.1716593242248897</v>
+        <v>0.1719981692920422</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5818880806986622</v>
+        <v>0.575121940225422</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1836986725626447</v>
+        <v>0.1852486725626448</v>
       </c>
       <c r="C88">
-        <v>-2662.53602803269</v>
+        <v>-2744.075304563779</v>
       </c>
       <c r="D88">
-        <v>2064.424887448324</v>
+        <v>2045.783993655386</v>
       </c>
       <c r="E88">
-        <v>3026.822641665881</v>
+        <v>3089.721024404033</v>
       </c>
       <c r="F88">
-        <v>5409.260915481013</v>
+        <v>5472.159298219165</v>
       </c>
       <c r="G88">
         <v>682.3</v>
@@ -8503,37 +8503,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M88">
-        <v>1086.179591828587</v>
+        <v>1098.809587082408</v>
       </c>
       <c r="N88">
-        <v>-461.4938775428733</v>
+        <v>-474.1238727966942</v>
       </c>
       <c r="O88">
-        <v>-115.0965730591926</v>
+        <v>-118.2464938754955</v>
       </c>
       <c r="P88">
-        <v>-346.3973044836807</v>
+        <v>-355.8773789211987</v>
       </c>
       <c r="Q88">
-        <v>-276.7973044836806</v>
+        <v>-286.2773789211986</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2555731926534892</v>
+        <v>0.271709592088373</v>
       </c>
       <c r="T88">
-        <v>4.844646481604832</v>
+        <v>5.217311595574435</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1434354118922203</v>
+        <v>0.1417867289969074</v>
       </c>
       <c r="W88">
-        <v>0.1719981692920422</v>
+        <v>0.172329224817421</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.575121940225422</v>
+        <v>0.5685113432113367</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1852486725626448</v>
+        <v>0.1867986725626448</v>
       </c>
       <c r="C89">
-        <v>-2744.075304563779</v>
+        <v>-2825.280954644348</v>
       </c>
       <c r="D89">
-        <v>2045.783993655386</v>
+        <v>2027.476726312969</v>
       </c>
       <c r="E89">
-        <v>3089.721024404033</v>
+        <v>3152.619407142184</v>
       </c>
       <c r="F89">
-        <v>5472.159298219165</v>
+        <v>5535.057680957317</v>
       </c>
       <c r="G89">
         <v>682.3</v>
@@ -8585,37 +8585,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M89">
-        <v>1098.809587082408</v>
+        <v>1111.439582336229</v>
       </c>
       <c r="N89">
-        <v>-474.1238727966942</v>
+        <v>-486.7538680505151</v>
       </c>
       <c r="O89">
-        <v>-118.2464938754955</v>
+        <v>-121.3964146917985</v>
       </c>
       <c r="P89">
-        <v>-355.8773789211987</v>
+        <v>-365.3574533587166</v>
       </c>
       <c r="Q89">
-        <v>-286.2773789211986</v>
+        <v>-295.7574533587166</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.271709592088373</v>
+        <v>0.2905353914290708</v>
       </c>
       <c r="T89">
-        <v>5.217311595574435</v>
+        <v>5.652087561872305</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1417867289969074</v>
+        <v>0.1401755161673971</v>
       </c>
       <c r="W89">
-        <v>0.172329224817421</v>
+        <v>0.1726527563535867</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5685113432113367</v>
+        <v>0.5620509870384806</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1867986725626448</v>
+        <v>0.1883486725626448</v>
       </c>
       <c r="C90">
-        <v>-2825.280954644348</v>
+        <v>-2906.161855481623</v>
       </c>
       <c r="D90">
-        <v>2027.476726312969</v>
+        <v>2009.494208213844</v>
       </c>
       <c r="E90">
-        <v>3152.619407142184</v>
+        <v>3215.517789880335</v>
       </c>
       <c r="F90">
-        <v>5535.057680957317</v>
+        <v>5597.956063695467</v>
       </c>
       <c r="G90">
         <v>682.3</v>
@@ -8667,37 +8667,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M90">
-        <v>1111.439582336229</v>
+        <v>1124.06957759005</v>
       </c>
       <c r="N90">
-        <v>-486.7538680505151</v>
+        <v>-499.3838633043357</v>
       </c>
       <c r="O90">
-        <v>-121.3964146917985</v>
+        <v>-124.5463355081013</v>
       </c>
       <c r="P90">
-        <v>-365.3574533587166</v>
+        <v>-374.8375277962344</v>
       </c>
       <c r="Q90">
-        <v>-295.7574533587166</v>
+        <v>-305.2375277962344</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2905353914290708</v>
+        <v>0.3127840633771681</v>
       </c>
       <c r="T90">
-        <v>5.652087561872305</v>
+        <v>6.165913703860697</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1401755161673971</v>
+        <v>0.1386005103677634</v>
       </c>
       <c r="W90">
-        <v>0.1726527563535867</v>
+        <v>0.1729690175181531</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5620509870384806</v>
+        <v>0.5557358074088348</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1883486725626448</v>
+        <v>0.1898986725626448</v>
       </c>
       <c r="C91">
-        <v>-2906.161855481623</v>
+        <v>-2986.726572109345</v>
       </c>
       <c r="D91">
-        <v>2009.494208213844</v>
+        <v>1991.827874324274</v>
       </c>
       <c r="E91">
-        <v>3215.517789880335</v>
+        <v>3278.416172618487</v>
       </c>
       <c r="F91">
-        <v>5597.956063695467</v>
+        <v>5660.854446433619</v>
       </c>
       <c r="G91">
         <v>682.3</v>
@@ -8749,37 +8749,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M91">
-        <v>1124.06957759005</v>
+        <v>1136.699572843871</v>
       </c>
       <c r="N91">
-        <v>-499.3838633043357</v>
+        <v>-512.0138585581566</v>
       </c>
       <c r="O91">
-        <v>-124.5463355081013</v>
+        <v>-127.6962563244043</v>
       </c>
       <c r="P91">
-        <v>-374.8375277962344</v>
+        <v>-384.3176022337523</v>
       </c>
       <c r="Q91">
-        <v>-305.2375277962344</v>
+        <v>-314.7176022337523</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3127840633771681</v>
+        <v>0.339482469714885</v>
       </c>
       <c r="T91">
-        <v>6.165913703860697</v>
+        <v>6.782505074246767</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1386005103677634</v>
+        <v>0.1370605046970104</v>
       </c>
       <c r="W91">
-        <v>0.1729690175181531</v>
+        <v>0.1732782506568403</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5557358074088348</v>
+        <v>0.5495609651042921</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1898986725626448</v>
+        <v>0.1914486725626448</v>
       </c>
       <c r="C92">
-        <v>-2986.726572109345</v>
+        <v>-3066.98337099043</v>
       </c>
       <c r="D92">
-        <v>1991.827874324274</v>
+        <v>1974.469458181341</v>
       </c>
       <c r="E92">
-        <v>3278.416172618487</v>
+        <v>3341.314555356638</v>
       </c>
       <c r="F92">
-        <v>5660.854446433619</v>
+        <v>5723.752829171771</v>
       </c>
       <c r="G92">
         <v>682.3</v>
@@ -8831,37 +8831,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M92">
-        <v>1136.699572843871</v>
+        <v>1149.329568097692</v>
       </c>
       <c r="N92">
-        <v>-512.0138585581566</v>
+        <v>-524.6438538119775</v>
       </c>
       <c r="O92">
-        <v>-127.6962563244043</v>
+        <v>-130.8461771407072</v>
       </c>
       <c r="P92">
-        <v>-384.3176022337523</v>
+        <v>-393.7976766712703</v>
       </c>
       <c r="Q92">
-        <v>-314.7176022337523</v>
+        <v>-324.1976766712702</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.339482469714885</v>
+        <v>0.3721138552387611</v>
       </c>
       <c r="T92">
-        <v>6.782505074246767</v>
+        <v>7.536116749163075</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1370605046970104</v>
+        <v>0.1355543453047356</v>
       </c>
       <c r="W92">
-        <v>0.1732782506568403</v>
+        <v>0.1735806874628091</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5495609651042921</v>
+        <v>0.5435218336196295</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1914486725626448</v>
+        <v>0.1929986725626448</v>
       </c>
       <c r="C93">
-        <v>-3066.98337099043</v>
+        <v>-3146.940232914528</v>
       </c>
       <c r="D93">
-        <v>1974.469458181341</v>
+        <v>1957.410978995394</v>
       </c>
       <c r="E93">
-        <v>3341.314555356638</v>
+        <v>3404.212938094789</v>
       </c>
       <c r="F93">
-        <v>5723.752829171771</v>
+        <v>5786.651211909922</v>
       </c>
       <c r="G93">
         <v>682.3</v>
@@ -8913,37 +8913,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M93">
-        <v>1149.329568097692</v>
+        <v>1161.959563351512</v>
       </c>
       <c r="N93">
-        <v>-524.6438538119775</v>
+        <v>-537.2738490657981</v>
       </c>
       <c r="O93">
-        <v>-130.8461771407072</v>
+        <v>-133.9960979570101</v>
       </c>
       <c r="P93">
-        <v>-393.7976766712703</v>
+        <v>-403.277751108788</v>
       </c>
       <c r="Q93">
-        <v>-324.1976766712702</v>
+        <v>-333.677751108788</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3721138552387611</v>
+        <v>0.4129030871436063</v>
       </c>
       <c r="T93">
-        <v>7.536116749163075</v>
+        <v>8.47813134280846</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1355543453047356</v>
+        <v>0.134080928507945</v>
       </c>
       <c r="W93">
-        <v>0.1735806874628091</v>
+        <v>0.1738765495556046</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5435218336196295</v>
+        <v>0.5376139876020249</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1929986725626448</v>
+        <v>0.1945486725626448</v>
       </c>
       <c r="C94">
-        <v>-3146.940232914528</v>
+        <v>-3226.604865232726</v>
       </c>
       <c r="D94">
-        <v>1957.410978995394</v>
+        <v>1940.644729415347</v>
       </c>
       <c r="E94">
-        <v>3404.212938094789</v>
+        <v>3467.111320832941</v>
       </c>
       <c r="F94">
-        <v>5786.651211909922</v>
+        <v>5849.549594648073</v>
       </c>
       <c r="G94">
         <v>682.3</v>
@@ -8995,37 +8995,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M94">
-        <v>1161.959563351512</v>
+        <v>1174.589558605333</v>
       </c>
       <c r="N94">
-        <v>-537.2738490657981</v>
+        <v>-549.903844319619</v>
       </c>
       <c r="O94">
-        <v>-133.9960979570101</v>
+        <v>-137.146018773313</v>
       </c>
       <c r="P94">
-        <v>-403.277751108788</v>
+        <v>-412.757825546306</v>
       </c>
       <c r="Q94">
-        <v>-333.677751108788</v>
+        <v>-343.157825546306</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4129030871436063</v>
+        <v>0.4653463853069788</v>
       </c>
       <c r="T94">
-        <v>8.47813134280846</v>
+        <v>9.689292963209672</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.134080928507945</v>
+        <v>0.1326391980938811</v>
       </c>
       <c r="W94">
-        <v>0.1738765495556046</v>
+        <v>0.1741660490227487</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5376139876020249</v>
+        <v>0.5318331920364117</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1945486725626448</v>
+        <v>0.1960986725626448</v>
       </c>
       <c r="C95">
-        <v>-3226.604865232726</v>
+        <v>-3305.984713468816</v>
       </c>
       <c r="D95">
-        <v>1940.644729415347</v>
+        <v>1924.163263917409</v>
       </c>
       <c r="E95">
-        <v>3467.111320832941</v>
+        <v>3530.009703571092</v>
       </c>
       <c r="F95">
-        <v>5849.549594648073</v>
+        <v>5912.447977386225</v>
       </c>
       <c r="G95">
         <v>682.3</v>
@@ -9077,37 +9077,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M95">
-        <v>1174.589558605333</v>
+        <v>1187.219553859154</v>
       </c>
       <c r="N95">
-        <v>-549.903844319619</v>
+        <v>-562.5338395734399</v>
       </c>
       <c r="O95">
-        <v>-137.146018773313</v>
+        <v>-140.2959395896159</v>
       </c>
       <c r="P95">
-        <v>-412.757825546306</v>
+        <v>-422.237899983824</v>
       </c>
       <c r="Q95">
-        <v>-343.157825546306</v>
+        <v>-352.637899983824</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4653463853069788</v>
+        <v>0.535270782858142</v>
       </c>
       <c r="T95">
-        <v>9.689292963209672</v>
+        <v>11.30417512374462</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1326391980938811</v>
+        <v>0.13122814279501</v>
       </c>
       <c r="W95">
-        <v>0.1741660490227487</v>
+        <v>0.174449388926762</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5318331920364117</v>
+        <v>0.5261753921211307</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1960986725626448</v>
+        <v>0.1976486725626448</v>
       </c>
       <c r="C96">
-        <v>-3305.984713468816</v>
+        <v>-3385.086972343865</v>
       </c>
       <c r="D96">
-        <v>1924.163263917409</v>
+        <v>1907.95938778051</v>
       </c>
       <c r="E96">
-        <v>3530.009703571092</v>
+        <v>3592.908086309243</v>
       </c>
       <c r="F96">
-        <v>5912.447977386225</v>
+        <v>5975.346360124376</v>
       </c>
       <c r="G96">
         <v>682.3</v>
@@ -9159,37 +9159,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M96">
-        <v>1187.219553859154</v>
+        <v>1199.849549112975</v>
       </c>
       <c r="N96">
-        <v>-562.5338395734399</v>
+        <v>-575.1638348272605</v>
       </c>
       <c r="O96">
-        <v>-140.2959395896159</v>
+        <v>-143.4458604059188</v>
       </c>
       <c r="P96">
-        <v>-422.237899983824</v>
+        <v>-431.7179744213418</v>
       </c>
       <c r="Q96">
-        <v>-352.637899983824</v>
+        <v>-362.1179744213417</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.535270782858142</v>
+        <v>0.6331649394297707</v>
       </c>
       <c r="T96">
-        <v>11.30417512374462</v>
+        <v>13.56501014849355</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.13122814279501</v>
+        <v>0.1298467939234836</v>
       </c>
       <c r="W96">
-        <v>0.174449388926762</v>
+        <v>0.1747267637801645</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5261753921211307</v>
+        <v>0.5206367037830135</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1976486725626448</v>
+        <v>0.1991986725626448</v>
       </c>
       <c r="C97">
-        <v>-3385.086972343865</v>
+        <v>-3463.918596248409</v>
       </c>
       <c r="D97">
-        <v>1907.95938778051</v>
+        <v>1892.026146614119</v>
       </c>
       <c r="E97">
-        <v>3592.908086309243</v>
+        <v>3655.806469047395</v>
       </c>
       <c r="F97">
-        <v>5975.346360124376</v>
+        <v>6038.244742862527</v>
       </c>
       <c r="G97">
         <v>682.3</v>
@@ -9241,37 +9241,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M97">
-        <v>1199.849549112975</v>
+        <v>1212.479544366796</v>
       </c>
       <c r="N97">
-        <v>-575.1638348272605</v>
+        <v>-587.7938300810814</v>
       </c>
       <c r="O97">
-        <v>-143.4458604059188</v>
+        <v>-146.5957812222217</v>
       </c>
       <c r="P97">
-        <v>-431.7179744213418</v>
+        <v>-441.1980488588597</v>
       </c>
       <c r="Q97">
-        <v>-362.1179744213417</v>
+        <v>-371.5980488588597</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6331649394297707</v>
+        <v>0.7800061742872136</v>
       </c>
       <c r="T97">
-        <v>13.56501014849355</v>
+        <v>16.95626268561695</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1298467939234836</v>
+        <v>0.1284942231534473</v>
       </c>
       <c r="W97">
-        <v>0.1747267637801645</v>
+        <v>0.1749983599907878</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5206367037830135</v>
+        <v>0.5152134047852738</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1991986725626448</v>
+        <v>0.2007486725626448</v>
       </c>
       <c r="C98">
-        <v>-3463.918596248408</v>
+        <v>-3542.486309194256</v>
       </c>
       <c r="D98">
-        <v>1892.026146614119</v>
+        <v>1876.356816406422</v>
       </c>
       <c r="E98">
-        <v>3655.806469047394</v>
+        <v>3718.704851785546</v>
       </c>
       <c r="F98">
-        <v>6038.244742862526</v>
+        <v>6101.143125600678</v>
       </c>
       <c r="G98">
         <v>682.3</v>
@@ -9323,37 +9323,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M98">
-        <v>1212.479544366795</v>
+        <v>1225.109539620616</v>
       </c>
       <c r="N98">
-        <v>-587.7938300810812</v>
+        <v>-600.4238253349021</v>
       </c>
       <c r="O98">
-        <v>-146.5957812222217</v>
+        <v>-149.7457020385246</v>
       </c>
       <c r="P98">
-        <v>-441.1980488588595</v>
+        <v>-450.6781232963775</v>
       </c>
       <c r="Q98">
-        <v>-371.5980488588595</v>
+        <v>-381.0781232963775</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7800061742872116</v>
+        <v>1.024741565716282</v>
       </c>
       <c r="T98">
-        <v>16.9562626856169</v>
+        <v>22.6083502474892</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1284942231534473</v>
+        <v>0.1271695404405252</v>
       </c>
       <c r="W98">
-        <v>0.1749983599907878</v>
+        <v>0.1752643562795425</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5152134047852739</v>
+        <v>0.5099019263854256</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2007486725626448</v>
+        <v>0.2022986725626447</v>
       </c>
       <c r="C99">
-        <v>-3542.486309194256</v>
+        <v>-3620.79661427586</v>
       </c>
       <c r="D99">
-        <v>1876.356816406422</v>
+        <v>1860.94489406297</v>
       </c>
       <c r="E99">
-        <v>3718.704851785546</v>
+        <v>3781.603234523697</v>
       </c>
       <c r="F99">
-        <v>6101.143125600678</v>
+        <v>6164.04150833883</v>
       </c>
       <c r="G99">
         <v>682.3</v>
@@ -9405,37 +9405,37 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M99">
-        <v>1225.109539620616</v>
+        <v>1237.739534874437</v>
       </c>
       <c r="N99">
-        <v>-600.4238253349021</v>
+        <v>-613.0538205887229</v>
       </c>
       <c r="O99">
-        <v>-149.7457020385246</v>
+        <v>-152.8956228548275</v>
       </c>
       <c r="P99">
-        <v>-450.6781232963775</v>
+        <v>-460.1581977338955</v>
       </c>
       <c r="Q99">
-        <v>-381.0781232963775</v>
+        <v>-390.5581977338954</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.024741565716282</v>
+        <v>1.514212348574423</v>
       </c>
       <c r="T99">
-        <v>22.6083502474892</v>
+        <v>33.9125253712338</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1271695404405252</v>
+        <v>0.1258718920686831</v>
       </c>
       <c r="W99">
-        <v>0.1752643562795425</v>
+        <v>0.1755249240726084</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5099019263854256</v>
+        <v>0.5046988455039416</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2022986725626447</v>
+        <v>0.2391120574518767</v>
       </c>
       <c r="C100">
-        <v>-3620.79661427586</v>
+        <v>-3987.469648834779</v>
       </c>
       <c r="D100">
-        <v>1860.94489406297</v>
+        <v>1557.170242242201</v>
       </c>
       <c r="E100">
-        <v>3781.603234523697</v>
+        <v>3844.501617261848</v>
       </c>
       <c r="F100">
-        <v>6164.04150833883</v>
+        <v>6226.939891076981</v>
       </c>
       <c r="G100">
         <v>682.3</v>
@@ -9487,129 +9487,47 @@
         <v>624.6857142857142</v>
       </c>
       <c r="M100">
-        <v>1237.739534874437</v>
+        <v>1468.312426315952</v>
       </c>
       <c r="N100">
-        <v>-613.0538205887229</v>
+        <v>-843.6267120302379</v>
       </c>
       <c r="O100">
-        <v>-152.8956228548275</v>
+        <v>-210.4005019803413</v>
       </c>
       <c r="P100">
-        <v>-460.1581977338955</v>
+        <v>-633.2262100498965</v>
       </c>
       <c r="Q100">
-        <v>-390.5581977338954</v>
+        <v>-563.6262100498965</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.514212348574423</v>
+        <v>3.043963186072048</v>
       </c>
       <c r="T100">
-        <v>33.9125253712338</v>
+        <v>69.24164402013967</v>
       </c>
       <c r="U100">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1258718920686831</v>
+        <v>0.1061059038598184</v>
       </c>
       <c r="W100">
-        <v>0.1755249240726084</v>
+        <v>0.2107802278698548</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5046988455039416</v>
+        <v>0.4254446826777002</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2391120574518767</v>
-      </c>
-      <c r="C101">
-        <v>-3987.469648834779</v>
-      </c>
-      <c r="D101">
-        <v>1557.170242242201</v>
-      </c>
-      <c r="E101">
-        <v>3844.501617261848</v>
-      </c>
-      <c r="F101">
-        <v>6226.939891076981</v>
-      </c>
-      <c r="G101">
-        <v>682.3</v>
-      </c>
-      <c r="H101">
-        <v>3907.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>694.2857142857142</v>
-      </c>
-      <c r="K101">
-        <v>69.60000000000002</v>
-      </c>
-      <c r="L101">
-        <v>624.6857142857142</v>
-      </c>
-      <c r="M101">
-        <v>1468.312426315952</v>
-      </c>
-      <c r="N101">
-        <v>-843.6267120302379</v>
-      </c>
-      <c r="O101">
-        <v>-210.4005019803413</v>
-      </c>
-      <c r="P101">
-        <v>-633.2262100498965</v>
-      </c>
-      <c r="Q101">
-        <v>-563.6262100498965</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.043963186072048</v>
-      </c>
-      <c r="T101">
-        <v>69.24164402013967</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1061059038598184</v>
-      </c>
-      <c r="W101">
-        <v>0.2107802278698548</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4254446826777002</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
